--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\NewGit\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CBB15B6-7C27-47A9-AB7D-83A672447B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EBE3927-517E-4925-AF9C-6A987DACDD8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="31" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="24" activeTab="29" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
   <sheets>
     <sheet name="Fevrier" sheetId="3" r:id="rId1"/>
@@ -23894,8 +23894,8 @@
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11">
-        <f>6500+1500</f>
-        <v>8000</v>
+        <f>6500+1000</f>
+        <v>7500</v>
       </c>
       <c r="I4" s="11"/>
       <c r="J4" s="12"/>
@@ -24688,7 +24688,7 @@
       </c>
       <c r="C34" s="11">
         <f>H4-D26</f>
-        <v>2053</v>
+        <v>1553</v>
       </c>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
@@ -25561,6 +25561,9 @@
       <c r="L11" t="s">
         <v>222</v>
       </c>
+      <c r="M11">
+        <v>500</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J12">
@@ -25587,7 +25590,7 @@
       </c>
       <c r="J16">
         <f>J14-M22</f>
-        <v>3116</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -25610,13 +25613,13 @@
       </c>
       <c r="B20">
         <f>B6-F41</f>
-        <v>19500</v>
+        <v>18500</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="M22">
         <f>SUM(M7:M20)</f>
-        <v>2000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -25694,7 +25697,9 @@
         <v>222</v>
       </c>
       <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
+      <c r="C30" s="17">
+        <v>1000</v>
+      </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
@@ -25795,7 +25800,7 @@
       </c>
       <c r="C41" s="18">
         <f>SUM(C27:C39)</f>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D41" s="18">
         <f>SUM(D27:D39)</f>
@@ -25807,7 +25812,7 @@
       </c>
       <c r="F41" s="18">
         <f>SUM(B41:E41)</f>
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
   </sheetData>
@@ -26353,7 +26358,7 @@
   <dimension ref="A1:R94"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
@@ -27269,15 +27274,15 @@
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="A76" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="B76">
+      <c r="B76" s="5">
         <v>675000</v>
       </c>
-      <c r="C76">
-        <f>300000+150000</f>
-        <v>450000</v>
+      <c r="C76" s="5">
+        <f>300000+150000+125000+100000</f>
+        <v>675000</v>
       </c>
       <c r="K76" t="s">
         <v>443</v>
@@ -27296,10 +27301,11 @@
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="A77" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="C77">
+      <c r="B77" s="5"/>
+      <c r="C77" s="5">
         <f>300000+201000+150000</f>
         <v>651000</v>
       </c>
@@ -27375,7 +27381,7 @@
       </c>
       <c r="C84">
         <f>SUM(C67:C82)</f>
-        <v>6476750</v>
+        <v>6701750</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
@@ -27388,7 +27394,7 @@
       </c>
       <c r="C85">
         <f>C84/655</f>
-        <v>9888.1679389312976</v>
+        <v>10231.679389312978</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
@@ -27447,7 +27453,7 @@
       </c>
       <c r="B90">
         <f>B88-C85</f>
-        <v>-88.167938931297613</v>
+        <v>-431.67938931297795</v>
       </c>
       <c r="L90">
         <f>L87*7000</f>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\NewGit\myDocs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AG_AUTOMATION\Documents\projet-git\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EBE3927-517E-4925-AF9C-6A987DACDD8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2EE9FF-CE24-4CF7-9262-6EE40DA5D2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="24" activeTab="29" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="24" activeTab="31" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
   <sheets>
     <sheet name="Fevrier" sheetId="3" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="459">
   <si>
     <t>Loyer</t>
   </si>
@@ -1441,6 +1441,12 @@
   </si>
   <si>
     <t>sous escalier</t>
+  </si>
+  <si>
+    <t>Escalier</t>
+  </si>
+  <si>
+    <t>Temu</t>
   </si>
 </sst>
 </file>
@@ -26355,7 +26361,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94700D3-58F8-480F-AA59-9339E917FDF7}">
-  <dimension ref="A1:R94"/>
+  <dimension ref="A1:R96"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
@@ -27355,125 +27361,148 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>457</v>
+      </c>
+      <c r="B81">
+        <v>480000</v>
+      </c>
+      <c r="C81">
+        <v>280000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>455</v>
       </c>
-      <c r="C81">
+      <c r="C82">
         <f>292000</f>
         <v>292000</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>458</v>
+      </c>
+      <c r="B83">
+        <v>200000</v>
+      </c>
+      <c r="C83">
+        <f>50000</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>433</v>
       </c>
-      <c r="C82">
+      <c r="C84">
         <f>200000</f>
         <v>200000</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>6</v>
       </c>
-      <c r="B84">
-        <f>SUM(B67:B82)</f>
-        <v>8095750</v>
-      </c>
-      <c r="C84">
-        <f>SUM(C67:C82)</f>
-        <v>6701750</v>
-      </c>
-    </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="B86">
+        <f>SUM(B67:B84)</f>
+        <v>8775750</v>
+      </c>
+      <c r="C86">
+        <f>SUM(C67:C84)</f>
+        <v>7031750</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>421</v>
       </c>
-      <c r="B85">
-        <f>B84/655</f>
-        <v>12359.923664122138</v>
-      </c>
-      <c r="C85">
-        <f>C84/655</f>
-        <v>10231.679389312978</v>
-      </c>
-    </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="H86" t="s">
+      <c r="B87">
+        <f>B86/655</f>
+        <v>13398.091603053435</v>
+      </c>
+      <c r="C87">
+        <f>C86/655</f>
+        <v>10735.496183206107</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H88" t="s">
         <v>453</v>
       </c>
-      <c r="I86">
+      <c r="I88">
         <f>SUM(I74:I80)</f>
         <v>45.894999999999996</v>
       </c>
-      <c r="K86" t="s">
+      <c r="K88" t="s">
         <v>6</v>
       </c>
-      <c r="L86">
-        <f>SUM(L72:L85)</f>
+      <c r="L88">
+        <f>SUM(L72:L87)</f>
         <v>84.603999999999985</v>
       </c>
-      <c r="N86" t="s">
+      <c r="N88" t="s">
         <v>6</v>
       </c>
-      <c r="O86">
-        <f t="shared" ref="O86" si="0">SUM(O72:O85)</f>
+      <c r="O88">
+        <f t="shared" ref="O88" si="0">SUM(O72:O87)</f>
         <v>11.743600000000001</v>
       </c>
-      <c r="Q86" t="s">
+      <c r="Q88" t="s">
         <v>175</v>
       </c>
-      <c r="R86">
-        <f t="shared" ref="R86" si="1">SUM(R72:R85)</f>
+      <c r="R88">
+        <f t="shared" ref="R88" si="1">SUM(R72:R87)</f>
         <v>67.2</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="L87">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L89">
         <v>130</v>
       </c>
-      <c r="O87">
+      <c r="O89">
         <v>6</v>
       </c>
-      <c r="R87">
+      <c r="R89">
         <v>67</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>417</v>
       </c>
-      <c r="B88">
+      <c r="B90">
         <f>2000+4000+3000+800</f>
         <v>9800</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>99</v>
       </c>
-      <c r="B90">
-        <f>B88-C85</f>
-        <v>-431.67938931297795</v>
-      </c>
-      <c r="L90">
-        <f>L87*7000</f>
+      <c r="B92">
+        <f>B90-C87</f>
+        <v>-935.49618320610716</v>
+      </c>
+      <c r="L92">
+        <f>L89*7000</f>
         <v>910000</v>
       </c>
-      <c r="O90">
-        <f>O87*5000</f>
+      <c r="O92">
+        <f>O89*5000</f>
         <v>30000</v>
       </c>
-      <c r="R90">
-        <f>R87*5500</f>
+      <c r="R92">
+        <f>R89*5500</f>
         <v>368500</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K94" t="s">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="K96" t="s">
         <v>175</v>
       </c>
-      <c r="M94">
-        <f>I90+L90+O90+R90</f>
+      <c r="M96">
+        <f>I92+L92+O92+R92</f>
         <v>1308500</v>
       </c>
     </row>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AG_AUTOMATION\Documents\projet-git\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2EE9FF-CE24-4CF7-9262-6EE40DA5D2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E80E9E-4B53-4AA2-AE99-49FA886FD185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="24" activeTab="31" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="461">
   <si>
     <t>Loyer</t>
   </si>
@@ -1447,6 +1447,12 @@
   </si>
   <si>
     <t>Temu</t>
+  </si>
+  <si>
+    <t>Avril</t>
+  </si>
+  <si>
+    <t>fervier</t>
   </si>
 </sst>
 </file>
@@ -27085,7 +27091,7 @@
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="A67" s="5" t="s">
         <v>407</v>
       </c>
       <c r="B67" s="5">
@@ -27098,7 +27104,7 @@
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="A68" s="5" t="s">
         <v>408</v>
       </c>
       <c r="B68" s="5">
@@ -27109,7 +27115,7 @@
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="A69" s="5" t="s">
         <v>409</v>
       </c>
       <c r="B69" s="5">
@@ -27120,7 +27126,7 @@
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="A70" s="5" t="s">
         <v>410</v>
       </c>
       <c r="B70" s="5">
@@ -27131,7 +27137,7 @@
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="A71" s="5" t="s">
         <v>412</v>
       </c>
       <c r="B71" s="5">
@@ -27151,7 +27157,7 @@
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="A72" s="5" t="s">
         <v>416</v>
       </c>
       <c r="B72" s="5">
@@ -27217,15 +27223,15 @@
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="A74" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="B74">
+      <c r="B74" s="5">
         <v>2100000</v>
       </c>
-      <c r="C74">
-        <f>500000+200000+300000+200000+100000+250000+150000</f>
-        <v>1700000</v>
+      <c r="C74" s="5">
+        <f>500000+200000+300000+200000+100000+250000+150000+300000</f>
+        <v>2000000</v>
       </c>
       <c r="H74" t="s">
         <v>441</v>
@@ -27250,14 +27256,14 @@
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="A75" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="B75">
+      <c r="B75" s="5">
         <f>675000+120000</f>
         <v>795000</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="5">
         <f>73000+73000+73000+73000+73000+88000</f>
         <v>453000</v>
       </c>
@@ -27310,7 +27316,9 @@
       <c r="A77" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="B77" s="5"/>
+      <c r="B77" s="5">
+        <v>650000</v>
+      </c>
       <c r="C77" s="5">
         <f>300000+201000+150000</f>
         <v>651000</v>
@@ -27345,10 +27353,13 @@
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="A80" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="C80">
+      <c r="B80" s="5">
+        <v>155000</v>
+      </c>
+      <c r="C80" s="5">
         <f>155000</f>
         <v>155000</v>
       </c>
@@ -27371,10 +27382,13 @@
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="A82" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="C82">
+      <c r="B82" s="5">
+        <v>292000</v>
+      </c>
+      <c r="C82" s="5">
         <f>292000</f>
         <v>292000</v>
       </c>
@@ -27392,10 +27406,13 @@
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="A84" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="C84">
+      <c r="B84" s="5">
+        <v>200000</v>
+      </c>
+      <c r="C84" s="5">
         <f>200000</f>
         <v>200000</v>
       </c>
@@ -27406,11 +27423,11 @@
       </c>
       <c r="B86">
         <f>SUM(B67:B84)</f>
-        <v>8775750</v>
+        <v>10072750</v>
       </c>
       <c r="C86">
         <f>SUM(C67:C84)</f>
-        <v>7031750</v>
+        <v>7331750</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
@@ -27419,11 +27436,11 @@
       </c>
       <c r="B87">
         <f>B86/655</f>
-        <v>13398.091603053435</v>
+        <v>15378.24427480916</v>
       </c>
       <c r="C87">
         <f>C86/655</f>
-        <v>10735.496183206107</v>
+        <v>11193.511450381679</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
@@ -27472,8 +27489,23 @@
         <v>417</v>
       </c>
       <c r="B90">
-        <f>2000+4000+3000+800</f>
-        <v>9800</v>
+        <f>2000+4000+3000+800+1500</f>
+        <v>11300</v>
+      </c>
+      <c r="C90" t="s">
+        <v>234</v>
+      </c>
+      <c r="D90" t="s">
+        <v>240</v>
+      </c>
+      <c r="E90" t="s">
+        <v>460</v>
+      </c>
+      <c r="F90" t="s">
+        <v>222</v>
+      </c>
+      <c r="G90" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
@@ -27482,7 +27514,7 @@
       </c>
       <c r="B92">
         <f>B90-C87</f>
-        <v>-935.49618320610716</v>
+        <v>106.48854961832149</v>
       </c>
       <c r="L92">
         <f>L89*7000</f>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AG_AUTOMATION\Documents\projet-git\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E80E9E-4B53-4AA2-AE99-49FA886FD185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC9D1F1-9641-4DF3-B2D2-6B50F41A88C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="24" activeTab="31" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="24" activeTab="31" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
   <sheets>
     <sheet name="Fevrier" sheetId="3" r:id="rId1"/>
@@ -27337,13 +27337,28 @@
       <c r="B78">
         <v>1500000</v>
       </c>
+      <c r="C78">
+        <f>500000</f>
+        <v>500000</v>
+      </c>
+      <c r="E78">
+        <f>45*6750</f>
+        <v>303750</v>
+      </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>435</v>
       </c>
       <c r="B79">
-        <v>400000</v>
+        <v>450000</v>
+      </c>
+      <c r="C79">
+        <v>250000</v>
+      </c>
+      <c r="D79">
+        <f>30000+50000</f>
+        <v>80000</v>
       </c>
       <c r="H79" t="s">
         <v>456</v>
@@ -27423,11 +27438,11 @@
       </c>
       <c r="B86">
         <f>SUM(B67:B84)</f>
-        <v>10072750</v>
+        <v>10122750</v>
       </c>
       <c r="C86">
-        <f>SUM(C67:C84)</f>
-        <v>7331750</v>
+        <f>SUM(C67:C84)+D79</f>
+        <v>8161750</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
@@ -27436,11 +27451,11 @@
       </c>
       <c r="B87">
         <f>B86/655</f>
-        <v>15378.24427480916</v>
+        <v>15454.580152671755</v>
       </c>
       <c r="C87">
         <f>C86/655</f>
-        <v>11193.511450381679</v>
+        <v>12460.687022900764</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
@@ -27514,7 +27529,7 @@
       </c>
       <c r="B92">
         <f>B90-C87</f>
-        <v>106.48854961832149</v>
+        <v>-1160.6870229007636</v>
       </c>
       <c r="L92">
         <f>L89*7000</f>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AG_AUTOMATION\Documents\projet-git\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC9D1F1-9641-4DF3-B2D2-6B50F41A88C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64024D3F-B513-46B5-9FBE-B54D7721832B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="24" activeTab="31" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="24" activeTab="29" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
   <sheets>
     <sheet name="Fevrier" sheetId="3" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="462">
   <si>
     <t>Loyer</t>
   </si>
@@ -1453,6 +1453,9 @@
   </si>
   <si>
     <t>fervier</t>
+  </si>
+  <si>
+    <t>chambre, elhad, SDE</t>
   </si>
 </sst>
 </file>
@@ -25584,6 +25587,9 @@
       <c r="L12" t="s">
         <v>427</v>
       </c>
+      <c r="M12">
+        <v>500</v>
+      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="L13" t="s">
@@ -25602,7 +25608,7 @@
       </c>
       <c r="J16">
         <f>J14-M22</f>
-        <v>2616</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -25625,13 +25631,13 @@
       </c>
       <c r="B20">
         <f>B6-F41</f>
-        <v>18500</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="M22">
         <f>SUM(M7:M20)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -25720,7 +25726,9 @@
       <c r="A31" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="B31" s="17"/>
+      <c r="B31" s="17">
+        <v>500</v>
+      </c>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
@@ -25808,7 +25816,7 @@
       </c>
       <c r="B41" s="18">
         <f>SUM(B27:B39)</f>
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="C41" s="18">
         <f>SUM(C27:C39)</f>
@@ -25824,7 +25832,7 @@
       </c>
       <c r="F41" s="18">
         <f>SUM(B41:E41)</f>
-        <v>3000</v>
+        <v>3500</v>
       </c>
     </row>
   </sheetData>
@@ -27357,8 +27365,11 @@
         <v>250000</v>
       </c>
       <c r="D79">
-        <f>30000+50000</f>
-        <v>80000</v>
+        <f>30000+50000+150000</f>
+        <v>230000</v>
+      </c>
+      <c r="E79" t="s">
+        <v>461</v>
       </c>
       <c r="H79" t="s">
         <v>456</v>
@@ -27442,7 +27453,7 @@
       </c>
       <c r="C86">
         <f>SUM(C67:C84)+D79</f>
-        <v>8161750</v>
+        <v>8311750</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
@@ -27455,7 +27466,7 @@
       </c>
       <c r="C87">
         <f>C86/655</f>
-        <v>12460.687022900764</v>
+        <v>12689.694656488549</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
@@ -27503,9 +27514,8 @@
       <c r="A90" t="s">
         <v>417</v>
       </c>
-      <c r="B90">
-        <f>2000+4000+3000+800+1500</f>
-        <v>11300</v>
+      <c r="B90" t="s">
+        <v>216</v>
       </c>
       <c r="C90" t="s">
         <v>234</v>
@@ -27527,9 +27537,9 @@
       <c r="A92" t="s">
         <v>99</v>
       </c>
-      <c r="B92">
+      <c r="B92" t="e">
         <f>B90-C87</f>
-        <v>-1160.6870229007636</v>
+        <v>#VALUE!</v>
       </c>
       <c r="L92">
         <f>L89*7000</f>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AG_AUTOMATION\Documents\projet-git\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64024D3F-B513-46B5-9FBE-B54D7721832B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04367D7F-80F7-4910-BFFD-59470B388622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="24" activeTab="29" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="24" activeTab="31" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
   <sheets>
     <sheet name="Fevrier" sheetId="3" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="462">
   <si>
     <t>Loyer</t>
   </si>
@@ -27346,8 +27346,8 @@
         <v>1500000</v>
       </c>
       <c r="C78">
-        <f>500000</f>
-        <v>500000</v>
+        <f>500000+500000+300000</f>
+        <v>1300000</v>
       </c>
       <c r="E78">
         <f>45*6750</f>
@@ -27404,7 +27404,8 @@
         <v>480000</v>
       </c>
       <c r="C81">
-        <v>280000</v>
+        <f>280000+100000</f>
+        <v>380000</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
@@ -27427,8 +27428,8 @@
         <v>200000</v>
       </c>
       <c r="C83">
-        <f>50000</f>
-        <v>50000</v>
+        <f>50000+50000</f>
+        <v>100000</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
@@ -27453,7 +27454,7 @@
       </c>
       <c r="C86">
         <f>SUM(C67:C84)+D79</f>
-        <v>8311750</v>
+        <v>9261750</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
@@ -27466,7 +27467,7 @@
       </c>
       <c r="C87">
         <f>C86/655</f>
-        <v>12689.694656488549</v>
+        <v>14140.076335877862</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
@@ -27514,8 +27515,9 @@
       <c r="A90" t="s">
         <v>417</v>
       </c>
-      <c r="B90" t="s">
-        <v>216</v>
+      <c r="B90">
+        <f>2000+4000+3000+800+1500</f>
+        <v>11300</v>
       </c>
       <c r="C90" t="s">
         <v>234</v>
@@ -27537,9 +27539,9 @@
       <c r="A92" t="s">
         <v>99</v>
       </c>
-      <c r="B92" t="e">
+      <c r="B92">
         <f>B90-C87</f>
-        <v>#VALUE!</v>
+        <v>-2840.0763358778622</v>
       </c>
       <c r="L92">
         <f>L89*7000</f>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AG_AUTOMATION\Documents\projet-git\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04367D7F-80F7-4910-BFFD-59470B388622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{884F41B5-0A57-4B18-8344-C7D5053DB1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="24" activeTab="31" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="24" activeTab="32" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
   <sheets>
     <sheet name="Fevrier" sheetId="3" r:id="rId1"/>
@@ -42,14 +42,15 @@
     <sheet name="FEVR25" sheetId="46" r:id="rId27"/>
     <sheet name="Mars25" sheetId="47" r:id="rId28"/>
     <sheet name="Avril25" sheetId="48" r:id="rId29"/>
-    <sheet name="Credit" sheetId="28" r:id="rId30"/>
-    <sheet name="Entreprise" sheetId="35" r:id="rId31"/>
-    <sheet name="Construction " sheetId="27" r:id="rId32"/>
-    <sheet name="Construction2" sheetId="39" r:id="rId33"/>
-    <sheet name="Terrain" sheetId="18" r:id="rId34"/>
-    <sheet name="Poulailler" sheetId="20" r:id="rId35"/>
-    <sheet name="divers " sheetId="22" r:id="rId36"/>
-    <sheet name="MB MEACSYTEM" sheetId="40" r:id="rId37"/>
+    <sheet name="Mai25" sheetId="49" r:id="rId30"/>
+    <sheet name="Credit" sheetId="28" r:id="rId31"/>
+    <sheet name="Entreprise" sheetId="35" r:id="rId32"/>
+    <sheet name="Construction " sheetId="27" r:id="rId33"/>
+    <sheet name="Construction2" sheetId="39" r:id="rId34"/>
+    <sheet name="Terrain" sheetId="18" r:id="rId35"/>
+    <sheet name="Poulailler" sheetId="20" r:id="rId36"/>
+    <sheet name="divers " sheetId="22" r:id="rId37"/>
+    <sheet name="MB MEACSYTEM" sheetId="40" r:id="rId38"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -70,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="463">
   <si>
     <t>Loyer</t>
   </si>
@@ -1456,6 +1457,9 @@
   </si>
   <si>
     <t>chambre, elhad, SDE</t>
+  </si>
+  <si>
+    <t>Mai</t>
   </si>
 </sst>
 </file>
@@ -24025,7 +24029,9 @@
       <c r="E8" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="F8" s="11"/>
+      <c r="F8" s="11">
+        <v>1000</v>
+      </c>
       <c r="G8" s="11"/>
       <c r="H8" s="9"/>
       <c r="I8" s="11"/>
@@ -24420,7 +24426,7 @@
       <c r="E22" s="11"/>
       <c r="F22" s="11">
         <f>SUM(F7:F20)+150</f>
-        <v>2061</v>
+        <v>3061</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
@@ -24516,7 +24522,7 @@
       </c>
       <c r="D26" s="11">
         <f>C22+F22+I22</f>
-        <v>5947</v>
+        <v>6947</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
@@ -24588,7 +24594,7 @@
       </c>
       <c r="C29" s="11">
         <f>ABS(G4-D26)</f>
-        <v>5947</v>
+        <v>6947</v>
       </c>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
@@ -24703,7 +24709,7 @@
       </c>
       <c r="C34" s="11">
         <f>H4-D26</f>
-        <v>1553</v>
+        <v>553</v>
       </c>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
@@ -24713,7 +24719,7 @@
       <c r="I34" s="11"/>
       <c r="J34" s="11">
         <f>C29+L29</f>
-        <v>6451</v>
+        <v>7451</v>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="11"/>
@@ -25415,6 +25421,1258 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBC3F25E-31C5-496E-8089-BC63A88237EF}">
+  <dimension ref="A1:T125"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.125" customWidth="1"/>
+    <col min="9" max="9" width="19.625" customWidth="1"/>
+    <col min="11" max="11" width="8.125" customWidth="1"/>
+    <col min="13" max="13" width="18.125" customWidth="1"/>
+    <col min="18" max="18" width="3.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="10"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="10"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="J3" s="12"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="12"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="10"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11">
+        <v>6600</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="N4" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="O4" s="11">
+        <v>1480</v>
+      </c>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="12"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="10"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="12"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="10"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="15"/>
+      <c r="E6" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="15"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I6" s="14"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="L6" s="15"/>
+      <c r="M6" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="N6" s="15"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="12"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="10"/>
+      <c r="B7" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="F7" s="11">
+        <v>1012</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="N7" s="11">
+        <v>150</v>
+      </c>
+      <c r="O7" s="11"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="12"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="N8" s="11">
+        <v>200</v>
+      </c>
+      <c r="O8" s="11"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="12"/>
+      <c r="T8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="B9" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="11">
+        <v>400</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="F9" s="11">
+        <v>96</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="N9" s="11">
+        <v>200</v>
+      </c>
+      <c r="O9" s="11"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="12"/>
+      <c r="T9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="10"/>
+      <c r="B10" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="C10" s="11">
+        <v>200</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="F10" s="11">
+        <v>50</v>
+      </c>
+      <c r="G10" s="11"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="N10" s="11">
+        <v>300</v>
+      </c>
+      <c r="O10" s="11"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="12"/>
+      <c r="T10">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="10"/>
+      <c r="B11" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="C11" s="11">
+        <v>39</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="11">
+        <v>157</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="N11" s="11">
+        <v>100</v>
+      </c>
+      <c r="O11" s="11"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="12"/>
+      <c r="T11">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="C12" s="11">
+        <v>1500</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="11">
+        <v>300</v>
+      </c>
+      <c r="G12" s="11"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="N12" s="11">
+        <v>13</v>
+      </c>
+      <c r="O12" s="11"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="12"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="10"/>
+      <c r="B13" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="F13" s="11">
+        <v>52</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="N13" s="11">
+        <v>13</v>
+      </c>
+      <c r="O13" s="11"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="12"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="10"/>
+      <c r="B14" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="11">
+        <v>13</v>
+      </c>
+      <c r="G14" s="11"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="12"/>
+      <c r="T14">
+        <f>SUM(T8:T11)</f>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="10"/>
+      <c r="B15" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="F15" s="11">
+        <v>100</v>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="12"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="C16" s="11">
+        <v>247</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="F16" s="11">
+        <v>131</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="12"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="10"/>
+      <c r="B17" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="12"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="10"/>
+      <c r="B18" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="12"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="10"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="12"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="11"/>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="12"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="12"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" s="10"/>
+      <c r="B22" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="11">
+        <f>SUM(C7:C19)</f>
+        <v>2386</v>
+      </c>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11">
+        <f>SUM(F7:F20)+150</f>
+        <v>2061</v>
+      </c>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11">
+        <f>SUM(I7:I19)</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="12"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11">
+        <f>SUM(N7:N19)</f>
+        <v>976</v>
+      </c>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11">
+        <f>SUM(Q7:Q18)</f>
+        <v>0</v>
+      </c>
+      <c r="R22" s="11"/>
+      <c r="S22" s="12"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="12"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="12"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11"/>
+      <c r="R25" s="11"/>
+      <c r="S25" s="12"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="11">
+        <f>C22+F22+I22</f>
+        <v>4447</v>
+      </c>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11">
+        <f>N22+Q22</f>
+        <v>976</v>
+      </c>
+      <c r="Q26" s="11"/>
+      <c r="R26" s="11"/>
+      <c r="S26" s="12"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27" s="10"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="11"/>
+      <c r="R27" s="11"/>
+      <c r="S27" s="12"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" s="10"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="11"/>
+      <c r="P28" s="11"/>
+      <c r="Q28" s="11"/>
+      <c r="R28" s="11"/>
+      <c r="S28" s="12"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29" s="10"/>
+      <c r="B29" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="C29" s="11">
+        <f>ABS(G4-D26)</f>
+        <v>4447</v>
+      </c>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="L29" s="11">
+        <f>O4-P26</f>
+        <v>504</v>
+      </c>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="11"/>
+      <c r="R29" s="11"/>
+      <c r="S29" s="12"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="11"/>
+      <c r="R30" s="11"/>
+      <c r="S30" s="12"/>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="12"/>
+      <c r="P31" s="12"/>
+      <c r="Q31" s="12"/>
+      <c r="R31" s="12"/>
+      <c r="S31" s="12"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="12"/>
+      <c r="P32" s="12"/>
+      <c r="Q32" s="12"/>
+      <c r="R32" s="12"/>
+      <c r="S32" s="12"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="11"/>
+      <c r="P33" s="11"/>
+      <c r="Q33" s="11"/>
+      <c r="R33" s="11"/>
+      <c r="S33" s="11"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34" s="9"/>
+      <c r="B34" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C34" s="11">
+        <f>H4-D26</f>
+        <v>2153</v>
+      </c>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11">
+        <f>C29+L29</f>
+        <v>4951</v>
+      </c>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="11"/>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="11"/>
+      <c r="R34" s="11"/>
+      <c r="S34" s="11"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35" s="9"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="11"/>
+      <c r="P35" s="11"/>
+      <c r="Q35" s="11"/>
+      <c r="R35" s="11"/>
+      <c r="S35" s="11"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="E36">
+        <f>5.2+13.8+10.96+13+13+21+6.99+47+62+12+68+40</f>
+        <v>312.95</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I39" t="s">
+        <v>376</v>
+      </c>
+      <c r="J39">
+        <v>39</v>
+      </c>
+      <c r="L39" t="s">
+        <v>382</v>
+      </c>
+      <c r="M39">
+        <f>SUM(J39:J58)</f>
+        <v>22002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E40" s="22" t="s">
+        <v>364</v>
+      </c>
+      <c r="F40">
+        <v>500</v>
+      </c>
+      <c r="I40" t="s">
+        <v>377</v>
+      </c>
+      <c r="J40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E41" s="22" t="s">
+        <v>365</v>
+      </c>
+      <c r="F41">
+        <v>800</v>
+      </c>
+      <c r="I41" t="s">
+        <v>378</v>
+      </c>
+      <c r="J41">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E42" s="22" t="s">
+        <v>366</v>
+      </c>
+      <c r="F42">
+        <v>200</v>
+      </c>
+      <c r="I42" t="s">
+        <v>379</v>
+      </c>
+      <c r="J42">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E43" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="F43">
+        <v>2000</v>
+      </c>
+      <c r="I43" t="s">
+        <v>380</v>
+      </c>
+      <c r="J43">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E44" s="22" t="s">
+        <v>373</v>
+      </c>
+      <c r="F44">
+        <v>500</v>
+      </c>
+      <c r="I44" t="s">
+        <v>380</v>
+      </c>
+      <c r="J44">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E45" s="22" t="s">
+        <v>368</v>
+      </c>
+      <c r="F45">
+        <v>100</v>
+      </c>
+      <c r="I45" t="s">
+        <v>381</v>
+      </c>
+      <c r="J45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E46" s="22" t="s">
+        <v>369</v>
+      </c>
+      <c r="F46">
+        <v>67</v>
+      </c>
+      <c r="I46" t="s">
+        <v>101</v>
+      </c>
+      <c r="J46">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E47" s="22" t="s">
+        <v>370</v>
+      </c>
+      <c r="F47">
+        <v>50</v>
+      </c>
+      <c r="I47" t="s">
+        <v>383</v>
+      </c>
+      <c r="J47">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E48" s="22" t="s">
+        <v>371</v>
+      </c>
+      <c r="F48">
+        <v>70</v>
+      </c>
+      <c r="I48" t="s">
+        <v>384</v>
+      </c>
+      <c r="J48">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E49" s="22" t="s">
+        <v>372</v>
+      </c>
+      <c r="F49">
+        <v>300</v>
+      </c>
+      <c r="I49" t="s">
+        <v>385</v>
+      </c>
+      <c r="J49">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E50" s="22" t="s">
+        <v>374</v>
+      </c>
+      <c r="F50">
+        <v>100</v>
+      </c>
+      <c r="I50" t="s">
+        <v>108</v>
+      </c>
+      <c r="J50">
+        <v>20914</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I51" t="s">
+        <v>387</v>
+      </c>
+      <c r="J51">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J52">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F54">
+        <f>SUM(F40:F50)</f>
+        <v>4687</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B62" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62" s="11">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="98" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B98">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="99" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B99">
+        <v>2500</v>
+      </c>
+      <c r="J99">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="100" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B100">
+        <v>2500</v>
+      </c>
+      <c r="J100">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="101" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B101">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="102" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B102">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="106" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B106">
+        <f>SUM(B98:B102)</f>
+        <v>9500</v>
+      </c>
+      <c r="D106">
+        <f>B106-7000</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="107" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P107">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="108" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P108" s="11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P109" s="11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P110" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P111" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="112" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P112" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="113" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="P113" s="11">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="114" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="P114" s="11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="115" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="E115">
+        <v>1400</v>
+      </c>
+      <c r="P115" s="11">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="116" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="E116">
+        <v>1300</v>
+      </c>
+      <c r="P116" s="11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="117" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="E117">
+        <v>950</v>
+      </c>
+      <c r="P117" s="11"/>
+    </row>
+    <row r="118" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="P118" s="11">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="121" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="E121">
+        <f>SUM(E115:E119)</f>
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="125" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="P125">
+        <f>SUM(P105:P122)</f>
+        <v>516.99</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B974066F-70AB-4CE0-9413-18C0CA619219}">
   <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -25840,7 +27098,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A0FB8E-CB12-475E-9D50-00930E5BD370}">
   <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -26373,7 +27631,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94700D3-58F8-480F-AA59-9339E917FDF7}">
   <dimension ref="A1:R96"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -27197,16 +28455,16 @@
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="A73" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="B73">
+      <c r="B73" s="5">
         <f>450000+140000</f>
         <v>590000</v>
       </c>
-      <c r="C73">
-        <f>250000+60000+230000</f>
-        <v>540000</v>
+      <c r="C73" s="5">
+        <f>250000+60000+230000+50000</f>
+        <v>590000</v>
       </c>
       <c r="K73" t="s">
         <v>438</v>
@@ -27339,15 +28597,15 @@
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="A78" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="B78">
+      <c r="B78" s="5">
         <v>1500000</v>
       </c>
-      <c r="C78">
-        <f>500000+500000+300000</f>
-        <v>1300000</v>
+      <c r="C78" s="5">
+        <f>500000+500000+300000+300000</f>
+        <v>1600000</v>
       </c>
       <c r="E78">
         <f>45*6750</f>
@@ -27355,14 +28613,15 @@
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="A79" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="B79">
+      <c r="B79" s="5">
         <v>450000</v>
       </c>
-      <c r="C79">
-        <v>250000</v>
+      <c r="C79" s="5">
+        <f>250000+200000</f>
+        <v>450000</v>
       </c>
       <c r="D79">
         <f>30000+50000+150000</f>
@@ -27397,15 +28656,15 @@
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="A81" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="B81">
+      <c r="B81" s="5">
         <v>480000</v>
       </c>
-      <c r="C81">
-        <f>280000+100000</f>
-        <v>380000</v>
+      <c r="C81" s="5">
+        <f>280000+100000+110000</f>
+        <v>490000</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
@@ -27454,7 +28713,7 @@
       </c>
       <c r="C86">
         <f>SUM(C67:C84)+D79</f>
-        <v>9261750</v>
+        <v>9921750</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
@@ -27467,7 +28726,7 @@
       </c>
       <c r="C87">
         <f>C86/655</f>
-        <v>14140.076335877862</v>
+        <v>15147.709923664122</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
@@ -27516,8 +28775,8 @@
         <v>417</v>
       </c>
       <c r="B90">
-        <f>2000+4000+3000+800+1500</f>
-        <v>11300</v>
+        <f>2000+4000+3000+800+553+2150+4000</f>
+        <v>16503</v>
       </c>
       <c r="C90" t="s">
         <v>234</v>
@@ -27533,6 +28792,9 @@
       </c>
       <c r="G90" t="s">
         <v>459</v>
+      </c>
+      <c r="H90" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
@@ -27541,7 +28803,7 @@
       </c>
       <c r="B92">
         <f>B90-C87</f>
-        <v>-2840.0763358778622</v>
+        <v>1355.2900763358775</v>
       </c>
       <c r="L92">
         <f>L89*7000</f>
@@ -27570,7 +28832,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949D250C-39B2-4E80-98CE-CD0726DE900E}">
   <dimension ref="A3:G22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -27800,7 +29062,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A9C44F7-AFBE-4C6B-AF7F-6A7B39EB63FD}">
   <dimension ref="A2:P29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -28034,7 +29296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31B0527-2C58-45D2-85E0-B2079F911CE6}">
   <dimension ref="A2:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -28135,7 +29397,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60023A54-4F93-427E-93E6-1AE8B5C3C1AA}">
   <dimension ref="B3:H19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -28261,7 +29523,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3206B880-2680-4A84-A754-F93B2E76569E}">
   <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AG_AUTOMATION\Documents\projet-git\myDocs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\NewGit\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{884F41B5-0A57-4B18-8344-C7D5053DB1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7BED96-2F23-4E5E-AF61-1297E5A9E599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="24" activeTab="32" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="24" activeTab="30" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
   <sheets>
     <sheet name="Fevrier" sheetId="3" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1889" uniqueCount="467">
   <si>
     <t>Loyer</t>
   </si>
@@ -1460,6 +1460,18 @@
   </si>
   <si>
     <t>Mai</t>
+  </si>
+  <si>
+    <t>peintrure</t>
+  </si>
+  <si>
+    <t>ALUminium</t>
+  </si>
+  <si>
+    <t>retrait maroc</t>
+  </si>
+  <si>
+    <t>aout</t>
   </si>
 </sst>
 </file>
@@ -25790,9 +25802,11 @@
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
       <c r="B13" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="C13" s="11"/>
+        <v>465</v>
+      </c>
+      <c r="C13" s="11">
+        <v>200</v>
+      </c>
       <c r="D13" s="11"/>
       <c r="E13" s="9" t="s">
         <v>403</v>
@@ -26015,7 +26029,7 @@
       </c>
       <c r="C22" s="11">
         <f>SUM(C7:C19)</f>
-        <v>2386</v>
+        <v>2586</v>
       </c>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
@@ -26117,7 +26131,7 @@
       </c>
       <c r="D26" s="11">
         <f>C22+F22+I22</f>
-        <v>4447</v>
+        <v>4647</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
@@ -26189,7 +26203,7 @@
       </c>
       <c r="C29" s="11">
         <f>ABS(G4-D26)</f>
-        <v>4447</v>
+        <v>4647</v>
       </c>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
@@ -26304,7 +26318,7 @@
       </c>
       <c r="C34" s="11">
         <f>H4-D26</f>
-        <v>2153</v>
+        <v>1953</v>
       </c>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
@@ -26314,7 +26328,7 @@
       <c r="I34" s="11"/>
       <c r="J34" s="11">
         <f>C29+L29</f>
-        <v>4951</v>
+        <v>5151</v>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="11"/>
@@ -26800,6 +26814,9 @@
       <c r="M9">
         <v>500</v>
       </c>
+      <c r="O9">
+        <v>600</v>
+      </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G10" t="s">
@@ -26852,6 +26869,9 @@
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="L13" t="s">
         <v>221</v>
+      </c>
+      <c r="M13">
+        <v>500</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -26859,6 +26879,14 @@
         <f>SUM(J5:J12)</f>
         <v>5116</v>
       </c>
+      <c r="L14" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L15" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="I16" t="s">
@@ -26866,7 +26894,10 @@
       </c>
       <c r="J16">
         <f>J14-M22</f>
-        <v>2116</v>
+        <v>1616</v>
+      </c>
+      <c r="L16" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -26895,7 +26926,7 @@
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="M22">
         <f>SUM(M7:M20)</f>
-        <v>3000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -27633,7 +27664,7 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94700D3-58F8-480F-AA59-9339E917FDF7}">
-  <dimension ref="A1:R96"/>
+  <dimension ref="A1:R98"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
@@ -28624,8 +28655,8 @@
         <v>450000</v>
       </c>
       <c r="D79">
-        <f>30000+50000+150000</f>
-        <v>230000</v>
+        <f>30000+50000+150000+30000</f>
+        <v>260000</v>
       </c>
       <c r="E79" t="s">
         <v>461</v>
@@ -28693,137 +28724,156 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="B84" s="5">
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A85" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="B85" s="5">
+        <v>350000</v>
+      </c>
+      <c r="C85" s="5">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A86" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="B84" s="5">
+      <c r="B86" s="5">
         <v>200000</v>
       </c>
-      <c r="C84" s="5">
+      <c r="C86" s="5">
         <f>200000</f>
         <v>200000</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>6</v>
       </c>
-      <c r="B86">
-        <f>SUM(B67:B84)</f>
-        <v>10122750</v>
-      </c>
-      <c r="C86">
-        <f>SUM(C67:C84)+D79</f>
-        <v>9921750</v>
-      </c>
-    </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="B88">
+        <f>SUM(B67:B86)</f>
+        <v>11052750</v>
+      </c>
+      <c r="C88">
+        <f>SUM(C67:C86)+D79</f>
+        <v>10301750</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>421</v>
       </c>
-      <c r="B87">
-        <f>B86/655</f>
-        <v>15454.580152671755</v>
-      </c>
-      <c r="C87">
-        <f>C86/655</f>
-        <v>15147.709923664122</v>
-      </c>
-    </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="H88" t="s">
+      <c r="B89">
+        <f>B88/655</f>
+        <v>16874.427480916031</v>
+      </c>
+      <c r="C89">
+        <f>C88/655</f>
+        <v>15727.862595419847</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H90" t="s">
         <v>453</v>
       </c>
-      <c r="I88">
+      <c r="I90">
         <f>SUM(I74:I80)</f>
         <v>45.894999999999996</v>
       </c>
-      <c r="K88" t="s">
+      <c r="K90" t="s">
         <v>6</v>
       </c>
-      <c r="L88">
-        <f>SUM(L72:L87)</f>
+      <c r="L90">
+        <f>SUM(L72:L89)</f>
         <v>84.603999999999985</v>
       </c>
-      <c r="N88" t="s">
+      <c r="N90" t="s">
         <v>6</v>
       </c>
-      <c r="O88">
-        <f t="shared" ref="O88" si="0">SUM(O72:O87)</f>
+      <c r="O90">
+        <f t="shared" ref="O90" si="0">SUM(O72:O89)</f>
         <v>11.743600000000001</v>
       </c>
-      <c r="Q88" t="s">
+      <c r="Q90" t="s">
         <v>175</v>
       </c>
-      <c r="R88">
-        <f t="shared" ref="R88" si="1">SUM(R72:R87)</f>
+      <c r="R90">
+        <f t="shared" ref="R90" si="1">SUM(R72:R89)</f>
         <v>67.2</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="L89">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L91">
         <v>130</v>
       </c>
-      <c r="O89">
+      <c r="O91">
         <v>6</v>
       </c>
-      <c r="R89">
+      <c r="R91">
         <v>67</v>
-      </c>
-    </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>417</v>
-      </c>
-      <c r="B90">
-        <f>2000+4000+3000+800+553+2150+4000</f>
-        <v>16503</v>
-      </c>
-      <c r="C90" t="s">
-        <v>234</v>
-      </c>
-      <c r="D90" t="s">
-        <v>240</v>
-      </c>
-      <c r="E90" t="s">
-        <v>460</v>
-      </c>
-      <c r="F90" t="s">
-        <v>222</v>
-      </c>
-      <c r="G90" t="s">
-        <v>459</v>
-      </c>
-      <c r="H90" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>417</v>
+      </c>
+      <c r="B92">
+        <f>2000+4000+3000+800+553+1950+4000</f>
+        <v>16303</v>
+      </c>
+      <c r="C92" t="s">
+        <v>234</v>
+      </c>
+      <c r="D92" t="s">
+        <v>240</v>
+      </c>
+      <c r="E92" t="s">
+        <v>460</v>
+      </c>
+      <c r="F92" t="s">
+        <v>222</v>
+      </c>
+      <c r="G92" t="s">
+        <v>459</v>
+      </c>
+      <c r="H92" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>99</v>
       </c>
-      <c r="B92">
-        <f>B90-C87</f>
-        <v>1355.2900763358775</v>
-      </c>
-      <c r="L92">
-        <f>L89*7000</f>
+      <c r="B94">
+        <f>B92-C89</f>
+        <v>575.13740458015309</v>
+      </c>
+      <c r="L94">
+        <f>L91*7000</f>
         <v>910000</v>
       </c>
-      <c r="O92">
-        <f>O89*5000</f>
+      <c r="O94">
+        <f>O91*5000</f>
         <v>30000</v>
       </c>
-      <c r="R92">
-        <f>R89*5500</f>
+      <c r="R94">
+        <f>R91*5500</f>
         <v>368500</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K96" t="s">
+    <row r="98" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K98" t="s">
         <v>175</v>
       </c>
-      <c r="M96">
-        <f>I92+L92+O92+R92</f>
+      <c r="M98">
+        <f>I94+L94+O94+R94</f>
         <v>1308500</v>
       </c>
     </row>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\NewGit\myDocs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AG_AUTOMATION\Documents\projet-git\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7BED96-2F23-4E5E-AF61-1297E5A9E599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A3A898-C258-457A-9D01-4E5343B7CB51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="24" activeTab="30" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="24" activeTab="30" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
   <sheets>
     <sheet name="Fevrier" sheetId="3" r:id="rId1"/>
@@ -26920,7 +26920,7 @@
       </c>
       <c r="B20">
         <f>B6-F41</f>
-        <v>18000</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -27028,7 +27028,9 @@
         <v>221</v>
       </c>
       <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
+      <c r="C32" s="17">
+        <v>1000</v>
+      </c>
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
       <c r="F32" s="17"/>
@@ -27109,7 +27111,7 @@
       </c>
       <c r="C41" s="18">
         <f>SUM(C27:C39)</f>
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="D41" s="18">
         <f>SUM(D27:D39)</f>
@@ -27121,7 +27123,7 @@
       </c>
       <c r="F41" s="18">
         <f>SUM(B41:E41)</f>
-        <v>3500</v>
+        <v>4500</v>
       </c>
     </row>
   </sheetData>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AG_AUTOMATION\Documents\projet-git\myDocs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\NewGit\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A3A898-C258-457A-9D01-4E5343B7CB51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A97EC57-28BA-4EE8-9C57-3233076B1845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="24" activeTab="30" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="24" activeTab="32" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
   <sheets>
     <sheet name="Fevrier" sheetId="3" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1889" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="468">
   <si>
     <t>Loyer</t>
   </si>
@@ -1472,6 +1472,9 @@
   </si>
   <si>
     <t>aout</t>
+  </si>
+  <si>
+    <t>maroc</t>
   </si>
 </sst>
 </file>
@@ -25941,9 +25944,11 @@
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="10"/>
       <c r="B18" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="C18" s="11"/>
+        <v>467</v>
+      </c>
+      <c r="C18" s="11">
+        <v>200</v>
+      </c>
       <c r="D18" s="11"/>
       <c r="E18" s="9"/>
       <c r="F18" s="11"/>
@@ -26029,7 +26034,7 @@
       </c>
       <c r="C22" s="11">
         <f>SUM(C7:C19)</f>
-        <v>2586</v>
+        <v>2786</v>
       </c>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
@@ -26131,7 +26136,7 @@
       </c>
       <c r="D26" s="11">
         <f>C22+F22+I22</f>
-        <v>4647</v>
+        <v>4847</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
@@ -26203,7 +26208,7 @@
       </c>
       <c r="C29" s="11">
         <f>ABS(G4-D26)</f>
-        <v>4647</v>
+        <v>4847</v>
       </c>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
@@ -26318,7 +26323,7 @@
       </c>
       <c r="C34" s="11">
         <f>H4-D26</f>
-        <v>1953</v>
+        <v>1753</v>
       </c>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
@@ -26328,7 +26333,7 @@
       <c r="I34" s="11"/>
       <c r="J34" s="11">
         <f>C29+L29</f>
-        <v>5151</v>
+        <v>5351</v>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="11"/>
@@ -27666,7 +27671,7 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94700D3-58F8-480F-AA59-9339E917FDF7}">
-  <dimension ref="A1:R98"/>
+  <dimension ref="A1:R99"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
@@ -28657,8 +28662,8 @@
         <v>450000</v>
       </c>
       <c r="D79">
-        <f>30000+50000+150000+30000</f>
-        <v>260000</v>
+        <f>30000+50000+150000+30000+50000</f>
+        <v>310000</v>
       </c>
       <c r="E79" t="s">
         <v>461</v>
@@ -28731,151 +28736,165 @@
       <c r="B84" s="5">
         <v>580000</v>
       </c>
+      <c r="C84">
+        <v>380000</v>
+      </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>463</v>
+        <v>263</v>
       </c>
       <c r="B85" s="5">
-        <v>350000</v>
-      </c>
-      <c r="C85" s="5">
-        <v>350000</v>
+        <v>500000</v>
+      </c>
+      <c r="C85">
+        <v>500000</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="B86" s="5">
+        <v>350000</v>
+      </c>
+      <c r="C86" s="5">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A87" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="B86" s="5">
+      <c r="B87" s="5">
         <v>200000</v>
       </c>
-      <c r="C86" s="5">
+      <c r="C87" s="5">
         <f>200000</f>
         <v>200000</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>6</v>
-      </c>
-      <c r="B88">
-        <f>SUM(B67:B86)</f>
-        <v>11052750</v>
-      </c>
-      <c r="C88">
-        <f>SUM(C67:C86)+D79</f>
-        <v>10301750</v>
-      </c>
-    </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>6</v>
+      </c>
+      <c r="B89">
+        <f>SUM(B67:B87)</f>
+        <v>11552750</v>
+      </c>
+      <c r="C89">
+        <f>SUM(C67:C87)+D79</f>
+        <v>11231750</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>421</v>
       </c>
-      <c r="B89">
-        <f>B88/655</f>
-        <v>16874.427480916031</v>
-      </c>
-      <c r="C89">
-        <f>C88/655</f>
-        <v>15727.862595419847</v>
-      </c>
-    </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="H90" t="s">
+      <c r="B90">
+        <f>B89/655</f>
+        <v>17637.786259541987</v>
+      </c>
+      <c r="C90">
+        <f>C89/655</f>
+        <v>17147.709923664122</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H91" t="s">
         <v>453</v>
       </c>
-      <c r="I90">
+      <c r="I91">
         <f>SUM(I74:I80)</f>
         <v>45.894999999999996</v>
       </c>
-      <c r="K90" t="s">
+      <c r="K91" t="s">
         <v>6</v>
       </c>
-      <c r="L90">
-        <f>SUM(L72:L89)</f>
+      <c r="L91">
+        <f>SUM(L72:L90)</f>
         <v>84.603999999999985</v>
       </c>
-      <c r="N90" t="s">
+      <c r="N91" t="s">
         <v>6</v>
       </c>
-      <c r="O90">
-        <f t="shared" ref="O90" si="0">SUM(O72:O89)</f>
+      <c r="O91">
+        <f t="shared" ref="O91" si="0">SUM(O72:O90)</f>
         <v>11.743600000000001</v>
       </c>
-      <c r="Q90" t="s">
+      <c r="Q91" t="s">
         <v>175</v>
       </c>
-      <c r="R90">
-        <f t="shared" ref="R90" si="1">SUM(R72:R89)</f>
+      <c r="R91">
+        <f t="shared" ref="R91" si="1">SUM(R72:R90)</f>
         <v>67.2</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="L91">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L92">
         <v>130</v>
       </c>
-      <c r="O91">
+      <c r="O92">
         <v>6</v>
       </c>
-      <c r="R91">
+      <c r="R92">
         <v>67</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>417</v>
       </c>
-      <c r="B92">
-        <f>2000+4000+3000+800+553+1950+4000</f>
-        <v>16303</v>
-      </c>
-      <c r="C92" t="s">
+      <c r="B93">
+        <f>2000+4000+3000+800+553+1750+4000+1000</f>
+        <v>17103</v>
+      </c>
+      <c r="C93" t="s">
         <v>234</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D93" t="s">
         <v>240</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E93" t="s">
         <v>460</v>
       </c>
-      <c r="F92" t="s">
+      <c r="F93" t="s">
         <v>222</v>
       </c>
-      <c r="G92" t="s">
+      <c r="G93" t="s">
         <v>459</v>
       </c>
-      <c r="H92" t="s">
+      <c r="H93" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
         <v>99</v>
       </c>
-      <c r="B94">
-        <f>B92-C89</f>
-        <v>575.13740458015309</v>
-      </c>
-      <c r="L94">
-        <f>L91*7000</f>
+      <c r="B95">
+        <f>B93-C90</f>
+        <v>-44.709923664122471</v>
+      </c>
+      <c r="L95">
+        <f>L92*7000</f>
         <v>910000</v>
       </c>
-      <c r="O94">
-        <f>O91*5000</f>
+      <c r="O95">
+        <f>O92*5000</f>
         <v>30000</v>
       </c>
-      <c r="R94">
-        <f>R91*5500</f>
+      <c r="R95">
+        <f>R92*5500</f>
         <v>368500</v>
       </c>
     </row>
-    <row r="98" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K98" t="s">
+    <row r="99" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K99" t="s">
         <v>175</v>
       </c>
-      <c r="M98">
-        <f>I94+L94+O94+R94</f>
+      <c r="M99">
+        <f>I95+L95+O95+R95</f>
         <v>1308500</v>
       </c>
     </row>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\NewGit\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C7C1A8-F256-45BF-8BF5-A687AB777F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7EDE51-6605-46ED-AE3E-F6358CDE61E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="7" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="18" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
   <sheets>
     <sheet name="Sept23" sheetId="29" r:id="rId1"/>
@@ -31,11 +31,12 @@
     <sheet name="Mars25" sheetId="47" r:id="rId16"/>
     <sheet name="Avril25" sheetId="48" r:id="rId17"/>
     <sheet name="Mai25" sheetId="49" r:id="rId18"/>
-    <sheet name="Credit" sheetId="28" r:id="rId19"/>
-    <sheet name="Entreprise" sheetId="35" r:id="rId20"/>
-    <sheet name="Construction " sheetId="27" r:id="rId21"/>
-    <sheet name="Construction2" sheetId="39" r:id="rId22"/>
-    <sheet name="Terrain" sheetId="18" r:id="rId23"/>
+    <sheet name="Juin25" sheetId="50" r:id="rId19"/>
+    <sheet name="Credit" sheetId="28" r:id="rId20"/>
+    <sheet name="Entreprise" sheetId="35" r:id="rId21"/>
+    <sheet name="Construction " sheetId="27" r:id="rId22"/>
+    <sheet name="Construction2" sheetId="39" r:id="rId23"/>
+    <sheet name="Terrain" sheetId="18" r:id="rId24"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="301">
   <si>
     <t>Loyer</t>
   </si>
@@ -956,6 +957,9 @@
   </si>
   <si>
     <t>maroc</t>
+  </si>
+  <si>
+    <t>sanitaire</t>
   </si>
 </sst>
 </file>
@@ -13556,443 +13560,1248 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B974066F-70AB-4CE0-9413-18C0CA619219}">
-  <dimension ref="A1:O41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6639FC95-1DF9-4C8F-9F0D-8BF0D77A130D}">
+  <dimension ref="A1:T125"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.125" customWidth="1"/>
+    <col min="9" max="9" width="19.625" customWidth="1"/>
+    <col min="11" max="11" width="8.125" customWidth="1"/>
+    <col min="13" max="13" width="18.125" customWidth="1"/>
+    <col min="18" max="18" width="3.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>11500</v>
-      </c>
-      <c r="B2">
-        <v>10000</v>
-      </c>
-      <c r="G2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J3" s="5"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="5"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4">
+        <v>3145</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="O4" s="4">
+        <v>1480</v>
+      </c>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="5"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="5"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="8"/>
+      <c r="M6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N6" s="8"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="5"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1012</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="4">
+        <v>150</v>
+      </c>
+      <c r="O7" s="4"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="5"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N8" s="4">
+        <v>200</v>
+      </c>
+      <c r="O8" s="4"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="5"/>
+      <c r="T8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="4">
+        <v>200</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F9" s="4">
+        <v>96</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N9" s="4">
+        <v>200</v>
+      </c>
+      <c r="O9" s="4"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="5"/>
+      <c r="T9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C10" s="4">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F10" s="4">
+        <v>50</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="4">
+        <v>300</v>
+      </c>
+      <c r="O10" s="4"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="5"/>
+      <c r="T10">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" s="4">
+        <v>39</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4">
+        <v>157</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N11" s="4">
+        <v>100</v>
+      </c>
+      <c r="O11" s="4"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="5"/>
+      <c r="T11">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="B12" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="4">
+        <v>300</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="4">
+        <v>13</v>
+      </c>
+      <c r="O12" s="4"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="5"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+      <c r="B13" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F13" s="4">
+        <v>52</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N13" s="4">
+        <v>13</v>
+      </c>
+      <c r="O13" s="4"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="5"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="3"/>
+      <c r="B14" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="4">
+        <v>13</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="5"/>
+      <c r="T14">
+        <f>SUM(T8:T11)</f>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+      <c r="B15" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" s="4">
+        <v>100</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="5"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="3"/>
+      <c r="B16" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C16" s="4">
+        <v>247</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F16" s="4">
+        <v>131</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="5"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+      <c r="B17" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="5"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="3"/>
+      <c r="B18" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="5"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="5"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="3"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="5"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="3"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="5"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" s="3"/>
+      <c r="B22" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="4">
+        <f>SUM(C7:C19)</f>
+        <v>486</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4">
+        <f>SUM(F7:F20)+150</f>
+        <v>2061</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4">
+        <f>SUM(I7:I19)</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="5"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4">
+        <f>SUM(N7:N19)</f>
+        <v>976</v>
+      </c>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4">
+        <f>SUM(Q7:Q18)</f>
+        <v>0</v>
+      </c>
+      <c r="R22" s="4"/>
+      <c r="S22" s="5"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" s="3"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="5"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="3"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="5"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="5"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="4">
+        <f>C22+F22+I22</f>
+        <v>2547</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4">
+        <f>N22+Q22</f>
+        <v>976</v>
+      </c>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="5"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="5"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" s="3"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="4"/>
+      <c r="R28" s="4"/>
+      <c r="S28" s="5"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29" s="3"/>
+      <c r="B29" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="4">
+        <f>ABS(G4-D26)</f>
+        <v>2547</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="4">
+        <f>O4-P26</f>
+        <v>504</v>
+      </c>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="4"/>
+      <c r="R29" s="4"/>
+      <c r="S29" s="5"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" s="3"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="5"/>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="4"/>
+      <c r="S33" s="4"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="4">
+        <f>H4-D26</f>
+        <v>598</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4">
+        <f>C29+L29</f>
+        <v>3051</v>
+      </c>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="4"/>
+      <c r="R34" s="4"/>
+      <c r="S34" s="4"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4"/>
+      <c r="Q35" s="4"/>
+      <c r="R35" s="4"/>
+      <c r="S35" s="4"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="E36">
+        <f>5.2+13.8+10.96+13+13+21+6.99+47+62+12+68+40</f>
+        <v>312.95</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I39" t="s">
+        <v>208</v>
+      </c>
+      <c r="J39">
+        <v>39</v>
+      </c>
+      <c r="L39" t="s">
+        <v>214</v>
+      </c>
+      <c r="M39">
+        <f>SUM(J39:J58)</f>
+        <v>22002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E40" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F40">
+        <v>500</v>
+      </c>
+      <c r="I40" t="s">
+        <v>209</v>
+      </c>
+      <c r="J40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E41" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="F41">
+        <v>800</v>
+      </c>
+      <c r="I41" t="s">
+        <v>210</v>
+      </c>
+      <c r="J41">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E42" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="F42">
+        <v>200</v>
+      </c>
+      <c r="I42" t="s">
+        <v>211</v>
+      </c>
+      <c r="J42">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E43" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="F43">
+        <v>2000</v>
+      </c>
+      <c r="I43" t="s">
+        <v>212</v>
+      </c>
+      <c r="J43">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E44" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="F44">
+        <v>500</v>
+      </c>
+      <c r="I44" t="s">
+        <v>212</v>
+      </c>
+      <c r="J44">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E45" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="F45">
+        <v>100</v>
+      </c>
+      <c r="I45" t="s">
+        <v>213</v>
+      </c>
+      <c r="J45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E46" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="F46">
+        <v>67</v>
+      </c>
+      <c r="I46" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E47" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="F47">
+        <v>50</v>
+      </c>
+      <c r="I47" t="s">
+        <v>215</v>
+      </c>
+      <c r="J47">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E48" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="F48">
+        <v>70</v>
+      </c>
+      <c r="I48" t="s">
+        <v>216</v>
+      </c>
+      <c r="J48">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E49" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="F49">
+        <v>300</v>
+      </c>
+      <c r="I49" t="s">
+        <v>217</v>
+      </c>
+      <c r="J49">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E50" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="F50">
+        <v>100</v>
+      </c>
+      <c r="I50" t="s">
+        <v>24</v>
+      </c>
+      <c r="J50">
+        <v>20914</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I51" t="s">
+        <v>219</v>
+      </c>
+      <c r="J51">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J52">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F54">
+        <f>SUM(F40:F50)</f>
+        <v>4687</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B62" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="4">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="98" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B98">
         <v>3000</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G5" t="s">
-        <v>67</v>
-      </c>
-      <c r="H5">
+    <row r="99" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B99">
+        <v>2500</v>
+      </c>
+      <c r="J99">
         <v>3000</v>
       </c>
-      <c r="J5">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <f>SUM(A2:G2)</f>
-        <v>21500</v>
-      </c>
-      <c r="G6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6">
-        <v>5000</v>
-      </c>
-      <c r="J6">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H7">
-        <v>4000</v>
-      </c>
-      <c r="J7">
-        <v>163</v>
-      </c>
-      <c r="L7" t="s">
-        <v>225</v>
-      </c>
-      <c r="M7">
-        <v>500</v>
-      </c>
-      <c r="O7">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G8" t="s">
-        <v>71</v>
-      </c>
-      <c r="H8">
-        <v>4000</v>
-      </c>
-      <c r="J8">
-        <v>400</v>
-      </c>
-      <c r="L8" t="s">
-        <v>81</v>
-      </c>
-      <c r="M8">
-        <v>500</v>
-      </c>
-      <c r="O8">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H9">
-        <v>3000</v>
-      </c>
-      <c r="J9">
-        <v>300</v>
-      </c>
-      <c r="L9" t="s">
-        <v>87</v>
-      </c>
-      <c r="M9">
-        <v>500</v>
-      </c>
-      <c r="O9">
+    </row>
+    <row r="100" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B100">
+        <v>2500</v>
+      </c>
+      <c r="J100">
         <v>600</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G10" t="s">
-        <v>81</v>
-      </c>
-      <c r="H10">
-        <v>3000</v>
-      </c>
-      <c r="I10" t="s">
+    <row r="101" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B101">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="102" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B102">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="106" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B106">
+        <f>SUM(B98:B102)</f>
+        <v>9500</v>
+      </c>
+      <c r="D106">
+        <f>B106-7000</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="107" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P107">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="108" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P108" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P109" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P110" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P111" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="112" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P112" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="113" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="P113" s="4">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="114" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="P114" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="115" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="E115">
+        <v>1400</v>
+      </c>
+      <c r="P115" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="116" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="E116">
+        <v>1300</v>
+      </c>
+      <c r="P116" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="117" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="E117">
+        <v>950</v>
+      </c>
+      <c r="P117" s="4"/>
+    </row>
+    <row r="118" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="P118" s="4">
         <v>70</v>
       </c>
-      <c r="J10">
-        <v>1300</v>
-      </c>
-      <c r="L10" t="s">
-        <v>88</v>
-      </c>
-      <c r="M10">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G11" t="s">
-        <v>87</v>
-      </c>
-      <c r="H11">
-        <v>3000</v>
-      </c>
-      <c r="J11">
-        <v>1000</v>
-      </c>
-      <c r="L11" t="s">
-        <v>69</v>
-      </c>
-      <c r="M11">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J12">
-        <v>300</v>
-      </c>
-      <c r="L12" t="s">
-        <v>259</v>
-      </c>
-      <c r="M12">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L13" t="s">
-        <v>68</v>
-      </c>
-      <c r="M13">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J14">
-        <f>SUM(J5:J12)</f>
-        <v>5116</v>
-      </c>
-      <c r="L14" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="I16" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16">
-        <f>J14-M22</f>
-        <v>1616</v>
-      </c>
-      <c r="L16" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="O17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F19" t="s">
-        <v>4</v>
-      </c>
-      <c r="H19">
-        <f>SUM(H3:H17)</f>
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20">
-        <f>B6-F41</f>
-        <v>17000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M22">
-        <f>SUM(M7:M20)</f>
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="F26" s="9"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B27" s="9">
-        <v>500</v>
-      </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9">
-        <v>1000</v>
-      </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="B29" s="9">
-        <v>500</v>
-      </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9">
-        <v>1000</v>
-      </c>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B31" s="9">
-        <v>500</v>
-      </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9">
-        <v>1000</v>
-      </c>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B41" s="10">
-        <f>SUM(B27:B39)</f>
-        <v>1500</v>
-      </c>
-      <c r="C41" s="10">
-        <f>SUM(C27:C39)</f>
-        <v>3000</v>
-      </c>
-      <c r="D41" s="10">
-        <f>SUM(D27:D39)</f>
-        <v>0</v>
-      </c>
-      <c r="E41" s="10">
-        <f>SUM(E27:E39)</f>
-        <v>0</v>
-      </c>
-      <c r="F41" s="10">
-        <f>SUM(B41:E41)</f>
-        <v>4500</v>
+    </row>
+    <row r="121" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="E121">
+        <f>SUM(E115:E119)</f>
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="125" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="P125">
+        <f>SUM(P105:P122)</f>
+        <v>516.99</v>
       </c>
     </row>
   </sheetData>
@@ -15014,6 +15823,451 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B974066F-70AB-4CE0-9413-18C0CA619219}">
+  <dimension ref="A1:O41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>11500</v>
+      </c>
+      <c r="B2">
+        <v>10000</v>
+      </c>
+      <c r="G2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5">
+        <v>3000</v>
+      </c>
+      <c r="J5">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <f>SUM(A2:G2)</f>
+        <v>21500</v>
+      </c>
+      <c r="G6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H6">
+        <v>5000</v>
+      </c>
+      <c r="J6">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H7">
+        <v>4000</v>
+      </c>
+      <c r="J7">
+        <v>163</v>
+      </c>
+      <c r="L7" t="s">
+        <v>225</v>
+      </c>
+      <c r="M7">
+        <v>500</v>
+      </c>
+      <c r="O7">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8">
+        <v>4000</v>
+      </c>
+      <c r="J8">
+        <v>400</v>
+      </c>
+      <c r="L8" t="s">
+        <v>81</v>
+      </c>
+      <c r="M8">
+        <v>500</v>
+      </c>
+      <c r="O8">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9">
+        <v>3000</v>
+      </c>
+      <c r="J9">
+        <v>300</v>
+      </c>
+      <c r="L9" t="s">
+        <v>87</v>
+      </c>
+      <c r="M9">
+        <v>500</v>
+      </c>
+      <c r="O9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H10">
+        <v>3000</v>
+      </c>
+      <c r="I10" t="s">
+        <v>70</v>
+      </c>
+      <c r="J10">
+        <v>1300</v>
+      </c>
+      <c r="L10" t="s">
+        <v>88</v>
+      </c>
+      <c r="M10">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11">
+        <v>3000</v>
+      </c>
+      <c r="J11">
+        <v>1000</v>
+      </c>
+      <c r="L11" t="s">
+        <v>69</v>
+      </c>
+      <c r="M11">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J12">
+        <v>300</v>
+      </c>
+      <c r="L12" t="s">
+        <v>259</v>
+      </c>
+      <c r="M12">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L13" t="s">
+        <v>68</v>
+      </c>
+      <c r="M13">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J14">
+        <f>SUM(J5:J12)</f>
+        <v>5116</v>
+      </c>
+      <c r="L14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16">
+        <f>J14-M22</f>
+        <v>1616</v>
+      </c>
+      <c r="L16" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F19" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19">
+        <f>SUM(H3:H17)</f>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20">
+        <f>B6-F41</f>
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M22">
+        <f>SUM(M7:M20)</f>
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="10"/>
+      <c r="B26" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F26" s="9"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="9">
+        <v>500</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9">
+        <v>1000</v>
+      </c>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" s="9">
+        <v>500</v>
+      </c>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9">
+        <v>1000</v>
+      </c>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B31" s="9">
+        <v>500</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9">
+        <v>1000</v>
+      </c>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="9"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="9"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="9"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="9"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="10">
+        <f>SUM(B27:B39)</f>
+        <v>1500</v>
+      </c>
+      <c r="C41" s="10">
+        <f>SUM(C27:C39)</f>
+        <v>3000</v>
+      </c>
+      <c r="D41" s="10">
+        <f>SUM(D27:D39)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="10">
+        <f>SUM(E27:E39)</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="10">
+        <f>SUM(B41:E41)</f>
+        <v>4500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A0FB8E-CB12-475E-9D50-00930E5BD370}">
   <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -15546,9 +16800,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94700D3-58F8-480F-AA59-9339E917FDF7}">
-  <dimension ref="A1:R99"/>
+  <dimension ref="A1:R100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
@@ -16613,7 +17867,7 @@
       <c r="B84" s="1">
         <v>580000</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="1">
         <v>580000</v>
       </c>
     </row>
@@ -16624,154 +17878,165 @@
       <c r="B85" s="1">
         <v>500000</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="1">
         <v>500000</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B86" s="1">
-        <v>350000</v>
+        <v>250000</v>
       </c>
       <c r="C86" s="1">
-        <v>350000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B87" s="1">
+        <v>350000</v>
+      </c>
+      <c r="C87" s="1">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B87" s="1">
+      <c r="B88" s="1">
         <v>200000</v>
       </c>
-      <c r="C87" s="1">
+      <c r="C88" s="1">
         <f>200000</f>
         <v>200000</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>4</v>
-      </c>
-      <c r="B89">
-        <f>SUM(B67:B87)</f>
-        <v>11552750</v>
-      </c>
-      <c r="C89">
-        <f>SUM(C67:C87)+D79</f>
-        <v>11431750</v>
-      </c>
-    </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>4</v>
+      </c>
+      <c r="B90">
+        <f>SUM(B67:B88)</f>
+        <v>11802750</v>
+      </c>
+      <c r="C90">
+        <f>SUM(C67:C88)+D79</f>
+        <v>11681750</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
         <v>253</v>
       </c>
-      <c r="B90">
-        <f>B89/655</f>
-        <v>17637.786259541987</v>
-      </c>
-      <c r="C90">
-        <f>C89/655</f>
-        <v>17453.053435114503</v>
-      </c>
-    </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="H91" t="s">
+      <c r="B91">
+        <f>B90/655</f>
+        <v>18019.465648854963</v>
+      </c>
+      <c r="C91">
+        <f>C90/655</f>
+        <v>17834.732824427479</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H92" t="s">
         <v>285</v>
       </c>
-      <c r="I91">
+      <c r="I92">
         <f>SUM(I74:I80)</f>
         <v>45.894999999999996</v>
       </c>
-      <c r="K91" t="s">
+      <c r="K92" t="s">
         <v>4</v>
       </c>
-      <c r="L91">
-        <f>SUM(L72:L90)</f>
+      <c r="L92">
+        <f>SUM(L72:L91)</f>
         <v>84.603999999999985</v>
       </c>
-      <c r="N91" t="s">
+      <c r="N92" t="s">
         <v>4</v>
       </c>
-      <c r="O91">
-        <f t="shared" ref="O91" si="0">SUM(O72:O90)</f>
+      <c r="O92">
+        <f t="shared" ref="O92" si="0">SUM(O72:O91)</f>
         <v>11.743600000000001</v>
       </c>
-      <c r="Q91" t="s">
+      <c r="Q92" t="s">
         <v>35</v>
       </c>
-      <c r="R91">
-        <f t="shared" ref="R91" si="1">SUM(R72:R90)</f>
+      <c r="R92">
+        <f t="shared" ref="R92" si="1">SUM(R72:R91)</f>
         <v>67.2</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="L92">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L93">
         <v>130</v>
       </c>
-      <c r="O92">
+      <c r="O93">
         <v>6</v>
       </c>
-      <c r="R92">
+      <c r="R93">
         <v>67</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>249</v>
       </c>
-      <c r="B93">
+      <c r="B94">
         <f>2000+4000+3000+800+553+1950+4000+1000</f>
         <v>17303</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C94" t="s">
         <v>81</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D94" t="s">
         <v>87</v>
       </c>
-      <c r="E93" t="s">
+      <c r="E94" t="s">
         <v>292</v>
       </c>
-      <c r="F93" t="s">
+      <c r="F94" t="s">
         <v>69</v>
       </c>
-      <c r="G93" t="s">
+      <c r="G94" t="s">
         <v>291</v>
       </c>
-      <c r="H93" t="s">
+      <c r="H94" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>21</v>
       </c>
-      <c r="B95">
-        <f>B93-C90</f>
-        <v>-150.05343511450337</v>
-      </c>
-      <c r="L95">
-        <f>L92*7000</f>
+      <c r="B96">
+        <f>B94-C91</f>
+        <v>-531.7328244274795</v>
+      </c>
+      <c r="L96">
+        <f>L93*7000</f>
         <v>910000</v>
       </c>
-      <c r="O95">
-        <f>O92*5000</f>
+      <c r="O96">
+        <f>O93*5000</f>
         <v>30000</v>
       </c>
-      <c r="R95">
-        <f>R92*5500</f>
+      <c r="R96">
+        <f>R93*5500</f>
         <v>368500</v>
       </c>
     </row>
-    <row r="99" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K99" t="s">
+    <row r="100" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K100" t="s">
         <v>35</v>
       </c>
-      <c r="M99">
-        <f>I95+L95+O95+R95</f>
+      <c r="M100">
+        <f>I96+L96+O96+R96</f>
         <v>1308500</v>
       </c>
     </row>
@@ -16780,7 +18045,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949D250C-39B2-4E80-98CE-CD0726DE900E}">
   <dimension ref="A3:G22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -17010,7 +18275,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A9C44F7-AFBE-4C6B-AF7F-6A7B39EB63FD}">
   <dimension ref="A2:P29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\NewGit\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7EDE51-6605-46ED-AE3E-F6358CDE61E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89381B8A-ABA4-42E2-9FE3-A3EA7463DCE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="18" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="19" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
   <sheets>
     <sheet name="Sept23" sheetId="29" r:id="rId1"/>
@@ -38,7 +38,7 @@
     <sheet name="Construction2" sheetId="39" r:id="rId23"/>
     <sheet name="Terrain" sheetId="18" r:id="rId24"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="303">
   <si>
     <t>Loyer</t>
   </si>
@@ -960,6 +960,12 @@
   </si>
   <si>
     <t>sanitaire</t>
+  </si>
+  <si>
+    <t>jardin</t>
+  </si>
+  <si>
+    <t>Samba</t>
   </si>
 </sst>
 </file>
@@ -1404,6 +1410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{523BEFCC-E2C1-4A63-A878-2F0184845ABE}">
+  <sheetPr codeName="Feuil1"/>
   <dimension ref="A1:T123"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2405,6 +2412,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204AD329-0DC1-498B-A790-1EB77A8023CA}">
+  <sheetPr codeName="Feuil10"/>
   <dimension ref="A1:T124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3630,6 +3638,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{765F2F89-A56A-4328-AFC1-09E73433F3F3}">
+  <sheetPr codeName="Feuil11"/>
   <dimension ref="A1:T124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4845,6 +4854,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC4EF4F2-05C7-496E-95E0-029BFF75893E}">
+  <sheetPr codeName="Feuil12"/>
   <dimension ref="A1:T124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6070,6 +6080,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8D0046-6E8B-4E7A-BFB8-85F96EC96DBD}">
+  <sheetPr codeName="Feuil13"/>
   <dimension ref="A1:T124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7301,6 +7312,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7487C8C7-3406-4E54-ADE1-2B167EC852B1}">
+  <sheetPr codeName="Feuil14"/>
   <dimension ref="A1:T124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8530,6 +8542,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC8A3483-B416-4405-B16E-41B90F2A2DFA}">
+  <sheetPr codeName="Feuil15"/>
   <dimension ref="A1:T125"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9795,6 +9808,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{203118BA-A9DA-4209-85B1-21AB2F24CB40}">
+  <sheetPr codeName="Feuil16"/>
   <dimension ref="A1:T125"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11050,6 +11064,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77D1A72C-BABD-429C-BCAE-34A776D6F4E5}">
+  <sheetPr codeName="Feuil17"/>
   <dimension ref="A1:T125"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12307,6 +12322,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBC3F25E-31C5-496E-8089-BC63A88237EF}">
+  <sheetPr codeName="Feuil18"/>
   <dimension ref="A1:T125"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13561,6 +13577,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6639FC95-1DF9-4C8F-9F0D-8BF0D77A130D}">
+  <sheetPr codeName="Feuil19"/>
   <dimension ref="A1:T125"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -14811,6 +14828,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A004D6B5-EDB4-4F00-8178-BEA92D2455E4}">
+  <sheetPr codeName="Feuil2"/>
   <dimension ref="A1:T123"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -15824,6 +15842,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B974066F-70AB-4CE0-9413-18C0CA619219}">
+  <sheetPr codeName="Feuil20"/>
   <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -16056,7 +16075,7 @@
       </c>
       <c r="B20">
         <f>B6-F41</f>
-        <v>17000</v>
+        <v>16600</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -16163,7 +16182,9 @@
       <c r="A32" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="9"/>
+      <c r="B32" s="9">
+        <v>400</v>
+      </c>
       <c r="C32" s="9">
         <v>1000</v>
       </c>
@@ -16243,7 +16264,7 @@
       </c>
       <c r="B41" s="10">
         <f>SUM(B27:B39)</f>
-        <v>1500</v>
+        <v>1900</v>
       </c>
       <c r="C41" s="10">
         <f>SUM(C27:C39)</f>
@@ -16259,7 +16280,7 @@
       </c>
       <c r="F41" s="10">
         <f>SUM(B41:E41)</f>
-        <v>4500</v>
+        <v>4900</v>
       </c>
     </row>
   </sheetData>
@@ -16269,6 +16290,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A0FB8E-CB12-475E-9D50-00930E5BD370}">
+  <sheetPr codeName="Feuil21"/>
   <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -16802,7 +16824,8 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94700D3-58F8-480F-AA59-9339E917FDF7}">
-  <dimension ref="A1:R100"/>
+  <sheetPr codeName="Feuil22"/>
+  <dimension ref="A1:R102"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
@@ -17884,159 +17907,181 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B86" s="1">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="C86" s="1">
-        <v>250000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B87" s="1">
-        <v>350000</v>
+        <v>250000</v>
       </c>
       <c r="C87" s="1">
-        <v>350000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B88" s="1">
+        <v>100000</v>
+      </c>
+      <c r="C88" s="1">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B89" s="1">
+        <v>350000</v>
+      </c>
+      <c r="C89" s="1">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B88" s="1">
+      <c r="B90" s="1">
         <v>200000</v>
       </c>
-      <c r="C88" s="1">
+      <c r="C90" s="1">
         <f>200000</f>
         <v>200000</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>4</v>
       </c>
-      <c r="B90">
-        <f>SUM(B67:B88)</f>
-        <v>11802750</v>
-      </c>
-      <c r="C90">
-        <f>SUM(C67:C88)+D79</f>
-        <v>11681750</v>
-      </c>
-    </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="B92">
+        <f>SUM(B67:B90)</f>
+        <v>12102750</v>
+      </c>
+      <c r="C92">
+        <f>SUM(C67:C90)+D79</f>
+        <v>11981750</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>253</v>
       </c>
-      <c r="B91">
-        <f>B90/655</f>
-        <v>18019.465648854963</v>
-      </c>
-      <c r="C91">
-        <f>C90/655</f>
-        <v>17834.732824427479</v>
-      </c>
-    </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="H92" t="s">
+      <c r="B93">
+        <f>B92/655</f>
+        <v>18477.480916030534</v>
+      </c>
+      <c r="C93">
+        <f>C92/655</f>
+        <v>18292.748091603054</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H94" t="s">
         <v>285</v>
       </c>
-      <c r="I92">
+      <c r="I94">
         <f>SUM(I74:I80)</f>
         <v>45.894999999999996</v>
       </c>
-      <c r="K92" t="s">
+      <c r="K94" t="s">
         <v>4</v>
       </c>
-      <c r="L92">
-        <f>SUM(L72:L91)</f>
+      <c r="L94">
+        <f>SUM(L72:L93)</f>
         <v>84.603999999999985</v>
       </c>
-      <c r="N92" t="s">
+      <c r="N94" t="s">
         <v>4</v>
       </c>
-      <c r="O92">
-        <f t="shared" ref="O92" si="0">SUM(O72:O91)</f>
+      <c r="O94">
+        <f t="shared" ref="O94" si="0">SUM(O72:O93)</f>
         <v>11.743600000000001</v>
       </c>
-      <c r="Q92" t="s">
+      <c r="Q94" t="s">
         <v>35</v>
       </c>
-      <c r="R92">
-        <f t="shared" ref="R92" si="1">SUM(R72:R91)</f>
+      <c r="R94">
+        <f t="shared" ref="R94" si="1">SUM(R72:R93)</f>
         <v>67.2</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="L93">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L95">
         <v>130</v>
       </c>
-      <c r="O93">
+      <c r="O95">
         <v>6</v>
       </c>
-      <c r="R93">
+      <c r="R95">
         <v>67</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>249</v>
       </c>
-      <c r="B94">
+      <c r="B96">
         <f>2000+4000+3000+800+553+1950+4000+1000</f>
         <v>17303</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C96" t="s">
         <v>81</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D96" t="s">
         <v>87</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E96" t="s">
         <v>292</v>
       </c>
-      <c r="F94" t="s">
+      <c r="F96" t="s">
         <v>69</v>
       </c>
-      <c r="G94" t="s">
+      <c r="G96" t="s">
         <v>291</v>
       </c>
-      <c r="H94" t="s">
+      <c r="H96" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>21</v>
       </c>
-      <c r="B96">
-        <f>B94-C91</f>
-        <v>-531.7328244274795</v>
-      </c>
-      <c r="L96">
-        <f>L93*7000</f>
+      <c r="B98">
+        <f>B96-C93</f>
+        <v>-989.74809160305449</v>
+      </c>
+      <c r="L98">
+        <f>L95*7000</f>
         <v>910000</v>
       </c>
-      <c r="O96">
-        <f>O93*5000</f>
+      <c r="O98">
+        <f>O95*5000</f>
         <v>30000</v>
       </c>
-      <c r="R96">
-        <f>R93*5500</f>
+      <c r="R98">
+        <f>R95*5500</f>
         <v>368500</v>
       </c>
     </row>
-    <row r="100" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K100" t="s">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="K102" t="s">
         <v>35</v>
       </c>
-      <c r="M100">
-        <f>I96+L96+O96+R96</f>
+      <c r="M102">
+        <f>I98+L98+O98+R98</f>
         <v>1308500</v>
       </c>
     </row>
@@ -18047,6 +18092,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949D250C-39B2-4E80-98CE-CD0726DE900E}">
+  <sheetPr codeName="Feuil23"/>
   <dimension ref="A3:G22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -18277,6 +18323,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A9C44F7-AFBE-4C6B-AF7F-6A7B39EB63FD}">
+  <sheetPr codeName="Feuil24"/>
   <dimension ref="A2:P29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -18511,6 +18558,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80858377-DA6D-4793-BFDF-E57BFC7E784F}">
+  <sheetPr codeName="Feuil3"/>
   <dimension ref="A1:T123"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -19541,6 +19589,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8954BA60-EBA4-4FC7-A38C-A5D075E1C354}">
+  <sheetPr codeName="Feuil4"/>
   <dimension ref="A1:T123"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -20557,6 +20606,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3955CB3-126C-4293-8B88-AAD682FCCD60}">
+  <sheetPr codeName="Feuil5"/>
   <dimension ref="A1:T123"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -21567,6 +21617,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94A96170-A85A-4424-A731-7674D842F02C}">
+  <sheetPr codeName="Feuil6"/>
   <dimension ref="A1:T124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -22602,6 +22653,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B758DE3-F5ED-4261-AAFF-974C4232EE82}">
+  <sheetPr codeName="Feuil7"/>
   <dimension ref="A1:T124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -23636,6 +23688,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC67AF8C-947E-4356-B4C4-480E7AC7BE5D}">
+  <sheetPr codeName="Feuil8"/>
   <dimension ref="A1:T124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -24678,6 +24731,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C08CF61-A2D9-42E5-875A-94EAF9A3757F}">
+  <sheetPr codeName="Feuil9"/>
   <dimension ref="A1:T124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\NewGit\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89381B8A-ABA4-42E2-9FE3-A3EA7463DCE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A92632-7B88-4828-98CD-E9BFC35617A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="19" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="12" activeTab="22" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
   <sheets>
     <sheet name="Sept23" sheetId="29" r:id="rId1"/>
@@ -31,12 +31,13 @@
     <sheet name="Mars25" sheetId="47" r:id="rId16"/>
     <sheet name="Avril25" sheetId="48" r:id="rId17"/>
     <sheet name="Mai25" sheetId="49" r:id="rId18"/>
-    <sheet name="Juin25" sheetId="50" r:id="rId19"/>
-    <sheet name="Credit" sheetId="28" r:id="rId20"/>
-    <sheet name="Entreprise" sheetId="35" r:id="rId21"/>
-    <sheet name="Construction " sheetId="27" r:id="rId22"/>
-    <sheet name="Construction2" sheetId="39" r:id="rId23"/>
-    <sheet name="Terrain" sheetId="18" r:id="rId24"/>
+    <sheet name="JUIN125" sheetId="51" r:id="rId19"/>
+    <sheet name="Juin25" sheetId="50" r:id="rId20"/>
+    <sheet name="Credit" sheetId="28" r:id="rId21"/>
+    <sheet name="Entreprise" sheetId="35" r:id="rId22"/>
+    <sheet name="Construction " sheetId="27" r:id="rId23"/>
+    <sheet name="Construction2" sheetId="39" r:id="rId24"/>
+    <sheet name="Terrain" sheetId="18" r:id="rId25"/>
   </sheets>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="306">
   <si>
     <t>Loyer</t>
   </si>
@@ -966,6 +967,15 @@
   </si>
   <si>
     <t>Samba</t>
+  </si>
+  <si>
+    <t>Moton mere</t>
+  </si>
+  <si>
+    <t>tons Gora</t>
+  </si>
+  <si>
+    <t>lissage exter</t>
   </si>
 </sst>
 </file>
@@ -13576,8 +13586,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6639FC95-1DF9-4C8F-9F0D-8BF0D77A130D}">
-  <sheetPr codeName="Feuil19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72F08D44-5740-4FBB-BE22-89E626F4C9EB}">
   <dimension ref="A1:T125"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13669,7 +13678,8 @@
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4">
-        <v>3145</v>
+        <f>3000+2500</f>
+        <v>5500</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="5"/>
@@ -13812,7 +13822,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="4">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="2" t="s">
@@ -13845,10 +13855,10 @@
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>221</v>
+        <v>303</v>
       </c>
       <c r="C10" s="4">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="2" t="s">
@@ -13917,7 +13927,9 @@
       <c r="B12" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C12" s="4"/>
+      <c r="C12" s="4">
+        <v>1000</v>
+      </c>
       <c r="D12" s="4"/>
       <c r="E12" s="2" t="s">
         <v>9</v>
@@ -13973,9 +13985,11 @@
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="C14" s="4"/>
+        <v>304</v>
+      </c>
+      <c r="C14" s="4">
+        <v>224</v>
+      </c>
       <c r="D14" s="4"/>
       <c r="E14" s="2" t="s">
         <v>14</v>
@@ -14001,9 +14015,7 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
-      <c r="B15" s="2" t="s">
-        <v>258</v>
-      </c>
+      <c r="B15" s="2"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="2" t="s">
@@ -14057,9 +14069,7 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
-      <c r="B17" s="2" t="s">
-        <v>150</v>
-      </c>
+      <c r="B17" s="2"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="2"/>
@@ -14080,9 +14090,7 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
-      <c r="B18" s="2" t="s">
-        <v>299</v>
-      </c>
+      <c r="B18" s="2"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="2"/>
@@ -14169,7 +14177,7 @@
       </c>
       <c r="C22" s="4">
         <f>SUM(C7:C19)</f>
-        <v>486</v>
+        <v>2060</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -14271,7 +14279,7 @@
       </c>
       <c r="D26" s="4">
         <f>C22+F22+I22</f>
-        <v>2547</v>
+        <v>4121</v>
       </c>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
@@ -14343,7 +14351,7 @@
       </c>
       <c r="C29" s="4">
         <f>ABS(G4-D26)</f>
-        <v>2547</v>
+        <v>4121</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -14458,7 +14466,7 @@
       </c>
       <c r="C34" s="4">
         <f>H4-D26</f>
-        <v>598</v>
+        <v>1379</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -14468,7 +14476,7 @@
       <c r="I34" s="4"/>
       <c r="J34" s="4">
         <f>C29+L29</f>
-        <v>3051</v>
+        <v>4625</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -15841,6 +15849,1257 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6639FC95-1DF9-4C8F-9F0D-8BF0D77A130D}">
+  <sheetPr codeName="Feuil19"/>
+  <dimension ref="A1:T125"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.125" customWidth="1"/>
+    <col min="9" max="9" width="19.625" customWidth="1"/>
+    <col min="11" max="11" width="8.125" customWidth="1"/>
+    <col min="13" max="13" width="18.125" customWidth="1"/>
+    <col min="18" max="18" width="3.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J3" s="5"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="5"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4">
+        <v>3145</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="O4" s="4">
+        <v>1480</v>
+      </c>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="5"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="5"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="8"/>
+      <c r="M6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N6" s="8"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="5"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1012</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="4">
+        <v>150</v>
+      </c>
+      <c r="O7" s="4"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="5"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N8" s="4">
+        <v>200</v>
+      </c>
+      <c r="O8" s="4"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="5"/>
+      <c r="T8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="4">
+        <v>200</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F9" s="4">
+        <v>96</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N9" s="4">
+        <v>200</v>
+      </c>
+      <c r="O9" s="4"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="5"/>
+      <c r="T9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C10" s="4">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F10" s="4">
+        <v>50</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="4">
+        <v>300</v>
+      </c>
+      <c r="O10" s="4"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="5"/>
+      <c r="T10">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" s="4">
+        <v>39</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4">
+        <v>157</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N11" s="4">
+        <v>100</v>
+      </c>
+      <c r="O11" s="4"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="5"/>
+      <c r="T11">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="B12" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="4">
+        <v>300</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="4">
+        <v>13</v>
+      </c>
+      <c r="O12" s="4"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="5"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+      <c r="B13" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F13" s="4">
+        <v>52</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N13" s="4">
+        <v>13</v>
+      </c>
+      <c r="O13" s="4"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="5"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="3"/>
+      <c r="B14" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="4">
+        <v>13</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="5"/>
+      <c r="T14">
+        <f>SUM(T8:T11)</f>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+      <c r="B15" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" s="4">
+        <v>100</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="5"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="3"/>
+      <c r="B16" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C16" s="4">
+        <v>247</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F16" s="4">
+        <v>131</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="5"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+      <c r="B17" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="5"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="3"/>
+      <c r="B18" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="5"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="5"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="3"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="5"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="3"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="5"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" s="3"/>
+      <c r="B22" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="4">
+        <f>SUM(C7:C19)</f>
+        <v>486</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4">
+        <f>SUM(F7:F20)+150</f>
+        <v>2061</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4">
+        <f>SUM(I7:I19)</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="5"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4">
+        <f>SUM(N7:N19)</f>
+        <v>976</v>
+      </c>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4">
+        <f>SUM(Q7:Q18)</f>
+        <v>0</v>
+      </c>
+      <c r="R22" s="4"/>
+      <c r="S22" s="5"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" s="3"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="5"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="3"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="5"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="5"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="4">
+        <f>C22+F22+I22</f>
+        <v>2547</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4">
+        <f>N22+Q22</f>
+        <v>976</v>
+      </c>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="5"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="5"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" s="3"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="4"/>
+      <c r="R28" s="4"/>
+      <c r="S28" s="5"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29" s="3"/>
+      <c r="B29" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="4">
+        <f>ABS(G4-D26)</f>
+        <v>2547</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="4">
+        <f>O4-P26</f>
+        <v>504</v>
+      </c>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="4"/>
+      <c r="R29" s="4"/>
+      <c r="S29" s="5"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" s="3"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="5"/>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="4"/>
+      <c r="S33" s="4"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="4">
+        <f>H4-D26</f>
+        <v>598</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4">
+        <f>C29+L29</f>
+        <v>3051</v>
+      </c>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="4"/>
+      <c r="R34" s="4"/>
+      <c r="S34" s="4"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4"/>
+      <c r="Q35" s="4"/>
+      <c r="R35" s="4"/>
+      <c r="S35" s="4"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="E36">
+        <f>5.2+13.8+10.96+13+13+21+6.99+47+62+12+68+40</f>
+        <v>312.95</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I39" t="s">
+        <v>208</v>
+      </c>
+      <c r="J39">
+        <v>39</v>
+      </c>
+      <c r="L39" t="s">
+        <v>214</v>
+      </c>
+      <c r="M39">
+        <f>SUM(J39:J58)</f>
+        <v>22002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E40" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F40">
+        <v>500</v>
+      </c>
+      <c r="I40" t="s">
+        <v>209</v>
+      </c>
+      <c r="J40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E41" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="F41">
+        <v>800</v>
+      </c>
+      <c r="I41" t="s">
+        <v>210</v>
+      </c>
+      <c r="J41">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E42" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="F42">
+        <v>200</v>
+      </c>
+      <c r="I42" t="s">
+        <v>211</v>
+      </c>
+      <c r="J42">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E43" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="F43">
+        <v>2000</v>
+      </c>
+      <c r="I43" t="s">
+        <v>212</v>
+      </c>
+      <c r="J43">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E44" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="F44">
+        <v>500</v>
+      </c>
+      <c r="I44" t="s">
+        <v>212</v>
+      </c>
+      <c r="J44">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E45" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="F45">
+        <v>100</v>
+      </c>
+      <c r="I45" t="s">
+        <v>213</v>
+      </c>
+      <c r="J45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E46" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="F46">
+        <v>67</v>
+      </c>
+      <c r="I46" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E47" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="F47">
+        <v>50</v>
+      </c>
+      <c r="I47" t="s">
+        <v>215</v>
+      </c>
+      <c r="J47">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E48" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="F48">
+        <v>70</v>
+      </c>
+      <c r="I48" t="s">
+        <v>216</v>
+      </c>
+      <c r="J48">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E49" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="F49">
+        <v>300</v>
+      </c>
+      <c r="I49" t="s">
+        <v>217</v>
+      </c>
+      <c r="J49">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E50" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="F50">
+        <v>100</v>
+      </c>
+      <c r="I50" t="s">
+        <v>24</v>
+      </c>
+      <c r="J50">
+        <v>20914</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I51" t="s">
+        <v>219</v>
+      </c>
+      <c r="J51">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J52">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F54">
+        <f>SUM(F40:F50)</f>
+        <v>4687</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B62" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="4">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="98" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B98">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="99" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B99">
+        <v>2500</v>
+      </c>
+      <c r="J99">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="100" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B100">
+        <v>2500</v>
+      </c>
+      <c r="J100">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="101" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B101">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="102" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B102">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="106" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B106">
+        <f>SUM(B98:B102)</f>
+        <v>9500</v>
+      </c>
+      <c r="D106">
+        <f>B106-7000</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="107" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P107">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="108" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P108" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P109" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P110" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P111" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="112" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P112" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="113" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="P113" s="4">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="114" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="P114" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="115" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="E115">
+        <v>1400</v>
+      </c>
+      <c r="P115" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="116" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="E116">
+        <v>1300</v>
+      </c>
+      <c r="P116" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="117" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="E117">
+        <v>950</v>
+      </c>
+      <c r="P117" s="4"/>
+    </row>
+    <row r="118" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="P118" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="121" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="E121">
+        <f>SUM(E115:E119)</f>
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="125" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="P125">
+        <f>SUM(P105:P122)</f>
+        <v>516.99</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B974066F-70AB-4CE0-9413-18C0CA619219}">
   <sheetPr codeName="Feuil20"/>
   <dimension ref="A1:O41"/>
@@ -16288,7 +17547,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A0FB8E-CB12-475E-9D50-00930E5BD370}">
   <sheetPr codeName="Feuil21"/>
   <dimension ref="A1:J36"/>
@@ -16822,10 +18081,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94700D3-58F8-480F-AA59-9339E917FDF7}">
   <sheetPr codeName="Feuil22"/>
-  <dimension ref="A1:R102"/>
+  <dimension ref="A1:R103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
@@ -17816,8 +19075,8 @@
         <v>450000</v>
       </c>
       <c r="D79">
-        <f>30000+50000+150000+30000+50000</f>
-        <v>310000</v>
+        <f>30000+50000+150000+30000+50000+50000</f>
+        <v>360000</v>
       </c>
       <c r="E79" t="s">
         <v>293</v>
@@ -17940,148 +19199,159 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B89" s="1">
-        <v>350000</v>
+        <v>360000</v>
       </c>
       <c r="C89" s="1">
-        <v>350000</v>
+        <v>360000</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B90" s="1">
+        <v>350000</v>
+      </c>
+      <c r="C90" s="1">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B90" s="1">
+      <c r="B91" s="1">
         <v>200000</v>
       </c>
-      <c r="C90" s="1">
+      <c r="C91" s="1">
         <f>200000</f>
         <v>200000</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>4</v>
-      </c>
-      <c r="B92">
-        <f>SUM(B67:B90)</f>
-        <v>12102750</v>
-      </c>
-      <c r="C92">
-        <f>SUM(C67:C90)+D79</f>
-        <v>11981750</v>
-      </c>
-    </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>4</v>
+      </c>
+      <c r="B93">
+        <f>SUM(B67:B91)</f>
+        <v>12462750</v>
+      </c>
+      <c r="C93">
+        <f>SUM(C67:C91)+D79</f>
+        <v>12391750</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>253</v>
       </c>
-      <c r="B93">
-        <f>B92/655</f>
-        <v>18477.480916030534</v>
-      </c>
-      <c r="C93">
-        <f>C92/655</f>
-        <v>18292.748091603054</v>
-      </c>
-    </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="H94" t="s">
+      <c r="B94">
+        <f>B93/655</f>
+        <v>19027.099236641221</v>
+      </c>
+      <c r="C94">
+        <f>C93/655</f>
+        <v>18918.702290076337</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H95" t="s">
         <v>285</v>
       </c>
-      <c r="I94">
+      <c r="I95">
         <f>SUM(I74:I80)</f>
         <v>45.894999999999996</v>
       </c>
-      <c r="K94" t="s">
+      <c r="K95" t="s">
         <v>4</v>
       </c>
-      <c r="L94">
-        <f>SUM(L72:L93)</f>
+      <c r="L95">
+        <f>SUM(L72:L94)</f>
         <v>84.603999999999985</v>
       </c>
-      <c r="N94" t="s">
+      <c r="N95" t="s">
         <v>4</v>
       </c>
-      <c r="O94">
-        <f t="shared" ref="O94" si="0">SUM(O72:O93)</f>
+      <c r="O95">
+        <f t="shared" ref="O95" si="0">SUM(O72:O94)</f>
         <v>11.743600000000001</v>
       </c>
-      <c r="Q94" t="s">
+      <c r="Q95" t="s">
         <v>35</v>
       </c>
-      <c r="R94">
-        <f t="shared" ref="R94" si="1">SUM(R72:R93)</f>
+      <c r="R95">
+        <f t="shared" ref="R95" si="1">SUM(R72:R94)</f>
         <v>67.2</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="L95">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L96">
         <v>130</v>
       </c>
-      <c r="O95">
+      <c r="O96">
         <v>6</v>
       </c>
-      <c r="R95">
+      <c r="R96">
         <v>67</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
         <v>249</v>
       </c>
-      <c r="B96">
-        <f>2000+4000+3000+800+553+1950+4000+1000</f>
-        <v>17303</v>
-      </c>
-      <c r="C96" t="s">
+      <c r="B97">
+        <f>2000+4000+3000+800+553+1950+4000+1000+1300</f>
+        <v>18603</v>
+      </c>
+      <c r="C97" t="s">
         <v>81</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D97" t="s">
         <v>87</v>
       </c>
-      <c r="E96" t="s">
+      <c r="E97" t="s">
         <v>292</v>
       </c>
-      <c r="F96" t="s">
+      <c r="F97" t="s">
         <v>69</v>
       </c>
-      <c r="G96" t="s">
+      <c r="G97" t="s">
         <v>291</v>
       </c>
-      <c r="H96" t="s">
+      <c r="H97" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>21</v>
       </c>
-      <c r="B98">
-        <f>B96-C93</f>
-        <v>-989.74809160305449</v>
-      </c>
-      <c r="L98">
-        <f>L95*7000</f>
+      <c r="B99">
+        <f>B97-C94</f>
+        <v>-315.70229007633679</v>
+      </c>
+      <c r="L99">
+        <f>L96*7000</f>
         <v>910000</v>
       </c>
-      <c r="O98">
-        <f>O95*5000</f>
+      <c r="O99">
+        <f>O96*5000</f>
         <v>30000</v>
       </c>
-      <c r="R98">
-        <f>R95*5500</f>
+      <c r="R99">
+        <f>R96*5500</f>
         <v>368500</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K102" t="s">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="K103" t="s">
         <v>35</v>
       </c>
-      <c r="M102">
-        <f>I98+L98+O98+R98</f>
+      <c r="M103">
+        <f>I99+L99+O99+R99</f>
         <v>1308500</v>
       </c>
     </row>
@@ -18090,7 +19360,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949D250C-39B2-4E80-98CE-CD0726DE900E}">
   <sheetPr codeName="Feuil23"/>
   <dimension ref="A3:G22"/>
@@ -18321,7 +19591,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A9C44F7-AFBE-4C6B-AF7F-6A7B39EB63FD}">
   <sheetPr codeName="Feuil24"/>
   <dimension ref="A2:P29"/>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git-projet\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E7E0B10-4297-49B7-95C4-5467CB1A6ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71227AB-09C0-44F6-972F-53C274CDFC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" firstSheet="12" activeTab="20" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
@@ -33,11 +33,13 @@
     <sheet name="Mai25" sheetId="49" r:id="rId18"/>
     <sheet name="JUIN125" sheetId="51" r:id="rId19"/>
     <sheet name="Juin25" sheetId="50" r:id="rId20"/>
-    <sheet name="Credit" sheetId="28" r:id="rId21"/>
-    <sheet name="Entreprise" sheetId="35" r:id="rId22"/>
-    <sheet name="Construction " sheetId="27" r:id="rId23"/>
-    <sheet name="Construction2" sheetId="39" r:id="rId24"/>
-    <sheet name="Terrain" sheetId="18" r:id="rId25"/>
+    <sheet name="Juillet25" sheetId="52" r:id="rId21"/>
+    <sheet name="Feuil2" sheetId="53" r:id="rId22"/>
+    <sheet name="Credit" sheetId="28" r:id="rId23"/>
+    <sheet name="Entreprise" sheetId="35" r:id="rId24"/>
+    <sheet name="Construction " sheetId="27" r:id="rId25"/>
+    <sheet name="Construction2" sheetId="39" r:id="rId26"/>
+    <sheet name="Terrain" sheetId="18" r:id="rId27"/>
   </sheets>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -58,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="311">
   <si>
     <t>Loyer</t>
   </si>
@@ -982,6 +984,15 @@
   </si>
   <si>
     <t>auot</t>
+  </si>
+  <si>
+    <t>boua</t>
+  </si>
+  <si>
+    <t>manty</t>
+  </si>
+  <si>
+    <t>frigo</t>
   </si>
 </sst>
 </file>
@@ -17106,6 +17117,1266 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB1474C9-5FCD-4AA4-B4FC-6451FD68E67A}">
+  <dimension ref="A1:T125"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.125" customWidth="1"/>
+    <col min="8" max="8" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.625" customWidth="1"/>
+    <col min="11" max="11" width="8.125" customWidth="1"/>
+    <col min="13" max="13" width="18.125" customWidth="1"/>
+    <col min="18" max="18" width="3.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A3" s="3"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J3" s="5"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="5"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A4" s="3"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4">
+        <v>6000</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="O4" s="4">
+        <v>1480</v>
+      </c>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="5"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A5" s="3"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="5"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A6" s="3"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="8"/>
+      <c r="M6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N6" s="8"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="5"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A7" s="3"/>
+      <c r="B7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1012</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="4">
+        <v>150</v>
+      </c>
+      <c r="O7" s="4"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="5"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A8" s="3"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N8" s="4">
+        <v>200</v>
+      </c>
+      <c r="O8" s="4"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="5"/>
+      <c r="T8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A9" s="3"/>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="4">
+        <v>200</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F9" s="4">
+        <v>96</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N9" s="4">
+        <v>200</v>
+      </c>
+      <c r="O9" s="4"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="5"/>
+      <c r="T9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A10" s="3"/>
+      <c r="B10" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C10" s="4">
+        <v>200</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F10" s="4">
+        <v>50</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="4">
+        <v>300</v>
+      </c>
+      <c r="O10" s="4"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="5"/>
+      <c r="T10">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A11" s="3"/>
+      <c r="B11" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" s="4">
+        <v>39</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4">
+        <v>157</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N11" s="4">
+        <v>100</v>
+      </c>
+      <c r="O11" s="4"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="5"/>
+      <c r="T11">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A12" s="3"/>
+      <c r="B12" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="4">
+        <v>300</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="4">
+        <v>13</v>
+      </c>
+      <c r="O12" s="4"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="5"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A13" s="3"/>
+      <c r="B13" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C13" s="4">
+        <v>100</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F13" s="4">
+        <v>52</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N13" s="4">
+        <v>13</v>
+      </c>
+      <c r="O13" s="4"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="5"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A14" s="3"/>
+      <c r="B14" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C14" s="4">
+        <v>100</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="4">
+        <v>13</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="5"/>
+      <c r="T14">
+        <f>SUM(T8:T11)</f>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A15" s="3"/>
+      <c r="B15" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C15" s="4">
+        <v>280</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" s="4">
+        <v>100</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="5"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A16" s="3"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F16" s="4">
+        <v>131</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="5"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A17" s="3"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="5"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A18" s="3"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="5"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A19" s="3"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="5"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A20" s="3"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="5"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A21" s="3"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="5"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A22" s="3"/>
+      <c r="B22" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="4">
+        <f>SUM(C7:C19)</f>
+        <v>919</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4">
+        <f>SUM(F7:F20)+150</f>
+        <v>3061</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4">
+        <f>SUM(I7:I19)</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="5"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4">
+        <f>SUM(N7:N19)</f>
+        <v>976</v>
+      </c>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4">
+        <f>SUM(Q7:Q18)</f>
+        <v>0</v>
+      </c>
+      <c r="R22" s="4"/>
+      <c r="S22" s="5"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A23" s="3"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="5"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A24" s="3"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="5"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A25" s="3"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="5"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A26" s="3"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="4">
+        <f>C22+F22+I22</f>
+        <v>3980</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4">
+        <f>N22+Q22</f>
+        <v>976</v>
+      </c>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="5"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A27" s="3"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="5"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A28" s="3"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="4"/>
+      <c r="R28" s="4"/>
+      <c r="S28" s="5"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A29" s="3"/>
+      <c r="B29" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="4">
+        <f>ABS(G4-D26)</f>
+        <v>3980</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="4">
+        <f>O4-P26</f>
+        <v>504</v>
+      </c>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="4"/>
+      <c r="R29" s="4"/>
+      <c r="S29" s="5"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A30" s="3"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="5"/>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="4"/>
+      <c r="S33" s="4"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A34" s="2"/>
+      <c r="B34" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="4">
+        <f>H4-D26</f>
+        <v>2020</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4">
+        <f>C29+L29</f>
+        <v>4484</v>
+      </c>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="4"/>
+      <c r="R34" s="4"/>
+      <c r="S34" s="4"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A35" s="2"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4"/>
+      <c r="Q35" s="4"/>
+      <c r="R35" s="4"/>
+      <c r="S35" s="4"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="E36">
+        <f>5.2+13.8+10.96+13+13+21+6.99+47+62+12+68+40</f>
+        <v>312.95</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="I39" t="s">
+        <v>208</v>
+      </c>
+      <c r="J39">
+        <v>39</v>
+      </c>
+      <c r="L39" t="s">
+        <v>214</v>
+      </c>
+      <c r="M39">
+        <f>SUM(J39:J58)</f>
+        <v>22002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E40" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F40">
+        <v>500</v>
+      </c>
+      <c r="I40" t="s">
+        <v>209</v>
+      </c>
+      <c r="J40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E41" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="F41">
+        <v>800</v>
+      </c>
+      <c r="I41" t="s">
+        <v>210</v>
+      </c>
+      <c r="J41">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E42" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="F42">
+        <v>200</v>
+      </c>
+      <c r="I42" t="s">
+        <v>211</v>
+      </c>
+      <c r="J42">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E43" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="F43">
+        <v>2000</v>
+      </c>
+      <c r="I43" t="s">
+        <v>212</v>
+      </c>
+      <c r="J43">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E44" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="F44">
+        <v>500</v>
+      </c>
+      <c r="I44" t="s">
+        <v>212</v>
+      </c>
+      <c r="J44">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E45" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="F45">
+        <v>100</v>
+      </c>
+      <c r="I45" t="s">
+        <v>213</v>
+      </c>
+      <c r="J45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E46" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="F46">
+        <v>67</v>
+      </c>
+      <c r="I46" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E47" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="F47">
+        <v>50</v>
+      </c>
+      <c r="I47" t="s">
+        <v>215</v>
+      </c>
+      <c r="J47">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E48" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="F48">
+        <v>70</v>
+      </c>
+      <c r="I48" t="s">
+        <v>216</v>
+      </c>
+      <c r="J48">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E49" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="F49">
+        <v>300</v>
+      </c>
+      <c r="I49" t="s">
+        <v>217</v>
+      </c>
+      <c r="J49">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E50" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="F50">
+        <v>100</v>
+      </c>
+      <c r="I50" t="s">
+        <v>24</v>
+      </c>
+      <c r="J50">
+        <v>20914</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.5">
+      <c r="I51" t="s">
+        <v>219</v>
+      </c>
+      <c r="J51">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.5">
+      <c r="J52">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.5">
+      <c r="F54">
+        <f>SUM(F40:F50)</f>
+        <v>4687</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.5">
+      <c r="B62" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="4">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="98" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="B98">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="99" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="B99">
+        <v>2500</v>
+      </c>
+      <c r="J99">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="100" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="B100">
+        <v>2500</v>
+      </c>
+      <c r="J100">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="101" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="B101">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="102" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="B102">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="106" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="B106">
+        <f>SUM(B98:B102)</f>
+        <v>9500</v>
+      </c>
+      <c r="D106">
+        <f>B106-7000</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="107" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="P107">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="108" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="P108" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="P109" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="P110" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="P111" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="112" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="P112" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="113" spans="5:16" x14ac:dyDescent="0.5">
+      <c r="P113" s="4">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="114" spans="5:16" x14ac:dyDescent="0.5">
+      <c r="P114" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="115" spans="5:16" x14ac:dyDescent="0.5">
+      <c r="E115">
+        <v>1400</v>
+      </c>
+      <c r="P115" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="116" spans="5:16" x14ac:dyDescent="0.5">
+      <c r="E116">
+        <v>1300</v>
+      </c>
+      <c r="P116" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="117" spans="5:16" x14ac:dyDescent="0.5">
+      <c r="E117">
+        <v>950</v>
+      </c>
+      <c r="P117" s="4"/>
+    </row>
+    <row r="118" spans="5:16" x14ac:dyDescent="0.5">
+      <c r="P118" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="121" spans="5:16" x14ac:dyDescent="0.5">
+      <c r="E121">
+        <f>SUM(E115:E119)</f>
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="125" spans="5:16" x14ac:dyDescent="0.5">
+      <c r="P125">
+        <f>SUM(P105:P122)</f>
+        <v>516.99</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCF680BA-C5EE-4B0D-B474-B9A682483A7B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B974066F-70AB-4CE0-9413-18C0CA619219}">
   <sheetPr codeName="Feuil20"/>
   <dimension ref="A1:O41"/>
@@ -17561,7 +18832,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A0FB8E-CB12-475E-9D50-00930E5BD370}">
   <sheetPr codeName="Feuil21"/>
   <dimension ref="A1:J36"/>
@@ -17970,8 +19241,7 @@
         <v>8150</v>
       </c>
       <c r="D28" s="1">
-        <f>C28+(C28*20%)</f>
-        <v>9780</v>
+        <v>9660</v>
       </c>
       <c r="E28" s="1">
         <f>C28*21%</f>
@@ -17983,7 +19253,7 @@
       </c>
       <c r="G28" s="1">
         <f>D28-C28</f>
-        <v>1630</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.5">
@@ -17996,7 +19266,7 @@
       </c>
       <c r="D30">
         <f>D27+D28</f>
-        <v>9780</v>
+        <v>9660</v>
       </c>
       <c r="E30" s="1">
         <f>E27+E28</f>
@@ -18008,7 +19278,7 @@
       </c>
       <c r="G30" s="1">
         <f>G27+G28</f>
-        <v>1630</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.5">
@@ -18046,23 +19316,22 @@
         <v>193</v>
       </c>
       <c r="C34" s="1">
-        <v>4250</v>
+        <v>8050</v>
       </c>
       <c r="D34" s="1">
-        <f>C34+(C34*20%)</f>
-        <v>5100</v>
+        <v>9660</v>
       </c>
       <c r="E34" s="1">
         <f>C34*26%</f>
-        <v>1105</v>
+        <v>2093</v>
       </c>
       <c r="F34" s="1">
         <f>C34-E34</f>
-        <v>3145</v>
+        <v>5957</v>
       </c>
       <c r="G34" s="1">
         <f>D34-C34</f>
-        <v>850</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.5">
@@ -18071,23 +19340,23 @@
       </c>
       <c r="C36">
         <f>C33+C34</f>
-        <v>4250</v>
+        <v>8050</v>
       </c>
       <c r="D36">
         <f>D33+D34</f>
-        <v>5100</v>
+        <v>9660</v>
       </c>
       <c r="E36" s="1">
         <f>E33+E34</f>
-        <v>1105</v>
+        <v>2093</v>
       </c>
       <c r="F36" s="11">
         <f>F33+F34</f>
-        <v>3145</v>
+        <v>5957</v>
       </c>
       <c r="G36" s="1">
         <f>G33+G34</f>
-        <v>850</v>
+        <v>1610</v>
       </c>
     </row>
   </sheetData>
@@ -18095,7 +19364,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94700D3-58F8-480F-AA59-9339E917FDF7}">
   <sheetPr codeName="Feuil22"/>
   <dimension ref="A1:R103"/>
@@ -19374,7 +20643,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949D250C-39B2-4E80-98CE-CD0726DE900E}">
   <sheetPr codeName="Feuil23"/>
   <dimension ref="A3:G22"/>
@@ -19605,7 +20874,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A9C44F7-AFBE-4C6B-AF7F-6A7B39EB63FD}">
   <sheetPr codeName="Feuil24"/>
   <dimension ref="A2:P29"/>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git-projet\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71227AB-09C0-44F6-972F-53C274CDFC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DFFE692-7A46-4525-A4A8-41D1915898AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" firstSheet="12" activeTab="20" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="313">
   <si>
     <t>Loyer</t>
   </si>
@@ -993,6 +993,12 @@
   </si>
   <si>
     <t>frigo</t>
+  </si>
+  <si>
+    <t>vacin</t>
+  </si>
+  <si>
+    <t>Potre alu</t>
   </si>
 </sst>
 </file>
@@ -17325,9 +17331,7 @@
       <c r="E8" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="F8" s="4">
-        <v>1000</v>
-      </c>
+      <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="2"/>
       <c r="I8" s="4"/>
@@ -17460,7 +17464,9 @@
       <c r="B12" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C12" s="4"/>
+      <c r="C12" s="4">
+        <v>1000</v>
+      </c>
       <c r="D12" s="4"/>
       <c r="E12" s="2" t="s">
         <v>9</v>
@@ -17577,8 +17583,12 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A16" s="3"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="4"/>
+      <c r="B16" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C16" s="4">
+        <v>400</v>
+      </c>
       <c r="D16" s="4"/>
       <c r="E16" s="2" t="s">
         <v>222</v>
@@ -17602,8 +17612,12 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A17" s="3"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="4"/>
+      <c r="B17" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C17" s="4">
+        <v>300</v>
+      </c>
       <c r="D17" s="4"/>
       <c r="E17" s="2"/>
       <c r="F17" s="4"/>
@@ -17710,13 +17724,13 @@
       </c>
       <c r="C22" s="4">
         <f>SUM(C7:C19)</f>
-        <v>919</v>
+        <v>2619</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4">
         <f>SUM(F7:F20)+150</f>
-        <v>3061</v>
+        <v>2061</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
@@ -17812,7 +17826,7 @@
       </c>
       <c r="D26" s="4">
         <f>C22+F22+I22</f>
-        <v>3980</v>
+        <v>4680</v>
       </c>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
@@ -17884,7 +17898,7 @@
       </c>
       <c r="C29" s="4">
         <f>ABS(G4-D26)</f>
-        <v>3980</v>
+        <v>4680</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -17999,7 +18013,7 @@
       </c>
       <c r="C34" s="4">
         <f>H4-D26</f>
-        <v>2020</v>
+        <v>1320</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -18009,7 +18023,7 @@
       <c r="I34" s="4"/>
       <c r="J34" s="4">
         <f>C29+L29</f>
-        <v>4484</v>
+        <v>5184</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git-projet\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DFFE692-7A46-4525-A4A8-41D1915898AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9594F3B3-1D21-4C6B-B5CE-CD30C43F6D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" firstSheet="12" activeTab="20" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" firstSheet="13" activeTab="22" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
   <sheets>
     <sheet name="Sept23" sheetId="29" r:id="rId1"/>
@@ -18592,6 +18592,9 @@
       <c r="L15" t="s">
         <v>67</v>
       </c>
+      <c r="M15">
+        <v>500</v>
+      </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.5">
       <c r="I16" t="s">
@@ -18599,7 +18602,7 @@
       </c>
       <c r="J16">
         <f>J14-M22</f>
-        <v>1616</v>
+        <v>1116</v>
       </c>
       <c r="L16" t="s">
         <v>298</v>
@@ -18625,13 +18628,13 @@
       </c>
       <c r="B20">
         <f>B6-F41</f>
-        <v>16000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.5">
       <c r="M22">
         <f>SUM(M7:M20)</f>
-        <v>3500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.5">
@@ -18759,7 +18762,9 @@
         <v>306</v>
       </c>
       <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
+      <c r="C34" s="9">
+        <v>1000</v>
+      </c>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
@@ -18826,7 +18831,7 @@
       </c>
       <c r="C41" s="10">
         <f>SUM(C27:C39)</f>
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="D41" s="10">
         <f>SUM(D27:D39)</f>
@@ -18838,7 +18843,7 @@
       </c>
       <c r="F41" s="10">
         <f>SUM(B41:E41)</f>
-        <v>5500</v>
+        <v>6500</v>
       </c>
     </row>
   </sheetData>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git-projet\myDocs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AG_AUTOMATION\Documents\projet-git\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9594F3B3-1D21-4C6B-B5CE-CD30C43F6D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F30FFA-C23C-4A35-964A-DDC8D2FF6C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" firstSheet="13" activeTab="22" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="13" activeTab="20" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
   <sheets>
     <sheet name="Sept23" sheetId="29" r:id="rId1"/>
@@ -17465,7 +17465,7 @@
         <v>223</v>
       </c>
       <c r="C12" s="4">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="2" t="s">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="C22" s="4">
         <f>SUM(C7:C19)</f>
-        <v>2619</v>
+        <v>3619</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -17826,7 +17826,7 @@
       </c>
       <c r="D26" s="4">
         <f>C22+F22+I22</f>
-        <v>4680</v>
+        <v>5680</v>
       </c>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
@@ -17898,7 +17898,7 @@
       </c>
       <c r="C29" s="4">
         <f>ABS(G4-D26)</f>
-        <v>4680</v>
+        <v>5680</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -18013,7 +18013,7 @@
       </c>
       <c r="C34" s="4">
         <f>H4-D26</f>
-        <v>1320</v>
+        <v>320</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -18023,7 +18023,7 @@
       <c r="I34" s="4"/>
       <c r="J34" s="4">
         <f>C29+L29</f>
-        <v>5184</v>
+        <v>6184</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AG_AUTOMATION\Documents\projet-git\myDocs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git-projet\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F30FFA-C23C-4A35-964A-DDC8D2FF6C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28F8F0B-7EDF-41D9-89BE-80EB8A88BFF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="13" activeTab="20" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" firstSheet="13" activeTab="21" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
   <sheets>
     <sheet name="Sept23" sheetId="29" r:id="rId1"/>
@@ -34,7 +34,7 @@
     <sheet name="JUIN125" sheetId="51" r:id="rId19"/>
     <sheet name="Juin25" sheetId="50" r:id="rId20"/>
     <sheet name="Juillet25" sheetId="52" r:id="rId21"/>
-    <sheet name="Feuil2" sheetId="53" r:id="rId22"/>
+    <sheet name="AOUT25" sheetId="53" r:id="rId22"/>
     <sheet name="Credit" sheetId="28" r:id="rId23"/>
     <sheet name="Entreprise" sheetId="35" r:id="rId24"/>
     <sheet name="Construction " sheetId="27" r:id="rId25"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="313">
   <si>
     <t>Loyer</t>
   </si>
@@ -18383,9 +18383,1251 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCF680BA-C5EE-4B0D-B474-B9A682483A7B}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:T125"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.125" customWidth="1"/>
+    <col min="8" max="8" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.625" customWidth="1"/>
+    <col min="11" max="11" width="8.125" customWidth="1"/>
+    <col min="13" max="13" width="18.125" customWidth="1"/>
+    <col min="18" max="18" width="3.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A3" s="3"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J3" s="5"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="5"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A4" s="3"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4">
+        <v>6000</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="O4" s="4">
+        <v>1480</v>
+      </c>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="5"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A5" s="3"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="5"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A6" s="3"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="8"/>
+      <c r="M6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N6" s="8"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="5"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A7" s="3"/>
+      <c r="B7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1034</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="4">
+        <v>150</v>
+      </c>
+      <c r="O7" s="4"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="5"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A8" s="3"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N8" s="4">
+        <v>200</v>
+      </c>
+      <c r="O8" s="4"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="5"/>
+      <c r="T8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A9" s="3"/>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="4">
+        <v>150</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F9" s="4">
+        <v>96</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N9" s="4">
+        <v>200</v>
+      </c>
+      <c r="O9" s="4"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="5"/>
+      <c r="T9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A10" s="3"/>
+      <c r="B10" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F10" s="4">
+        <v>50</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="4">
+        <v>300</v>
+      </c>
+      <c r="O10" s="4"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="5"/>
+      <c r="T10">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A11" s="3"/>
+      <c r="B11" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" s="4">
+        <v>39</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4">
+        <v>157</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N11" s="4">
+        <v>100</v>
+      </c>
+      <c r="O11" s="4"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="5"/>
+      <c r="T11">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A12" s="3"/>
+      <c r="B12" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="4">
+        <v>300</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="4">
+        <v>13</v>
+      </c>
+      <c r="O12" s="4"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="5"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A13" s="3"/>
+      <c r="B13" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F13" s="4">
+        <v>52</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N13" s="4">
+        <v>13</v>
+      </c>
+      <c r="O13" s="4"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="5"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A14" s="3"/>
+      <c r="B14" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="4">
+        <v>13</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="5"/>
+      <c r="T14">
+        <f>SUM(T8:T11)</f>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A15" s="3"/>
+      <c r="B15" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" s="4">
+        <v>100</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="5"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.5">
+      <c r="A16" s="3"/>
+      <c r="B16" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="5"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A17" s="3"/>
+      <c r="B17" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="4">
+        <v>200</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="5"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A18" s="3"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="5"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A19" s="3"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="5"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A20" s="3"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="5"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A21" s="3"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="5"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A22" s="3"/>
+      <c r="B22" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="4">
+        <f>SUM(C7:C19)</f>
+        <v>189</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4">
+        <f>SUM(F7:F20)+150</f>
+        <v>3152</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4">
+        <f>SUM(I7:I19)</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="5"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4">
+        <f>SUM(N7:N19)</f>
+        <v>976</v>
+      </c>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4">
+        <f>SUM(Q7:Q18)</f>
+        <v>0</v>
+      </c>
+      <c r="R22" s="4"/>
+      <c r="S22" s="5"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A23" s="3"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="5"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A24" s="3"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="5"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A25" s="3"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="5"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A26" s="3"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="4">
+        <f>C22+F22+I22</f>
+        <v>3341</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4">
+        <f>N22+Q22</f>
+        <v>976</v>
+      </c>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="5"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A27" s="3"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="5"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A28" s="3"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="4"/>
+      <c r="R28" s="4"/>
+      <c r="S28" s="5"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A29" s="3"/>
+      <c r="B29" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="4">
+        <f>ABS(G4-D26)</f>
+        <v>3341</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="4">
+        <f>O4-P26</f>
+        <v>504</v>
+      </c>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="4"/>
+      <c r="R29" s="4"/>
+      <c r="S29" s="5"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A30" s="3"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="5"/>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="4"/>
+      <c r="S33" s="4"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A34" s="2"/>
+      <c r="B34" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="4">
+        <f>H4-D26</f>
+        <v>2659</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4">
+        <f>C29+L29</f>
+        <v>3845</v>
+      </c>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="4"/>
+      <c r="R34" s="4"/>
+      <c r="S34" s="4"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A35" s="2"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4"/>
+      <c r="Q35" s="4"/>
+      <c r="R35" s="4"/>
+      <c r="S35" s="4"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="E36">
+        <f>5.2+13.8+10.96+13+13+21+6.99+47+62+12+68+40</f>
+        <v>312.95</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="I39" t="s">
+        <v>208</v>
+      </c>
+      <c r="J39">
+        <v>39</v>
+      </c>
+      <c r="L39" t="s">
+        <v>214</v>
+      </c>
+      <c r="M39">
+        <f>SUM(J39:J58)</f>
+        <v>22002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E40" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F40">
+        <v>500</v>
+      </c>
+      <c r="I40" t="s">
+        <v>209</v>
+      </c>
+      <c r="J40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E41" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="F41">
+        <v>800</v>
+      </c>
+      <c r="I41" t="s">
+        <v>210</v>
+      </c>
+      <c r="J41">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E42" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="F42">
+        <v>200</v>
+      </c>
+      <c r="I42" t="s">
+        <v>211</v>
+      </c>
+      <c r="J42">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E43" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="F43">
+        <v>2000</v>
+      </c>
+      <c r="I43" t="s">
+        <v>212</v>
+      </c>
+      <c r="J43">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E44" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="F44">
+        <v>500</v>
+      </c>
+      <c r="I44" t="s">
+        <v>212</v>
+      </c>
+      <c r="J44">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E45" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="F45">
+        <v>100</v>
+      </c>
+      <c r="I45" t="s">
+        <v>213</v>
+      </c>
+      <c r="J45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E46" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="F46">
+        <v>67</v>
+      </c>
+      <c r="I46" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E47" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="F47">
+        <v>50</v>
+      </c>
+      <c r="I47" t="s">
+        <v>215</v>
+      </c>
+      <c r="J47">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E48" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="F48">
+        <v>70</v>
+      </c>
+      <c r="I48" t="s">
+        <v>216</v>
+      </c>
+      <c r="J48">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E49" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="F49">
+        <v>300</v>
+      </c>
+      <c r="I49" t="s">
+        <v>217</v>
+      </c>
+      <c r="J49">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="E50" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="F50">
+        <v>100</v>
+      </c>
+      <c r="I50" t="s">
+        <v>24</v>
+      </c>
+      <c r="J50">
+        <v>20914</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.5">
+      <c r="I51" t="s">
+        <v>219</v>
+      </c>
+      <c r="J51">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.5">
+      <c r="J52">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.5">
+      <c r="F54">
+        <f>SUM(F40:F50)</f>
+        <v>4687</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.5">
+      <c r="B62" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="4">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="98" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="B98">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="99" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="B99">
+        <v>2500</v>
+      </c>
+      <c r="J99">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="100" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="B100">
+        <v>2500</v>
+      </c>
+      <c r="J100">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="101" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="B101">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="102" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="B102">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="106" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="B106">
+        <f>SUM(B98:B102)</f>
+        <v>9500</v>
+      </c>
+      <c r="D106">
+        <f>B106-7000</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="107" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="P107">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="108" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="P108" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="P109" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="P110" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="P111" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="112" spans="2:16" x14ac:dyDescent="0.5">
+      <c r="P112" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="113" spans="5:16" x14ac:dyDescent="0.5">
+      <c r="P113" s="4">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="114" spans="5:16" x14ac:dyDescent="0.5">
+      <c r="P114" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="115" spans="5:16" x14ac:dyDescent="0.5">
+      <c r="E115">
+        <v>1400</v>
+      </c>
+      <c r="P115" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="116" spans="5:16" x14ac:dyDescent="0.5">
+      <c r="E116">
+        <v>1300</v>
+      </c>
+      <c r="P116" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="117" spans="5:16" x14ac:dyDescent="0.5">
+      <c r="E117">
+        <v>950</v>
+      </c>
+      <c r="P117" s="4"/>
+    </row>
+    <row r="118" spans="5:16" x14ac:dyDescent="0.5">
+      <c r="P118" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="121" spans="5:16" x14ac:dyDescent="0.5">
+      <c r="E121">
+        <f>SUM(E115:E119)</f>
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="125" spans="5:16" x14ac:dyDescent="0.5">
+      <c r="P125">
+        <f>SUM(P105:P122)</f>
+        <v>516.99</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git-projet\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28F8F0B-7EDF-41D9-89BE-80EB8A88BFF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60B28F1-C7FB-44C1-955E-32F458E66CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" firstSheet="13" activeTab="21" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" firstSheet="13" activeTab="22" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
   <sheets>
     <sheet name="Sept23" sheetId="29" r:id="rId1"/>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="B20">
         <f>B6-F41</f>
-        <v>15000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.5">
@@ -20003,7 +20003,9 @@
       <c r="A34" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="B34" s="9"/>
+      <c r="B34" s="9">
+        <v>500</v>
+      </c>
       <c r="C34" s="9">
         <v>1000</v>
       </c>
@@ -20015,7 +20017,9 @@
       <c r="A35" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="B35" s="9"/>
+      <c r="B35" s="9">
+        <v>500</v>
+      </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
@@ -20069,7 +20073,7 @@
       </c>
       <c r="B41" s="10">
         <f>SUM(B27:B39)</f>
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="C41" s="10">
         <f>SUM(C27:C39)</f>
@@ -20085,7 +20089,7 @@
       </c>
       <c r="F41" s="10">
         <f>SUM(B41:E41)</f>
-        <v>6500</v>
+        <v>7500</v>
       </c>
     </row>
   </sheetData>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git-projet\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{076ECAEA-D52A-4142-80BE-84A215C4B5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED0C9D8C-273F-4A79-911E-64176F42D3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" firstSheet="19" activeTab="22" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1614" uniqueCount="315">
   <si>
     <t>Loyer</t>
   </si>
@@ -255,18 +255,9 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>YG Consulting</t>
-  </si>
-  <si>
     <t>septembre</t>
   </si>
   <si>
-    <t xml:space="preserve">aout </t>
-  </si>
-  <si>
-    <t>juillet</t>
-  </si>
-  <si>
     <t>mai</t>
   </si>
   <si>
@@ -315,9 +306,6 @@
     <t>yaba</t>
   </si>
   <si>
-    <t>idi</t>
-  </si>
-  <si>
     <t>opel</t>
   </si>
   <si>
@@ -840,9 +828,6 @@
     <t>voiture</t>
   </si>
   <si>
-    <t>avirl</t>
-  </si>
-  <si>
     <t>CANAPé</t>
   </si>
   <si>
@@ -957,9 +942,6 @@
     <t>retrait maroc</t>
   </si>
   <si>
-    <t>aout</t>
-  </si>
-  <si>
     <t>maroc</t>
   </si>
   <si>
@@ -1018,6 +1000,12 @@
   </si>
   <si>
     <t>Aliment finition et vaccin</t>
+  </si>
+  <si>
+    <t>Lahat</t>
+  </si>
+  <si>
+    <t>R 5000</t>
   </si>
 </sst>
 </file>
@@ -2730,7 +2718,7 @@
     <row r="10" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C10" s="4">
         <v>50</v>
@@ -2762,7 +2750,7 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C11" s="4">
         <v>206</v>
@@ -2796,7 +2784,7 @@
     <row r="12" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C12" s="4">
         <v>100</v>
@@ -2942,7 +2930,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F17" s="4">
         <f>M38</f>
@@ -2968,7 +2956,7 @@
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F18" s="4">
         <v>1000</v>
@@ -3204,7 +3192,7 @@
     <row r="28" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A28" s="3"/>
       <c r="B28" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C28" s="4">
         <f>ABS(G4-D25)</f>
@@ -3369,13 +3357,13 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.5">
       <c r="I38" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="J38">
         <v>39</v>
       </c>
       <c r="L38" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M38">
         <f>SUM(J38:J57)</f>
@@ -3384,13 +3372,13 @@
     </row>
     <row r="39" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E39" s="13" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F39">
         <v>500</v>
       </c>
       <c r="I39" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J39">
         <v>100</v>
@@ -3398,13 +3386,13 @@
     </row>
     <row r="40" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E40" s="13" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F40">
         <v>800</v>
       </c>
       <c r="I40" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J40">
         <v>21</v>
@@ -3412,13 +3400,13 @@
     </row>
     <row r="41" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E41" s="13" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F41">
         <v>200</v>
       </c>
       <c r="I41" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J41">
         <v>20</v>
@@ -3426,13 +3414,13 @@
     </row>
     <row r="42" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E42" s="13" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F42">
         <v>2000</v>
       </c>
       <c r="I42" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J42">
         <v>20</v>
@@ -3440,13 +3428,13 @@
     </row>
     <row r="43" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E43" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F43">
         <v>500</v>
       </c>
       <c r="I43" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J43">
         <v>27</v>
@@ -3454,13 +3442,13 @@
     </row>
     <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E44" s="13" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F44">
         <v>100</v>
       </c>
       <c r="I44" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="J44">
         <v>67</v>
@@ -3468,7 +3456,7 @@
     </row>
     <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E45" s="13" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F45">
         <v>67</v>
@@ -3482,13 +3470,13 @@
     </row>
     <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E46" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F46">
         <v>50</v>
       </c>
       <c r="I46" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J46">
         <v>31</v>
@@ -3496,13 +3484,13 @@
     </row>
     <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E47" s="13" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F47">
         <v>70</v>
       </c>
       <c r="I47" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J47">
         <v>32</v>
@@ -3510,13 +3498,13 @@
     </row>
     <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E48" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F48">
         <v>300</v>
       </c>
       <c r="I48" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="J48">
         <v>46</v>
@@ -3524,7 +3512,7 @@
     </row>
     <row r="49" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E49" s="13" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F49">
         <v>100</v>
@@ -3538,7 +3526,7 @@
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.5">
       <c r="I50" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J50">
         <v>357</v>
@@ -3895,7 +3883,7 @@
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F8" s="4">
         <v>1000</v>
@@ -3958,14 +3946,14 @@
     <row r="10" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C10" s="4">
         <v>200</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F10" s="4">
         <v>50</v>
@@ -3994,7 +3982,7 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C11" s="4">
         <v>229</v>
@@ -4028,7 +4016,7 @@
     <row r="12" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -4417,7 +4405,7 @@
     <row r="28" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A28" s="3"/>
       <c r="B28" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C28" s="4">
         <f>ABS(G4-D25)</f>
@@ -4585,13 +4573,13 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.5">
       <c r="I38" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="J38">
         <v>39</v>
       </c>
       <c r="L38" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M38">
         <f>SUM(J38:J57)</f>
@@ -4600,13 +4588,13 @@
     </row>
     <row r="39" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E39" s="13" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F39">
         <v>500</v>
       </c>
       <c r="I39" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J39">
         <v>100</v>
@@ -4614,13 +4602,13 @@
     </row>
     <row r="40" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E40" s="13" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F40">
         <v>800</v>
       </c>
       <c r="I40" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J40">
         <v>21</v>
@@ -4628,13 +4616,13 @@
     </row>
     <row r="41" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E41" s="13" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F41">
         <v>200</v>
       </c>
       <c r="I41" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J41">
         <v>20</v>
@@ -4642,13 +4630,13 @@
     </row>
     <row r="42" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E42" s="13" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F42">
         <v>2000</v>
       </c>
       <c r="I42" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J42">
         <v>20</v>
@@ -4656,13 +4644,13 @@
     </row>
     <row r="43" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E43" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F43">
         <v>500</v>
       </c>
       <c r="I43" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J43">
         <v>27</v>
@@ -4670,13 +4658,13 @@
     </row>
     <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E44" s="13" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F44">
         <v>100</v>
       </c>
       <c r="I44" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="J44">
         <v>67</v>
@@ -4684,7 +4672,7 @@
     </row>
     <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E45" s="13" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F45">
         <v>67</v>
@@ -4698,13 +4686,13 @@
     </row>
     <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E46" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F46">
         <v>50</v>
       </c>
       <c r="I46" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J46">
         <v>31</v>
@@ -4712,13 +4700,13 @@
     </row>
     <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E47" s="13" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F47">
         <v>70</v>
       </c>
       <c r="I47" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J47">
         <v>32</v>
@@ -4726,13 +4714,13 @@
     </row>
     <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E48" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F48">
         <v>300</v>
       </c>
       <c r="I48" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="J48">
         <v>46</v>
@@ -4740,7 +4728,7 @@
     </row>
     <row r="49" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E49" s="13" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F49">
         <v>100</v>
@@ -4754,7 +4742,7 @@
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.5">
       <c r="I50" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J50">
         <v>357</v>
@@ -5111,7 +5099,7 @@
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F8" s="4">
         <v>1000</v>
@@ -5174,14 +5162,14 @@
     <row r="10" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C10" s="4">
         <v>200</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F10" s="4">
         <v>30</v>
@@ -5210,7 +5198,7 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C11" s="4">
         <v>198</v>
@@ -5244,7 +5232,7 @@
     <row r="12" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C12" s="4">
         <v>500</v>
@@ -5275,7 +5263,7 @@
     <row r="13" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A13" s="3"/>
       <c r="B13" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C13" s="4">
         <v>150</v>
@@ -5306,7 +5294,7 @@
     <row r="14" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C14" s="4">
         <v>1500</v>
@@ -5365,7 +5353,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F16" s="4">
         <v>100</v>
@@ -5643,7 +5631,7 @@
     <row r="28" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A28" s="3"/>
       <c r="B28" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C28" s="4">
         <f>ABS(G4-D25)</f>
@@ -5811,13 +5799,13 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.5">
       <c r="I38" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="J38">
         <v>39</v>
       </c>
       <c r="L38" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M38">
         <f>SUM(J38:J57)</f>
@@ -5826,13 +5814,13 @@
     </row>
     <row r="39" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E39" s="13" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F39">
         <v>500</v>
       </c>
       <c r="I39" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J39">
         <v>100</v>
@@ -5840,13 +5828,13 @@
     </row>
     <row r="40" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E40" s="13" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F40">
         <v>800</v>
       </c>
       <c r="I40" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J40">
         <v>21</v>
@@ -5854,13 +5842,13 @@
     </row>
     <row r="41" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E41" s="13" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F41">
         <v>200</v>
       </c>
       <c r="I41" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J41">
         <v>20</v>
@@ -5868,13 +5856,13 @@
     </row>
     <row r="42" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E42" s="13" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F42">
         <v>2000</v>
       </c>
       <c r="I42" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J42">
         <v>20</v>
@@ -5882,13 +5870,13 @@
     </row>
     <row r="43" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E43" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F43">
         <v>500</v>
       </c>
       <c r="I43" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J43">
         <v>27</v>
@@ -5896,13 +5884,13 @@
     </row>
     <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E44" s="13" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F44">
         <v>100</v>
       </c>
       <c r="I44" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="J44">
         <v>67</v>
@@ -5910,7 +5898,7 @@
     </row>
     <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E45" s="13" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F45">
         <v>67</v>
@@ -5924,13 +5912,13 @@
     </row>
     <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E46" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F46">
         <v>50</v>
       </c>
       <c r="I46" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J46">
         <v>31</v>
@@ -5938,13 +5926,13 @@
     </row>
     <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E47" s="13" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F47">
         <v>70</v>
       </c>
       <c r="I47" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J47">
         <v>32</v>
@@ -5952,13 +5940,13 @@
     </row>
     <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E48" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F48">
         <v>300</v>
       </c>
       <c r="I48" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="J48">
         <v>46</v>
@@ -5966,7 +5954,7 @@
     </row>
     <row r="49" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E49" s="13" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F49">
         <v>100</v>
@@ -5980,7 +5968,7 @@
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.5">
       <c r="I50" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J50">
         <v>357</v>
@@ -6337,7 +6325,7 @@
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F8" s="4">
         <v>800</v>
@@ -6400,14 +6388,14 @@
     <row r="10" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C10" s="4">
         <v>350</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F10" s="4">
         <v>50</v>
@@ -6436,7 +6424,7 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C11" s="4">
         <v>198</v>
@@ -6470,7 +6458,7 @@
     <row r="12" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C12" s="4">
         <v>1000</v>
@@ -6509,7 +6497,7 @@
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F13" s="4">
         <f>95+52</f>
@@ -6534,7 +6522,7 @@
     <row r="14" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C14" s="4">
         <v>100</v>
@@ -6565,7 +6553,7 @@
     <row r="15" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C15" s="4">
         <v>500</v>
@@ -6597,7 +6585,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F16" s="4">
         <v>110</v>
@@ -6875,7 +6863,7 @@
     <row r="28" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A28" s="3"/>
       <c r="B28" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C28" s="4">
         <f>ABS(G4-D25)</f>
@@ -7043,13 +7031,13 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.5">
       <c r="I38" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="J38">
         <v>39</v>
       </c>
       <c r="L38" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M38">
         <f>SUM(J38:J57)</f>
@@ -7058,13 +7046,13 @@
     </row>
     <row r="39" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E39" s="13" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F39">
         <v>500</v>
       </c>
       <c r="I39" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J39">
         <v>100</v>
@@ -7072,13 +7060,13 @@
     </row>
     <row r="40" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E40" s="13" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F40">
         <v>800</v>
       </c>
       <c r="I40" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J40">
         <v>21</v>
@@ -7086,13 +7074,13 @@
     </row>
     <row r="41" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E41" s="13" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F41">
         <v>200</v>
       </c>
       <c r="I41" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J41">
         <v>20</v>
@@ -7100,13 +7088,13 @@
     </row>
     <row r="42" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E42" s="13" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F42">
         <v>2000</v>
       </c>
       <c r="I42" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J42">
         <v>20</v>
@@ -7114,13 +7102,13 @@
     </row>
     <row r="43" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E43" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F43">
         <v>500</v>
       </c>
       <c r="I43" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J43">
         <v>27</v>
@@ -7128,13 +7116,13 @@
     </row>
     <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E44" s="13" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F44">
         <v>100</v>
       </c>
       <c r="I44" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="J44">
         <v>67</v>
@@ -7142,7 +7130,7 @@
     </row>
     <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E45" s="13" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F45">
         <v>67</v>
@@ -7156,13 +7144,13 @@
     </row>
     <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E46" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F46">
         <v>50</v>
       </c>
       <c r="I46" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J46">
         <v>31</v>
@@ -7170,13 +7158,13 @@
     </row>
     <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E47" s="13" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F47">
         <v>70</v>
       </c>
       <c r="I47" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J47">
         <v>32</v>
@@ -7184,13 +7172,13 @@
     </row>
     <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E48" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F48">
         <v>300</v>
       </c>
       <c r="I48" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="J48">
         <v>46</v>
@@ -7198,7 +7186,7 @@
     </row>
     <row r="49" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E49" s="13" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F49">
         <v>100</v>
@@ -7212,7 +7200,7 @@
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.5">
       <c r="I50" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J50">
         <v>357</v>
@@ -7569,7 +7557,7 @@
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F8" s="4">
         <v>1000</v>
@@ -7606,7 +7594,7 @@
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F9" s="4">
         <v>96</v>
@@ -7635,7 +7623,7 @@
     <row r="10" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C10" s="4">
         <f>150+175</f>
@@ -7643,7 +7631,7 @@
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F10" s="4">
         <v>50</v>
@@ -7672,7 +7660,7 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C11" s="4">
         <v>198</v>
@@ -7706,7 +7694,7 @@
     <row r="12" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C12" s="4">
         <v>1000</v>
@@ -7737,14 +7725,14 @@
     <row r="13" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A13" s="3"/>
       <c r="B13" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C13" s="4">
         <v>500</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F13" s="4">
         <v>52</v>
@@ -7768,7 +7756,7 @@
     <row r="14" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C14" s="4">
         <v>500</v>
@@ -7827,7 +7815,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F16" s="4">
         <v>110</v>
@@ -8105,7 +8093,7 @@
     <row r="28" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A28" s="3"/>
       <c r="B28" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C28" s="4">
         <f>ABS(G4-D25)</f>
@@ -8273,13 +8261,13 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.5">
       <c r="I38" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="J38">
         <v>39</v>
       </c>
       <c r="L38" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M38">
         <f>SUM(J38:J57)</f>
@@ -8288,13 +8276,13 @@
     </row>
     <row r="39" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E39" s="13" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F39">
         <v>500</v>
       </c>
       <c r="I39" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J39">
         <v>100</v>
@@ -8302,13 +8290,13 @@
     </row>
     <row r="40" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E40" s="13" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F40">
         <v>800</v>
       </c>
       <c r="I40" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J40">
         <v>21</v>
@@ -8316,13 +8304,13 @@
     </row>
     <row r="41" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E41" s="13" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F41">
         <v>200</v>
       </c>
       <c r="I41" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J41">
         <v>20</v>
@@ -8330,13 +8318,13 @@
     </row>
     <row r="42" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E42" s="13" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F42">
         <v>2000</v>
       </c>
       <c r="I42" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J42">
         <v>20</v>
@@ -8344,13 +8332,13 @@
     </row>
     <row r="43" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E43" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F43">
         <v>500</v>
       </c>
       <c r="I43" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J43">
         <v>27</v>
@@ -8358,13 +8346,13 @@
     </row>
     <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E44" s="13" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F44">
         <v>100</v>
       </c>
       <c r="I44" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="J44">
         <v>67</v>
@@ -8372,7 +8360,7 @@
     </row>
     <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E45" s="13" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F45">
         <v>67</v>
@@ -8386,13 +8374,13 @@
     </row>
     <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E46" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F46">
         <v>50</v>
       </c>
       <c r="I46" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J46">
         <v>31</v>
@@ -8400,13 +8388,13 @@
     </row>
     <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E47" s="13" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F47">
         <v>70</v>
       </c>
       <c r="I47" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J47">
         <v>32</v>
@@ -8414,13 +8402,13 @@
     </row>
     <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E48" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F48">
         <v>300</v>
       </c>
       <c r="I48" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="J48">
         <v>46</v>
@@ -8428,7 +8416,7 @@
     </row>
     <row r="49" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E49" s="13" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F49">
         <v>100</v>
@@ -8442,7 +8430,7 @@
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.5">
       <c r="I50" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J50">
         <v>357</v>
@@ -8799,7 +8787,7 @@
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F8" s="4">
         <v>1000</v>
@@ -8835,7 +8823,7 @@
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F9" s="4">
         <v>96</v>
@@ -8864,14 +8852,14 @@
     <row r="10" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C10" s="4">
         <v>0</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F10" s="4">
         <v>50</v>
@@ -8900,7 +8888,7 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C11" s="4">
         <v>198</v>
@@ -8934,7 +8922,7 @@
     <row r="12" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C12" s="4">
         <v>1500</v>
@@ -8965,14 +8953,14 @@
     <row r="13" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A13" s="3"/>
       <c r="B13" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C13" s="4">
         <v>250</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F13" s="4">
         <v>52</v>
@@ -8996,7 +8984,7 @@
     <row r="14" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C14" s="4">
         <v>200</v>
@@ -9027,7 +9015,7 @@
     <row r="15" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C15" s="4">
         <f>317+35</f>
@@ -9057,14 +9045,14 @@
     <row r="16" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C16" s="4">
         <v>248</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F16" s="4">
         <v>131</v>
@@ -9086,7 +9074,7 @@
     <row r="17" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A17" s="3"/>
       <c r="B17" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C17" s="4">
         <v>104</v>
@@ -9111,7 +9099,7 @@
     <row r="18" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A18" s="3"/>
       <c r="B18" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C18" s="4">
         <v>89</v>
@@ -9371,7 +9359,7 @@
     <row r="29" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A29" s="3"/>
       <c r="B29" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C29" s="4">
         <f>ABS(G4-D26)</f>
@@ -9539,13 +9527,13 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.5">
       <c r="I39" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="J39">
         <v>39</v>
       </c>
       <c r="L39" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M39">
         <f>SUM(J39:J58)</f>
@@ -9554,13 +9542,13 @@
     </row>
     <row r="40" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E40" s="13" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F40">
         <v>500</v>
       </c>
       <c r="I40" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J40">
         <v>100</v>
@@ -9568,13 +9556,13 @@
     </row>
     <row r="41" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E41" s="13" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F41">
         <v>800</v>
       </c>
       <c r="I41" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J41">
         <v>21</v>
@@ -9582,13 +9570,13 @@
     </row>
     <row r="42" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E42" s="13" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F42">
         <v>200</v>
       </c>
       <c r="I42" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J42">
         <v>20</v>
@@ -9596,13 +9584,13 @@
     </row>
     <row r="43" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E43" s="13" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F43">
         <v>2000</v>
       </c>
       <c r="I43" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J43">
         <v>20</v>
@@ -9610,13 +9598,13 @@
     </row>
     <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E44" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F44">
         <v>500</v>
       </c>
       <c r="I44" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J44">
         <v>27</v>
@@ -9624,13 +9612,13 @@
     </row>
     <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E45" s="13" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F45">
         <v>100</v>
       </c>
       <c r="I45" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="J45">
         <v>67</v>
@@ -9638,7 +9626,7 @@
     </row>
     <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E46" s="13" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F46">
         <v>67</v>
@@ -9652,13 +9640,13 @@
     </row>
     <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E47" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F47">
         <v>50</v>
       </c>
       <c r="I47" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J47">
         <v>31</v>
@@ -9666,13 +9654,13 @@
     </row>
     <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E48" s="13" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F48">
         <v>70</v>
       </c>
       <c r="I48" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J48">
         <v>32</v>
@@ -9680,13 +9668,13 @@
     </row>
     <row r="49" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E49" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F49">
         <v>300</v>
       </c>
       <c r="I49" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="J49">
         <v>46</v>
@@ -9694,7 +9682,7 @@
     </row>
     <row r="50" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E50" s="13" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F50">
         <v>100</v>
@@ -9708,7 +9696,7 @@
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.5">
       <c r="I51" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J51">
         <v>357</v>
@@ -10066,7 +10054,7 @@
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F8" s="4">
         <v>1000</v>
@@ -10102,7 +10090,7 @@
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F9" s="4">
         <v>96</v>
@@ -10131,14 +10119,14 @@
     <row r="10" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C10" s="4">
         <v>0</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F10" s="4">
         <v>50</v>
@@ -10167,7 +10155,7 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C11" s="4">
         <v>39</v>
@@ -10201,7 +10189,7 @@
     <row r="12" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C12" s="4">
         <v>1500</v>
@@ -10232,12 +10220,12 @@
     <row r="13" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A13" s="3"/>
       <c r="B13" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F13" s="4">
         <v>52</v>
@@ -10261,7 +10249,7 @@
     <row r="14" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -10290,7 +10278,7 @@
     <row r="15" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -10317,14 +10305,14 @@
     <row r="16" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C16" s="4">
         <v>247</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F16" s="4">
         <v>131</v>
@@ -10346,7 +10334,7 @@
     <row r="17" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A17" s="3"/>
       <c r="B17" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -10369,7 +10357,7 @@
     <row r="18" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A18" s="3"/>
       <c r="B18" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -10627,7 +10615,7 @@
     <row r="29" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A29" s="3"/>
       <c r="B29" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C29" s="4">
         <f>ABS(G4-D26)</f>
@@ -10795,13 +10783,13 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.5">
       <c r="I39" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="J39">
         <v>39</v>
       </c>
       <c r="L39" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M39">
         <f>SUM(J39:J58)</f>
@@ -10810,13 +10798,13 @@
     </row>
     <row r="40" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E40" s="13" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F40">
         <v>500</v>
       </c>
       <c r="I40" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J40">
         <v>100</v>
@@ -10824,13 +10812,13 @@
     </row>
     <row r="41" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E41" s="13" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F41">
         <v>800</v>
       </c>
       <c r="I41" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J41">
         <v>21</v>
@@ -10838,13 +10826,13 @@
     </row>
     <row r="42" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E42" s="13" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F42">
         <v>200</v>
       </c>
       <c r="I42" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J42">
         <v>20</v>
@@ -10852,13 +10840,13 @@
     </row>
     <row r="43" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E43" s="13" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F43">
         <v>2000</v>
       </c>
       <c r="I43" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J43">
         <v>20</v>
@@ -10866,13 +10854,13 @@
     </row>
     <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E44" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F44">
         <v>500</v>
       </c>
       <c r="I44" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J44">
         <v>27</v>
@@ -10880,13 +10868,13 @@
     </row>
     <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E45" s="13" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F45">
         <v>100</v>
       </c>
       <c r="I45" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="J45">
         <v>67</v>
@@ -10894,7 +10882,7 @@
     </row>
     <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E46" s="13" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F46">
         <v>67</v>
@@ -10908,13 +10896,13 @@
     </row>
     <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E47" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F47">
         <v>50</v>
       </c>
       <c r="I47" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J47">
         <v>31</v>
@@ -10922,13 +10910,13 @@
     </row>
     <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E48" s="13" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F48">
         <v>70</v>
       </c>
       <c r="I48" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J48">
         <v>32</v>
@@ -10936,13 +10924,13 @@
     </row>
     <row r="49" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E49" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F49">
         <v>300</v>
       </c>
       <c r="I49" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="J49">
         <v>46</v>
@@ -10950,7 +10938,7 @@
     </row>
     <row r="50" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E50" s="13" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F50">
         <v>100</v>
@@ -10964,7 +10952,7 @@
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.5">
       <c r="I51" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J51">
         <v>357</v>
@@ -11322,7 +11310,7 @@
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F8" s="4">
         <v>1000</v>
@@ -11358,7 +11346,7 @@
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F9" s="4">
         <v>96</v>
@@ -11387,14 +11375,14 @@
     <row r="10" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C10" s="4">
         <v>200</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F10" s="4">
         <v>50</v>
@@ -11423,7 +11411,7 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C11" s="4">
         <v>39</v>
@@ -11457,7 +11445,7 @@
     <row r="12" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C12" s="4">
         <v>1500</v>
@@ -11488,12 +11476,12 @@
     <row r="13" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A13" s="3"/>
       <c r="B13" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F13" s="4">
         <v>52</v>
@@ -11517,7 +11505,7 @@
     <row r="14" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -11546,7 +11534,7 @@
     <row r="15" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -11573,14 +11561,14 @@
     <row r="16" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C16" s="4">
         <v>247</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F16" s="4">
         <v>131</v>
@@ -11602,7 +11590,7 @@
     <row r="17" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A17" s="3"/>
       <c r="B17" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C17" s="4">
         <v>1500</v>
@@ -11627,7 +11615,7 @@
     <row r="18" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A18" s="3"/>
       <c r="B18" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -11885,7 +11873,7 @@
     <row r="29" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A29" s="3"/>
       <c r="B29" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C29" s="4">
         <f>ABS(G4-D26)</f>
@@ -12053,13 +12041,13 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.5">
       <c r="I39" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="J39">
         <v>39</v>
       </c>
       <c r="L39" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M39">
         <f>SUM(J39:J58)</f>
@@ -12068,13 +12056,13 @@
     </row>
     <row r="40" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E40" s="13" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F40">
         <v>500</v>
       </c>
       <c r="I40" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J40">
         <v>100</v>
@@ -12082,13 +12070,13 @@
     </row>
     <row r="41" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E41" s="13" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F41">
         <v>800</v>
       </c>
       <c r="I41" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J41">
         <v>21</v>
@@ -12096,13 +12084,13 @@
     </row>
     <row r="42" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E42" s="13" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F42">
         <v>200</v>
       </c>
       <c r="I42" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J42">
         <v>20</v>
@@ -12110,13 +12098,13 @@
     </row>
     <row r="43" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E43" s="13" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F43">
         <v>2000</v>
       </c>
       <c r="I43" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J43">
         <v>20</v>
@@ -12124,13 +12112,13 @@
     </row>
     <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E44" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F44">
         <v>500</v>
       </c>
       <c r="I44" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J44">
         <v>27</v>
@@ -12138,13 +12126,13 @@
     </row>
     <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E45" s="13" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F45">
         <v>100</v>
       </c>
       <c r="I45" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="J45">
         <v>67</v>
@@ -12152,7 +12140,7 @@
     </row>
     <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E46" s="13" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F46">
         <v>67</v>
@@ -12166,13 +12154,13 @@
     </row>
     <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E47" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F47">
         <v>50</v>
       </c>
       <c r="I47" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J47">
         <v>31</v>
@@ -12180,13 +12168,13 @@
     </row>
     <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E48" s="13" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F48">
         <v>70</v>
       </c>
       <c r="I48" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J48">
         <v>32</v>
@@ -12194,13 +12182,13 @@
     </row>
     <row r="49" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E49" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F49">
         <v>300</v>
       </c>
       <c r="I49" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="J49">
         <v>46</v>
@@ -12208,7 +12196,7 @@
     </row>
     <row r="50" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E50" s="13" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F50">
         <v>100</v>
@@ -12222,7 +12210,7 @@
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.5">
       <c r="I51" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J51">
         <v>357</v>
@@ -12579,7 +12567,7 @@
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
@@ -12613,7 +12601,7 @@
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F9" s="4">
         <v>96</v>
@@ -12642,14 +12630,14 @@
     <row r="10" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C10" s="4">
         <v>200</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F10" s="4">
         <v>50</v>
@@ -12678,7 +12666,7 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C11" s="4">
         <v>39</v>
@@ -12712,7 +12700,7 @@
     <row r="12" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C12" s="4">
         <v>1500</v>
@@ -12743,14 +12731,14 @@
     <row r="13" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A13" s="3"/>
       <c r="B13" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C13" s="4">
         <v>200</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F13" s="4">
         <v>52</v>
@@ -12774,7 +12762,7 @@
     <row r="14" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -12803,7 +12791,7 @@
     <row r="15" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -12830,14 +12818,14 @@
     <row r="16" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C16" s="4">
         <v>247</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F16" s="4">
         <v>131</v>
@@ -12859,7 +12847,7 @@
     <row r="17" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A17" s="3"/>
       <c r="B17" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -12882,7 +12870,7 @@
     <row r="18" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A18" s="3"/>
       <c r="B18" s="2" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -13140,7 +13128,7 @@
     <row r="29" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A29" s="3"/>
       <c r="B29" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C29" s="4">
         <f>ABS(G4-D26)</f>
@@ -13308,13 +13296,13 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.5">
       <c r="I39" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="J39">
         <v>39</v>
       </c>
       <c r="L39" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M39">
         <f>SUM(J39:J58)</f>
@@ -13323,13 +13311,13 @@
     </row>
     <row r="40" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E40" s="13" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F40">
         <v>500</v>
       </c>
       <c r="I40" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J40">
         <v>100</v>
@@ -13337,13 +13325,13 @@
     </row>
     <row r="41" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E41" s="13" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F41">
         <v>800</v>
       </c>
       <c r="I41" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J41">
         <v>21</v>
@@ -13351,13 +13339,13 @@
     </row>
     <row r="42" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E42" s="13" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F42">
         <v>200</v>
       </c>
       <c r="I42" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J42">
         <v>20</v>
@@ -13365,13 +13353,13 @@
     </row>
     <row r="43" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E43" s="13" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F43">
         <v>2000</v>
       </c>
       <c r="I43" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J43">
         <v>20</v>
@@ -13379,13 +13367,13 @@
     </row>
     <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E44" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F44">
         <v>500</v>
       </c>
       <c r="I44" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J44">
         <v>27</v>
@@ -13393,13 +13381,13 @@
     </row>
     <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E45" s="13" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F45">
         <v>100</v>
       </c>
       <c r="I45" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="J45">
         <v>67</v>
@@ -13407,7 +13395,7 @@
     </row>
     <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E46" s="13" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F46">
         <v>67</v>
@@ -13421,13 +13409,13 @@
     </row>
     <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E47" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F47">
         <v>50</v>
       </c>
       <c r="I47" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J47">
         <v>31</v>
@@ -13435,13 +13423,13 @@
     </row>
     <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E48" s="13" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F48">
         <v>70</v>
       </c>
       <c r="I48" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J48">
         <v>32</v>
@@ -13449,13 +13437,13 @@
     </row>
     <row r="49" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E49" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F49">
         <v>300</v>
       </c>
       <c r="I49" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="J49">
         <v>46</v>
@@ -13463,7 +13451,7 @@
     </row>
     <row r="50" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E50" s="13" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F50">
         <v>100</v>
@@ -13477,7 +13465,7 @@
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.5">
       <c r="I51" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J51">
         <v>357</v>
@@ -13834,7 +13822,7 @@
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
@@ -13868,7 +13856,7 @@
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F9" s="4">
         <v>96</v>
@@ -13897,14 +13885,14 @@
     <row r="10" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C10" s="4">
         <v>150</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F10" s="4">
         <v>50</v>
@@ -13933,7 +13921,7 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C11" s="4">
         <v>39</v>
@@ -13967,7 +13955,7 @@
     <row r="12" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C12" s="4">
         <v>1000</v>
@@ -13998,12 +13986,12 @@
     <row r="13" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A13" s="3"/>
       <c r="B13" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F13" s="4">
         <v>52</v>
@@ -14027,7 +14015,7 @@
     <row r="14" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C14" s="4">
         <v>224</v>
@@ -14083,14 +14071,14 @@
     <row r="16" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C16" s="4">
         <v>247</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F16" s="4">
         <v>131</v>
@@ -14389,7 +14377,7 @@
     <row r="29" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A29" s="3"/>
       <c r="B29" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C29" s="4">
         <f>ABS(G4-D26)</f>
@@ -14557,13 +14545,13 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.5">
       <c r="I39" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="J39">
         <v>39</v>
       </c>
       <c r="L39" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M39">
         <f>SUM(J39:J58)</f>
@@ -14572,13 +14560,13 @@
     </row>
     <row r="40" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E40" s="13" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F40">
         <v>500</v>
       </c>
       <c r="I40" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J40">
         <v>100</v>
@@ -14586,13 +14574,13 @@
     </row>
     <row r="41" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E41" s="13" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F41">
         <v>800</v>
       </c>
       <c r="I41" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J41">
         <v>21</v>
@@ -14600,13 +14588,13 @@
     </row>
     <row r="42" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E42" s="13" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F42">
         <v>200</v>
       </c>
       <c r="I42" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J42">
         <v>20</v>
@@ -14614,13 +14602,13 @@
     </row>
     <row r="43" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E43" s="13" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F43">
         <v>2000</v>
       </c>
       <c r="I43" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J43">
         <v>20</v>
@@ -14628,13 +14616,13 @@
     </row>
     <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E44" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F44">
         <v>500</v>
       </c>
       <c r="I44" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J44">
         <v>27</v>
@@ -14642,13 +14630,13 @@
     </row>
     <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E45" s="13" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F45">
         <v>100</v>
       </c>
       <c r="I45" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="J45">
         <v>67</v>
@@ -14656,7 +14644,7 @@
     </row>
     <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E46" s="13" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F46">
         <v>67</v>
@@ -14670,13 +14658,13 @@
     </row>
     <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E47" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F47">
         <v>50</v>
       </c>
       <c r="I47" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J47">
         <v>31</v>
@@ -14684,13 +14672,13 @@
     </row>
     <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E48" s="13" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F48">
         <v>70</v>
       </c>
       <c r="I48" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J48">
         <v>32</v>
@@ -14698,13 +14686,13 @@
     </row>
     <row r="49" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E49" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F49">
         <v>300</v>
       </c>
       <c r="I49" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="J49">
         <v>46</v>
@@ -14712,7 +14700,7 @@
     </row>
     <row r="50" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E50" s="13" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F50">
         <v>100</v>
@@ -14726,7 +14714,7 @@
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.5">
       <c r="I51" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J51">
         <v>357</v>
@@ -15193,7 +15181,7 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C11" s="4">
         <v>1250</v>
@@ -16097,7 +16085,7 @@
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
@@ -16131,7 +16119,7 @@
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F9" s="4">
         <v>96</v>
@@ -16160,14 +16148,14 @@
     <row r="10" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C10" s="4">
         <v>0</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F10" s="4">
         <v>50</v>
@@ -16196,7 +16184,7 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C11" s="4">
         <v>39</v>
@@ -16230,7 +16218,7 @@
     <row r="12" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -16259,12 +16247,12 @@
     <row r="13" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A13" s="3"/>
       <c r="B13" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F13" s="4">
         <v>52</v>
@@ -16288,7 +16276,7 @@
     <row r="14" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -16317,7 +16305,7 @@
     <row r="15" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -16344,14 +16332,14 @@
     <row r="16" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C16" s="4">
         <v>247</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F16" s="4">
         <v>131</v>
@@ -16373,7 +16361,7 @@
     <row r="17" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A17" s="3"/>
       <c r="B17" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -16396,7 +16384,7 @@
     <row r="18" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A18" s="3"/>
       <c r="B18" s="2" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -16654,7 +16642,7 @@
     <row r="29" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A29" s="3"/>
       <c r="B29" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C29" s="4">
         <f>ABS(G4-D26)</f>
@@ -16822,13 +16810,13 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.5">
       <c r="I39" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="J39">
         <v>39</v>
       </c>
       <c r="L39" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M39">
         <f>SUM(J39:J58)</f>
@@ -16837,13 +16825,13 @@
     </row>
     <row r="40" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E40" s="13" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F40">
         <v>500</v>
       </c>
       <c r="I40" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J40">
         <v>100</v>
@@ -16851,13 +16839,13 @@
     </row>
     <row r="41" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E41" s="13" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F41">
         <v>800</v>
       </c>
       <c r="I41" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J41">
         <v>21</v>
@@ -16865,13 +16853,13 @@
     </row>
     <row r="42" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E42" s="13" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F42">
         <v>200</v>
       </c>
       <c r="I42" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J42">
         <v>20</v>
@@ -16879,13 +16867,13 @@
     </row>
     <row r="43" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E43" s="13" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F43">
         <v>2000</v>
       </c>
       <c r="I43" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J43">
         <v>20</v>
@@ -16893,13 +16881,13 @@
     </row>
     <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E44" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F44">
         <v>500</v>
       </c>
       <c r="I44" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J44">
         <v>27</v>
@@ -16907,13 +16895,13 @@
     </row>
     <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E45" s="13" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F45">
         <v>100</v>
       </c>
       <c r="I45" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="J45">
         <v>67</v>
@@ -16921,7 +16909,7 @@
     </row>
     <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E46" s="13" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F46">
         <v>67</v>
@@ -16935,13 +16923,13 @@
     </row>
     <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E47" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F47">
         <v>50</v>
       </c>
       <c r="I47" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J47">
         <v>31</v>
@@ -16949,13 +16937,13 @@
     </row>
     <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E48" s="13" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F48">
         <v>70</v>
       </c>
       <c r="I48" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J48">
         <v>32</v>
@@ -16963,13 +16951,13 @@
     </row>
     <row r="49" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E49" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F49">
         <v>300</v>
       </c>
       <c r="I49" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="J49">
         <v>46</v>
@@ -16977,7 +16965,7 @@
     </row>
     <row r="50" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E50" s="13" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F50">
         <v>100</v>
@@ -16991,7 +16979,7 @@
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.5">
       <c r="I51" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J51">
         <v>357</v>
@@ -17148,7 +17136,7 @@
   <cols>
     <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.125" customWidth="1"/>
-    <col min="8" max="8" width="15.1875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.25" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.625" customWidth="1"/>
     <col min="11" max="11" width="8.125" customWidth="1"/>
     <col min="13" max="13" width="18.125" customWidth="1"/>
@@ -17348,7 +17336,7 @@
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
@@ -17382,7 +17370,7 @@
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F9" s="4">
         <v>96</v>
@@ -17411,14 +17399,14 @@
     <row r="10" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C10" s="4">
         <v>200</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F10" s="4">
         <v>50</v>
@@ -17447,7 +17435,7 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C11" s="4">
         <v>39</v>
@@ -17481,7 +17469,7 @@
     <row r="12" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C12" s="4">
         <v>2000</v>
@@ -17512,14 +17500,14 @@
     <row r="13" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A13" s="3"/>
       <c r="B13" s="2" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C13" s="4">
         <v>100</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F13" s="4">
         <v>52</v>
@@ -17543,7 +17531,7 @@
     <row r="14" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C14" s="4">
         <v>100</v>
@@ -17574,7 +17562,7 @@
     <row r="15" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C15" s="4">
         <v>280</v>
@@ -17603,14 +17591,14 @@
     <row r="16" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C16" s="4">
         <v>400</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F16" s="4">
         <v>131</v>
@@ -17632,7 +17620,7 @@
     <row r="17" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A17" s="3"/>
       <c r="B17" s="2" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C17" s="4">
         <v>300</v>
@@ -17913,7 +17901,7 @@
     <row r="29" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A29" s="3"/>
       <c r="B29" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C29" s="4">
         <f>ABS(G4-D26)</f>
@@ -18081,13 +18069,13 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.5">
       <c r="I39" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="J39">
         <v>39</v>
       </c>
       <c r="L39" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M39">
         <f>SUM(J39:J58)</f>
@@ -18096,13 +18084,13 @@
     </row>
     <row r="40" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E40" s="13" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F40">
         <v>500</v>
       </c>
       <c r="I40" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J40">
         <v>100</v>
@@ -18110,13 +18098,13 @@
     </row>
     <row r="41" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E41" s="13" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F41">
         <v>800</v>
       </c>
       <c r="I41" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J41">
         <v>21</v>
@@ -18124,13 +18112,13 @@
     </row>
     <row r="42" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E42" s="13" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F42">
         <v>200</v>
       </c>
       <c r="I42" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J42">
         <v>20</v>
@@ -18138,13 +18126,13 @@
     </row>
     <row r="43" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E43" s="13" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F43">
         <v>2000</v>
       </c>
       <c r="I43" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J43">
         <v>20</v>
@@ -18152,13 +18140,13 @@
     </row>
     <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E44" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F44">
         <v>500</v>
       </c>
       <c r="I44" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J44">
         <v>27</v>
@@ -18166,13 +18154,13 @@
     </row>
     <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E45" s="13" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F45">
         <v>100</v>
       </c>
       <c r="I45" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="J45">
         <v>67</v>
@@ -18180,7 +18168,7 @@
     </row>
     <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E46" s="13" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F46">
         <v>67</v>
@@ -18194,13 +18182,13 @@
     </row>
     <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E47" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F47">
         <v>50</v>
       </c>
       <c r="I47" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J47">
         <v>31</v>
@@ -18208,13 +18196,13 @@
     </row>
     <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E48" s="13" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F48">
         <v>70</v>
       </c>
       <c r="I48" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J48">
         <v>32</v>
@@ -18222,13 +18210,13 @@
     </row>
     <row r="49" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E49" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F49">
         <v>300</v>
       </c>
       <c r="I49" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="J49">
         <v>46</v>
@@ -18236,7 +18224,7 @@
     </row>
     <row r="50" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E50" s="13" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F50">
         <v>100</v>
@@ -18250,7 +18238,7 @@
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.5">
       <c r="I51" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J51">
         <v>357</v>
@@ -18407,7 +18395,7 @@
   <cols>
     <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.125" customWidth="1"/>
-    <col min="8" max="8" width="15.1875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.25" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.625" customWidth="1"/>
     <col min="11" max="11" width="8.125" customWidth="1"/>
     <col min="13" max="13" width="18.125" customWidth="1"/>
@@ -18607,7 +18595,7 @@
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F8" s="4">
         <v>1000</v>
@@ -18643,7 +18631,7 @@
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F9" s="4">
         <v>96</v>
@@ -18672,12 +18660,12 @@
     <row r="10" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F10" s="4">
         <v>50</v>
@@ -18706,7 +18694,7 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C11" s="4">
         <v>39</v>
@@ -18740,7 +18728,7 @@
     <row r="12" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -18769,12 +18757,12 @@
     <row r="13" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A13" s="3"/>
       <c r="B13" s="2" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F13" s="4">
         <v>52</v>
@@ -18798,7 +18786,7 @@
     <row r="14" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -18827,7 +18815,7 @@
     <row r="15" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -18854,12 +18842,12 @@
     <row r="16" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F16" s="4">
         <v>0</v>
@@ -18881,7 +18869,7 @@
     <row r="17" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A17" s="3"/>
       <c r="B17" s="2" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -19164,7 +19152,7 @@
     <row r="29" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A29" s="3"/>
       <c r="B29" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C29" s="4">
         <f>ABS(G4-D26)</f>
@@ -19332,13 +19320,13 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.5">
       <c r="I39" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="J39">
         <v>39</v>
       </c>
       <c r="L39" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M39">
         <f>SUM(J39:J58)</f>
@@ -19347,13 +19335,13 @@
     </row>
     <row r="40" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E40" s="13" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F40">
         <v>500</v>
       </c>
       <c r="I40" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J40">
         <v>100</v>
@@ -19361,13 +19349,13 @@
     </row>
     <row r="41" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E41" s="13" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F41">
         <v>800</v>
       </c>
       <c r="I41" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J41">
         <v>21</v>
@@ -19375,13 +19363,13 @@
     </row>
     <row r="42" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E42" s="13" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F42">
         <v>200</v>
       </c>
       <c r="I42" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J42">
         <v>20</v>
@@ -19389,13 +19377,13 @@
     </row>
     <row r="43" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E43" s="13" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F43">
         <v>2000</v>
       </c>
       <c r="I43" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J43">
         <v>20</v>
@@ -19403,13 +19391,13 @@
     </row>
     <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E44" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F44">
         <v>500</v>
       </c>
       <c r="I44" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J44">
         <v>27</v>
@@ -19417,13 +19405,13 @@
     </row>
     <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E45" s="13" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F45">
         <v>100</v>
       </c>
       <c r="I45" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="J45">
         <v>67</v>
@@ -19431,7 +19419,7 @@
     </row>
     <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E46" s="13" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F46">
         <v>67</v>
@@ -19445,13 +19433,13 @@
     </row>
     <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E47" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F47">
         <v>50</v>
       </c>
       <c r="I47" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J47">
         <v>31</v>
@@ -19459,13 +19447,13 @@
     </row>
     <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E48" s="13" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F48">
         <v>70</v>
       </c>
       <c r="I48" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J48">
         <v>32</v>
@@ -19473,13 +19461,13 @@
     </row>
     <row r="49" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E49" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F49">
         <v>300</v>
       </c>
       <c r="I49" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="J49">
         <v>46</v>
@@ -19487,7 +19475,7 @@
     </row>
     <row r="50" spans="2:10" ht="16.5" x14ac:dyDescent="0.6">
       <c r="E50" s="13" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F50">
         <v>100</v>
@@ -19501,7 +19489,7 @@
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.5">
       <c r="I51" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J51">
         <v>357</v>
@@ -19654,224 +19642,75 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B974066F-70AB-4CE0-9413-18C0CA619219}">
   <sheetPr codeName="Feuil20"/>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>57</v>
       </c>
       <c r="B1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.5">
+      <c r="C1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A2">
         <v>11500</v>
       </c>
       <c r="B2">
         <v>10000</v>
       </c>
-      <c r="G2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="G3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H3">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="G4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="G5" t="s">
-        <v>67</v>
-      </c>
-      <c r="H5">
-        <v>3000</v>
-      </c>
-      <c r="J5">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.5">
+      <c r="C2">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.5">
+      <c r="J4" t="s">
+        <v>314</v>
+      </c>
+      <c r="K4">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6">
         <f>SUM(A2:G2)</f>
-        <v>21500</v>
-      </c>
-      <c r="G6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6">
-        <v>5000</v>
+        <v>26500</v>
       </c>
       <c r="J6">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="G7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H7">
-        <v>4000</v>
-      </c>
-      <c r="J7">
-        <v>163</v>
-      </c>
-      <c r="L7" t="s">
-        <v>225</v>
-      </c>
-      <c r="M7">
-        <v>500</v>
-      </c>
-      <c r="O7">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="G8" t="s">
-        <v>71</v>
-      </c>
-      <c r="H8">
-        <v>4000</v>
-      </c>
-      <c r="J8">
-        <v>400</v>
-      </c>
-      <c r="L8" t="s">
-        <v>81</v>
-      </c>
-      <c r="M8">
-        <v>500</v>
-      </c>
-      <c r="O8">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="G9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H9">
-        <v>3000</v>
-      </c>
-      <c r="J9">
-        <v>300</v>
-      </c>
-      <c r="L9" t="s">
-        <v>87</v>
-      </c>
-      <c r="M9">
-        <v>500</v>
-      </c>
-      <c r="O9">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="G10" t="s">
-        <v>81</v>
-      </c>
-      <c r="H10">
-        <v>3000</v>
-      </c>
-      <c r="I10" t="s">
-        <v>70</v>
-      </c>
-      <c r="J10">
-        <v>1300</v>
-      </c>
-      <c r="L10" t="s">
-        <v>88</v>
-      </c>
-      <c r="M10">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="G11" t="s">
-        <v>87</v>
-      </c>
-      <c r="H11">
-        <v>3000</v>
-      </c>
-      <c r="J11">
         <v>1000</v>
       </c>
-      <c r="L11" t="s">
-        <v>69</v>
-      </c>
-      <c r="M11">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="J12">
-        <v>300</v>
-      </c>
-      <c r="L12" t="s">
-        <v>259</v>
-      </c>
-      <c r="M12">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="L13" t="s">
-        <v>68</v>
-      </c>
-      <c r="M13">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.5">
+      <c r="K6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.5">
       <c r="J14">
         <f>SUM(J5:J12)</f>
-        <v>5116</v>
-      </c>
-      <c r="L14" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="L15" t="s">
-        <v>67</v>
-      </c>
-      <c r="M15">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.5">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.5">
       <c r="I16" t="s">
         <v>21</v>
       </c>
       <c r="J16">
-        <f>J14-M22</f>
-        <v>1116</v>
-      </c>
-      <c r="L16" t="s">
-        <v>298</v>
+        <f>K4-J14</f>
+        <v>4000</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.5">
       <c r="O17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.5">
@@ -19880,7 +19719,7 @@
       </c>
       <c r="H19">
         <f>SUM(H3:H17)</f>
-        <v>32000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.5">
@@ -19888,19 +19727,13 @@
         <v>21</v>
       </c>
       <c r="B20">
-        <f>B6-F41</f>
-        <v>12500</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="M22">
-        <f>SUM(M7:M20)</f>
-        <v>4000</v>
+        <f>B6-F47</f>
+        <v>15600</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A24" s="9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -19919,20 +19752,20 @@
     <row r="26" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A26" s="10"/>
       <c r="B26" s="10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="10" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="F26" s="9"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A27" s="9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B27" s="9">
         <v>500</v>
@@ -19944,7 +19777,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A28" s="9" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B28" s="9"/>
       <c r="C28" s="9">
@@ -19956,7 +19789,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A29" s="9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B29" s="9">
         <v>500</v>
@@ -19968,7 +19801,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A30" s="9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B30" s="9"/>
       <c r="C30" s="9">
@@ -19980,7 +19813,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A31" s="9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B31" s="9">
         <v>500</v>
@@ -19992,7 +19825,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A32" s="9" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B32" s="9">
         <v>400</v>
@@ -20006,7 +19839,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A33" s="9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B33" s="9">
         <v>600</v>
@@ -20018,7 +19851,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A34" s="9" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B34" s="9">
         <v>500</v>
@@ -20032,7 +19865,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A35" s="9" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B35" s="9">
         <v>500</v>
@@ -20044,7 +19877,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A36" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B36" s="9">
         <v>500</v>
@@ -20058,7 +19891,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A37" s="9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B37" s="9">
         <v>0</v>
@@ -20070,7 +19903,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A38" s="9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B38" s="9">
         <v>500</v>
@@ -20081,15 +19914,25 @@
       <c r="F38" s="9"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.5">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
+      <c r="A39" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" s="9">
+        <v>400</v>
+      </c>
+      <c r="C39" s="9">
+        <v>1000</v>
+      </c>
+      <c r="D39" s="9">
+        <v>500</v>
+      </c>
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.5">
-      <c r="A40" s="9"/>
+      <c r="A40" s="9" t="s">
+        <v>83</v>
+      </c>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
@@ -20097,28 +19940,80 @@
       <c r="F40" s="9"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.5">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A42" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A44" s="9"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A45" s="9"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A46" s="9"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A47" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B41" s="10">
-        <f>SUM(B27:B39)</f>
-        <v>4500</v>
-      </c>
-      <c r="C41" s="10">
-        <f>SUM(C27:C39)</f>
-        <v>4500</v>
-      </c>
-      <c r="D41" s="10">
-        <f>SUM(D27:D39)</f>
+      <c r="B47" s="10">
+        <f>SUM(B27:B45)</f>
+        <v>4900</v>
+      </c>
+      <c r="C47" s="10">
+        <f>SUM(C27:C45)</f>
+        <v>5500</v>
+      </c>
+      <c r="D47" s="10">
+        <f>SUM(D27:D45)</f>
+        <v>500</v>
+      </c>
+      <c r="E47" s="10">
+        <f>SUM(E27:E45)</f>
         <v>0</v>
       </c>
-      <c r="E41" s="10">
-        <f>SUM(E27:E39)</f>
-        <v>0</v>
-      </c>
-      <c r="F41" s="10">
-        <f>SUM(B41:E41)</f>
-        <v>9000</v>
+      <c r="F47" s="10">
+        <f>SUM(B47:E47)</f>
+        <v>10900</v>
       </c>
     </row>
   </sheetData>
@@ -20133,42 +20028,42 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.6875" customWidth="1"/>
+    <col min="4" max="4" width="18.75" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.1875" customWidth="1"/>
+    <col min="6" max="6" width="22.25" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.5">
       <c r="C1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1" t="s">
         <v>126</v>
       </c>
-      <c r="F1" t="s">
-        <v>127</v>
-      </c>
-      <c r="G1" t="s">
-        <v>130</v>
-      </c>
       <c r="I1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C2" s="12">
         <v>9456</v>
@@ -20192,10 +20087,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C3" s="1">
         <v>0</v>
@@ -20219,7 +20114,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C5">
         <f>C2+C3</f>
@@ -20248,10 +20143,10 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C9" s="12">
         <v>9600</v>
@@ -20275,10 +20170,10 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B10" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C10" s="1">
         <f>1300+3200+600</f>
@@ -20303,7 +20198,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C12">
         <f>C9+C10</f>
@@ -20332,10 +20227,10 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B15" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C15" s="12">
         <v>12000</v>
@@ -20359,10 +20254,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B16" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C16" s="1">
         <f>3000+3750+3375</f>
@@ -20387,7 +20282,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C18">
         <f>C15+C16</f>
@@ -20416,10 +20311,10 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C21" s="12">
         <v>0</v>
@@ -20443,10 +20338,10 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B22" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C22" s="1">
         <v>19000</v>
@@ -20470,7 +20365,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C24">
         <f>C21+C22</f>
@@ -20499,10 +20394,10 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A27" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C27" s="12">
         <v>0</v>
@@ -20526,10 +20421,10 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A28" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B28" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C28" s="1">
         <v>8150</v>
@@ -20552,7 +20447,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A30" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C30">
         <f>C27+C28</f>
@@ -20577,7 +20472,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A33" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B33" s="15">
         <v>45658</v>
@@ -20604,10 +20499,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A34" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B34" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C34" s="1">
         <v>8050</v>
@@ -20630,7 +20525,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A36" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C36">
         <f>C33+C34</f>
@@ -20668,23 +20563,23 @@
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.6875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.75" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.5">
@@ -20692,13 +20587,13 @@
         <v>4700000</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E2">
         <v>500000</v>
       </c>
       <c r="H2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J2">
         <v>418000</v>
@@ -20710,13 +20605,13 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.5">
       <c r="D3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E3">
         <v>500000</v>
       </c>
       <c r="H3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="J3">
         <v>432000</v>
@@ -20724,13 +20619,13 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.5">
       <c r="D4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E4">
         <v>300000</v>
       </c>
       <c r="H4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="J4">
         <v>100000</v>
@@ -20738,13 +20633,13 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.5">
       <c r="D5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E5">
         <v>16000</v>
       </c>
       <c r="H5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="J5">
         <v>25000</v>
@@ -20752,36 +20647,36 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.5">
       <c r="D6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E6">
         <v>800000</v>
       </c>
       <c r="H6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="J6">
         <v>25000</v>
       </c>
       <c r="N6" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.5">
       <c r="D7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E7">
         <v>1000000</v>
       </c>
       <c r="H7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J7">
         <v>60000</v>
       </c>
       <c r="N7" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="O7">
         <v>1000</v>
@@ -20789,19 +20684,19 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.5">
       <c r="D8" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E8">
         <v>600000</v>
       </c>
       <c r="H8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J8">
         <v>35000</v>
       </c>
       <c r="N8" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="O8">
         <v>1000</v>
@@ -20809,19 +20704,19 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.5">
       <c r="D9" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E9">
         <v>600000</v>
       </c>
       <c r="H9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J9">
         <v>28000</v>
       </c>
       <c r="N9" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="O9">
         <v>4000</v>
@@ -20829,13 +20724,13 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.5">
       <c r="D10" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E10">
         <v>113000</v>
       </c>
       <c r="H10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="J10">
         <v>20000</v>
@@ -20843,13 +20738,13 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.5">
       <c r="D11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E11">
         <v>500000</v>
       </c>
       <c r="H11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J11">
         <v>32000</v>
@@ -20857,13 +20752,13 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.5">
       <c r="D12" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E12">
         <v>466000</v>
       </c>
       <c r="H12" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="J12">
         <v>125000</v>
@@ -20871,13 +20766,13 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.5">
       <c r="D13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E13">
         <v>450000</v>
       </c>
       <c r="H13" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="J13">
         <v>16000</v>
@@ -20885,13 +20780,13 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.5">
       <c r="D14" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E14">
         <v>1000000</v>
       </c>
       <c r="H14" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="J14">
         <v>500000</v>
@@ -20899,13 +20794,13 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.5">
       <c r="D15" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E15">
         <v>1000000</v>
       </c>
       <c r="H15" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J15">
         <v>400000</v>
@@ -20913,13 +20808,13 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.5">
       <c r="D16" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E16">
         <v>500000</v>
       </c>
       <c r="H16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J16">
         <v>460000</v>
@@ -20927,13 +20822,13 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.5">
       <c r="D17" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E17">
         <v>850000</v>
       </c>
       <c r="H17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J17">
         <v>45000</v>
@@ -20941,7 +20836,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.5">
       <c r="D18" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E18">
         <v>250000</v>
@@ -20949,7 +20844,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.5">
       <c r="D19" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E19">
         <v>125000</v>
@@ -20957,13 +20852,13 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.5">
       <c r="H23" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="J23">
         <v>14000</v>
       </c>
       <c r="N23" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="O23">
         <f>SUM(O7:O19)</f>
@@ -20999,7 +20894,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.5">
       <c r="H26" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="J26">
         <v>113000</v>
@@ -21007,7 +20902,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.5">
       <c r="H27" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J27">
         <v>300000</v>
@@ -21015,7 +20910,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.5">
       <c r="H28" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J28">
         <v>550500</v>
@@ -21023,7 +20918,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B31">
         <f>A2-E25</f>
@@ -21032,7 +20927,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A32" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B32">
         <f>A2-L2</f>
@@ -21041,22 +20936,22 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A37" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E37" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A38" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B38">
         <f>9*19</f>
         <v>171</v>
       </c>
       <c r="E38" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F38">
         <v>304000</v>
@@ -21064,14 +20959,14 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A39" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B39">
         <f>19*6</f>
         <v>114</v>
       </c>
       <c r="E39" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F39">
         <v>276000</v>
@@ -21079,26 +20974,26 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A40" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B40">
         <f>6*4</f>
         <v>24</v>
       </c>
       <c r="E40" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F40">
         <v>268000</v>
       </c>
       <c r="H40" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I40">
         <v>304000</v>
       </c>
       <c r="K40" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L40">
         <f>3800*40</f>
@@ -21107,26 +21002,26 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A41" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B41">
         <f>18*5</f>
         <v>90</v>
       </c>
       <c r="E41" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F41">
         <v>780000</v>
       </c>
       <c r="H41" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I41">
         <v>276000</v>
       </c>
       <c r="K41" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="L41">
         <v>30000</v>
@@ -21134,21 +21029,21 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A42" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B42">
         <f>15*8</f>
         <v>120</v>
       </c>
       <c r="E42" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F42">
         <f>76000*5</f>
         <v>380000</v>
       </c>
       <c r="H42" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="I42">
         <v>120000</v>
@@ -21162,27 +21057,27 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A43" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B43">
         <f>19*4</f>
         <v>76</v>
       </c>
       <c r="E43" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F43">
         <v>7000</v>
       </c>
       <c r="H43" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="I43">
         <f>30*3800</f>
         <v>114000</v>
       </c>
       <c r="K43" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L43">
         <v>500000</v>
@@ -21190,19 +21085,19 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A44" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B44">
         <v>20</v>
       </c>
       <c r="E44" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F44">
         <v>30000</v>
       </c>
       <c r="H44" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I44">
         <f>40*3800</f>
@@ -21211,7 +21106,7 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.5">
       <c r="E45" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F45">
         <v>120000</v>
@@ -21219,7 +21114,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.5">
       <c r="E46" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F46">
         <v>1300000</v>
@@ -21227,7 +21122,7 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.5">
       <c r="H47" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I47">
         <f>SUM(I40:I44)</f>
@@ -21252,7 +21147,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.5">
       <c r="M52" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="N52">
         <f>2000*655</f>
@@ -21269,7 +21164,7 @@
       <c r="G53" s="14"/>
       <c r="H53" s="14"/>
       <c r="L53" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="M53">
         <v>200000</v>
@@ -21279,7 +21174,7 @@
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -21287,7 +21182,7 @@
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="L54" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="M54">
         <v>200000</v>
@@ -21295,10 +21190,10 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.5">
       <c r="B55" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C55" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="M55">
         <v>400000</v>
@@ -21306,7 +21201,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.5">
       <c r="A56" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B56">
         <v>300000</v>
@@ -21320,7 +21215,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.5">
       <c r="A57" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B57">
         <v>400000</v>
@@ -21334,7 +21229,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B58">
         <v>2200000</v>
@@ -21352,7 +21247,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.5">
       <c r="A59" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B59">
         <v>450000</v>
@@ -21375,18 +21270,18 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.5">
       <c r="B66" t="s">
+        <v>239</v>
+      </c>
+      <c r="C66" t="s">
+        <v>241</v>
+      </c>
+      <c r="D66" t="s">
         <v>243</v>
-      </c>
-      <c r="C66" t="s">
-        <v>245</v>
-      </c>
-      <c r="D66" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A67" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B67" s="1">
         <f>364000+9000+56500</f>
@@ -21399,7 +21294,7 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A68" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B68" s="1">
         <v>396250</v>
@@ -21410,7 +21305,7 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A69" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B69" s="1">
         <v>350000</v>
@@ -21421,7 +21316,7 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A70" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B70" s="1">
         <v>400000</v>
@@ -21432,7 +21327,7 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A71" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B71" s="1">
         <v>260000</v>
@@ -21441,18 +21336,18 @@
         <v>260000</v>
       </c>
       <c r="K71" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="N71" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="Q71" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A72" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B72" s="1">
         <v>200000</v>
@@ -21461,21 +21356,21 @@
         <v>200000</v>
       </c>
       <c r="K72" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="L72">
         <f>3.4*3.9</f>
         <v>13.26</v>
       </c>
       <c r="N72" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="O72">
         <f>1.66*1.66</f>
         <v>2.7555999999999998</v>
       </c>
       <c r="Q72" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="R72">
         <f>(1.6*3)*4</f>
@@ -21484,7 +21379,7 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A73" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B73" s="1">
         <f>450000+140000</f>
@@ -21495,21 +21390,21 @@
         <v>590000</v>
       </c>
       <c r="K73" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="L73">
         <f>3.4*3.9</f>
         <v>13.26</v>
       </c>
       <c r="N73" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="O73">
         <f>1.66*1.8</f>
         <v>2.988</v>
       </c>
       <c r="Q73" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="R73">
         <f>(1.6*3)*2+(1.8*3)*2</f>
@@ -21518,7 +21413,7 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A74" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B74" s="1">
         <v>2100000</v>
@@ -21528,21 +21423,21 @@
         <v>2000000</v>
       </c>
       <c r="H74" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I74">
         <f>3*5</f>
         <v>15</v>
       </c>
       <c r="K74" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="L74">
         <f>5.56*3.9</f>
         <v>21.683999999999997</v>
       </c>
       <c r="Q74" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="R74">
         <f>(1.4*3)+(3.9*3)*2</f>
@@ -21551,7 +21446,7 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A75" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B75" s="1">
         <f>675000+120000</f>
@@ -21562,26 +21457,26 @@
         <v>453000</v>
       </c>
       <c r="H75" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="I75">
         <f>0.95*4.1</f>
         <v>3.8949999999999996</v>
       </c>
       <c r="K75" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="L75">
         <f>1.4*16</f>
         <v>22.4</v>
       </c>
       <c r="Q75" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A76" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B76" s="1">
         <v>675000</v>
@@ -21591,24 +21486,24 @@
         <v>675000</v>
       </c>
       <c r="K76" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="L76">
         <v>6</v>
       </c>
       <c r="N76" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="Q76" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A77" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B77" s="1">
         <v>650000</v>
@@ -21618,7 +21513,7 @@
         <v>651000</v>
       </c>
       <c r="K77" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="L77">
         <v>8</v>
@@ -21626,7 +21521,7 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A78" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B78" s="1">
         <v>1500000</v>
@@ -21642,7 +21537,7 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A79" s="1" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B79" s="1">
         <v>450000</v>
@@ -21656,10 +21551,10 @@
         <v>360000</v>
       </c>
       <c r="E79" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="H79" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="I79">
         <v>10</v>
@@ -21667,7 +21562,7 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A80" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B80" s="1">
         <v>155000</v>
@@ -21677,7 +21572,7 @@
         <v>155000</v>
       </c>
       <c r="H80" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="I80">
         <v>17</v>
@@ -21685,7 +21580,7 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A81" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B81" s="1">
         <v>480000</v>
@@ -21697,7 +21592,7 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A82" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B82" s="1">
         <v>292000</v>
@@ -21709,7 +21604,7 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A83" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B83">
         <v>200000</v>
@@ -21721,7 +21616,7 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A84" s="1" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B84" s="1">
         <v>580000</v>
@@ -21732,7 +21627,7 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A85" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B85" s="1">
         <v>500000</v>
@@ -21743,7 +21638,7 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A86" s="1" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B86" s="1">
         <v>200000</v>
@@ -21754,7 +21649,7 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A87" s="1" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B87" s="1">
         <v>250000</v>
@@ -21765,7 +21660,7 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A88" s="1" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B88" s="1">
         <v>100000</v>
@@ -21776,7 +21671,7 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A89" s="1" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B89" s="1">
         <v>360000</v>
@@ -21787,7 +21682,7 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A90" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B90" s="1">
         <v>350000</v>
@@ -21798,7 +21693,7 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A91" s="1" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B91" s="1">
         <v>200000</v>
@@ -21823,7 +21718,7 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A94" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B94">
         <f>B93/655</f>
@@ -21836,7 +21731,7 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.5">
       <c r="H95" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="I95">
         <f>SUM(I74:I80)</f>
@@ -21877,29 +21772,29 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A97" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B97">
         <f>2000+4000+3000+800+553+1950+4000+1000+1300</f>
         <v>18603</v>
       </c>
       <c r="C97" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D97" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E97" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="F97" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G97" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="H97" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.5">
@@ -21949,7 +21844,7 @@
   <sheetData>
     <row r="3" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -21960,17 +21855,17 @@
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C5" s="1">
         <f>75000*6</f>
@@ -21984,7 +21879,7 @@
     <row r="6" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C6" s="1">
         <v>432000</v>
@@ -21997,7 +21892,7 @@
     <row r="7" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -22008,7 +21903,7 @@
     <row r="8" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C8" s="1">
         <v>60000</v>
@@ -22021,7 +21916,7 @@
     <row r="9" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C9" s="1">
         <v>180000</v>
@@ -22041,7 +21936,7 @@
     <row r="11" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C11" s="1">
         <f>SUM(C5:C9)</f>
@@ -22059,10 +21954,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C14">
         <v>2000000</v>
@@ -22073,7 +21968,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.5">
       <c r="B15" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C15">
         <v>600000</v>
@@ -22084,7 +21979,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.5">
       <c r="B16" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C16">
         <v>45000</v>
@@ -22095,7 +21990,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.5">
       <c r="B17" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C17">
         <v>150000</v>
@@ -22106,7 +22001,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.5">
       <c r="B18" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E18" s="1">
         <v>32000</v>
@@ -22114,10 +22009,10 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.5">
       <c r="B19" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D19" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E19" s="1">
         <v>1390000</v>
@@ -22125,7 +22020,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.5">
       <c r="B20" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C20">
         <v>14000</v>
@@ -22136,10 +22031,10 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.5">
       <c r="B21" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E21" s="1">
         <v>500000</v>
@@ -22409,12 +22304,12 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="1:9" x14ac:dyDescent="0.5">
       <c r="B4" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="G4">
         <f>100*3500</f>
@@ -22423,7 +22318,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B5">
         <v>53000</v>
@@ -22431,7 +22326,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B6">
         <v>30000</v>
@@ -22439,7 +22334,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B8">
         <v>54000</v>
@@ -22455,7 +22350,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B9">
         <v>30000</v>
@@ -22481,7 +22376,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B12">
         <v>54000</v>
@@ -22850,7 +22745,7 @@
     <row r="12" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C12" s="4">
         <v>-300</v>
@@ -22881,7 +22776,7 @@
     <row r="13" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A13" s="3"/>
       <c r="B13" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C13" s="4">
         <v>380</v>
@@ -22912,7 +22807,7 @@
     <row r="14" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C14" s="4">
         <v>198</v>
@@ -22943,7 +22838,7 @@
     <row r="15" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C15" s="4">
         <v>192</v>
@@ -22972,7 +22867,7 @@
     <row r="16" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C16" s="4">
         <v>202</v>
@@ -23242,7 +23137,7 @@
     <row r="27" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A27" s="3"/>
       <c r="B27" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C27" s="4">
         <f>G4-D24</f>
@@ -23847,7 +23742,7 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C11" s="4">
         <v>-500</v>
@@ -23881,7 +23776,7 @@
     <row r="12" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C12" s="4">
         <v>100</v>
@@ -23912,7 +23807,7 @@
     <row r="13" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A13" s="3"/>
       <c r="B13" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C13" s="4">
         <v>120</v>
@@ -24259,7 +24154,7 @@
     <row r="27" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A27" s="3"/>
       <c r="B27" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C27" s="4">
         <f>G4-D24</f>
@@ -24864,7 +24759,7 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -24896,7 +24791,7 @@
     <row r="12" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -24925,7 +24820,7 @@
     <row r="13" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A13" s="3"/>
       <c r="B13" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -25270,7 +25165,7 @@
     <row r="27" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A27" s="3"/>
       <c r="B27" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C27" s="4">
         <f>G4-D24</f>
@@ -25869,7 +25764,7 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C11" s="4">
         <v>1000</v>
@@ -25903,7 +25798,7 @@
     <row r="12" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C12" s="4">
         <v>150</v>
@@ -26066,7 +25961,7 @@
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F18" s="4">
         <v>1250</v>
@@ -26306,7 +26201,7 @@
     <row r="28" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A28" s="3"/>
       <c r="B28" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C28" s="4">
         <f>G4-D25</f>
@@ -26828,7 +26723,7 @@
     <row r="9" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A9" s="3"/>
       <c r="B9" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C9" s="4">
         <v>173</v>
@@ -26864,7 +26759,7 @@
     <row r="10" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C10" s="4">
         <v>763</v>
@@ -26900,7 +26795,7 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C11" s="4">
         <v>717</v>
@@ -26934,7 +26829,7 @@
     <row r="12" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C12" s="4">
         <v>-1000</v>
@@ -26965,7 +26860,7 @@
     <row r="13" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A13" s="3"/>
       <c r="B13" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C13" s="4">
         <v>686</v>
@@ -26996,7 +26891,7 @@
     <row r="14" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C14" s="4">
         <v>-2500</v>
@@ -27027,7 +26922,7 @@
     <row r="15" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C15" s="4">
         <v>-1000</v>
@@ -27341,7 +27236,7 @@
     <row r="28" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A28" s="3"/>
       <c r="B28" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C28" s="4">
         <f>G4-D25</f>
@@ -27863,7 +27758,7 @@
     <row r="9" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A9" s="3"/>
       <c r="B9" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C9" s="4">
         <v>350</v>
@@ -27899,7 +27794,7 @@
     <row r="10" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C10" s="4">
         <v>80</v>
@@ -27935,7 +27830,7 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C11" s="4">
         <v>123</v>
@@ -27969,7 +27864,7 @@
     <row r="12" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C12" s="4">
         <v>191</v>
@@ -28000,7 +27895,7 @@
     <row r="13" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A13" s="3"/>
       <c r="B13" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C13" s="4">
         <v>-3500</v>
@@ -28031,7 +27926,7 @@
     <row r="14" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C14" s="4">
         <v>-2000</v>
@@ -28062,7 +27957,7 @@
     <row r="15" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C15" s="4">
         <v>1250</v>
@@ -28384,7 +28279,7 @@
     <row r="28" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A28" s="3"/>
       <c r="B28" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C28" s="4">
         <f>ABS(G4-D25)</f>
@@ -28941,7 +28836,7 @@
     <row r="10" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C10" s="4">
         <v>177</v>
@@ -28977,7 +28872,7 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C11" s="4">
         <v>200</v>
@@ -29011,7 +28906,7 @@
     <row r="12" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A12" s="3"/>
       <c r="B12" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C12" s="4">
         <v>450</v>
@@ -29042,7 +28937,7 @@
     <row r="13" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A13" s="3"/>
       <c r="B13" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C13" s="4">
         <v>200</v>
@@ -29073,7 +28968,7 @@
     <row r="14" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C14" s="4">
         <v>200</v>
@@ -29182,7 +29077,7 @@
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F18" s="4">
         <v>1000</v>
@@ -29418,7 +29313,7 @@
     <row r="28" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A28" s="3"/>
       <c r="B28" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C28" s="4">
         <f>ABS(G4-D25)</f>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git-projet\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED0C9D8C-273F-4A79-911E-64176F42D3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A1EF4C-B9FD-4B6D-99A1-BDFEFF9AD01C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" firstSheet="19" activeTab="22" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
@@ -19728,7 +19728,7 @@
       </c>
       <c r="B20">
         <f>B6-F47</f>
-        <v>15600</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.5">
@@ -19918,7 +19918,7 @@
         <v>78</v>
       </c>
       <c r="B39" s="9">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C39" s="9">
         <v>1000</v>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="B47" s="10">
         <f>SUM(B27:B45)</f>
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="C47" s="10">
         <f>SUM(C27:C45)</f>
@@ -20013,7 +20013,7 @@
       </c>
       <c r="F47" s="10">
         <f>SUM(B47:E47)</f>
-        <v>10900</v>
+        <v>11000</v>
       </c>
     </row>
   </sheetData>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git-projet\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A1EF4C-B9FD-4B6D-99A1-BDFEFF9AD01C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E43B5FE-61D9-41AA-AA61-D5A4F30D5937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" firstSheet="19" activeTab="22" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1614" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="317">
   <si>
     <t>Loyer</t>
   </si>
@@ -1006,6 +1006,12 @@
   </si>
   <si>
     <t>R 5000</t>
+  </si>
+  <si>
+    <t>Lhat</t>
+  </si>
+  <si>
+    <t>esp</t>
   </si>
 </sst>
 </file>
@@ -19695,8 +19701,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.5">
       <c r="J14">
-        <f>SUM(J5:J12)</f>
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.5">
@@ -19705,7 +19710,7 @@
       </c>
       <c r="J16">
         <f>K4-J14</f>
-        <v>4000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.5">
@@ -19728,7 +19733,7 @@
       </c>
       <c r="B20">
         <f>B6-F47</f>
-        <v>15500</v>
+        <v>13100</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.5">
@@ -19759,7 +19764,7 @@
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="10" t="s">
-        <v>58</v>
+        <v>315</v>
       </c>
       <c r="F26" s="9"/>
     </row>
@@ -19923,9 +19928,7 @@
       <c r="C39" s="9">
         <v>1000</v>
       </c>
-      <c r="D39" s="9">
-        <v>500</v>
-      </c>
+      <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
     </row>
@@ -19933,9 +19936,13 @@
       <c r="A40" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B40" s="9"/>
+      <c r="B40" s="9">
+        <v>500</v>
+      </c>
       <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
+      <c r="D40" s="9">
+        <v>500</v>
+      </c>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
     </row>
@@ -19943,9 +19950,13 @@
       <c r="A41" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B41" s="9"/>
+      <c r="B41" s="9">
+        <v>400</v>
+      </c>
       <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
+      <c r="D41" s="9">
+        <v>500</v>
+      </c>
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
     </row>
@@ -19955,8 +19966,12 @@
       </c>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
+      <c r="D42" s="9">
+        <v>1000</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>316</v>
+      </c>
       <c r="F42" s="9"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.5">
@@ -19997,7 +20012,7 @@
       </c>
       <c r="B47" s="10">
         <f>SUM(B27:B45)</f>
-        <v>5000</v>
+        <v>5900</v>
       </c>
       <c r="C47" s="10">
         <f>SUM(C27:C45)</f>
@@ -20005,7 +20020,7 @@
       </c>
       <c r="D47" s="10">
         <f>SUM(D27:D45)</f>
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="E47" s="10">
         <f>SUM(E27:E45)</f>
@@ -20013,7 +20028,7 @@
       </c>
       <c r="F47" s="10">
         <f>SUM(B47:E47)</f>
-        <v>11000</v>
+        <v>13400</v>
       </c>
     </row>
   </sheetData>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git-projet\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E43B5FE-61D9-41AA-AA61-D5A4F30D5937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E87F322-1D2A-44ED-83A7-5595E02F4E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" firstSheet="19" activeTab="22" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1619" uniqueCount="317">
   <si>
     <t>Loyer</t>
   </si>
@@ -19699,8 +19699,17 @@
         <v>83</v>
       </c>
     </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.5">
+      <c r="J7">
+        <v>1000</v>
+      </c>
+      <c r="K7" t="s">
+        <v>84</v>
+      </c>
+    </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.5">
       <c r="J14">
+        <f>1000+1000</f>
         <v>2000</v>
       </c>
     </row>
@@ -19733,7 +19742,7 @@
       </c>
       <c r="B20">
         <f>B6-F47</f>
-        <v>13100</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.5">
@@ -19964,8 +19973,12 @@
       <c r="A42" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
+      <c r="B42" s="9">
+        <v>400</v>
+      </c>
+      <c r="C42" s="9">
+        <v>500</v>
+      </c>
       <c r="D42" s="9">
         <v>1000</v>
       </c>
@@ -19975,7 +19988,9 @@
       <c r="F42" s="9"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.5">
-      <c r="A43" s="9"/>
+      <c r="A43" s="9" t="s">
+        <v>85</v>
+      </c>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
@@ -19983,7 +19998,9 @@
       <c r="F43" s="9"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.5">
-      <c r="A44" s="9"/>
+      <c r="A44" s="9" t="s">
+        <v>65</v>
+      </c>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
@@ -19991,7 +20008,9 @@
       <c r="F44" s="9"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.5">
-      <c r="A45" s="9"/>
+      <c r="A45" s="9" t="s">
+        <v>86</v>
+      </c>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
@@ -20012,11 +20031,11 @@
       </c>
       <c r="B47" s="10">
         <f>SUM(B27:B45)</f>
-        <v>5900</v>
+        <v>6300</v>
       </c>
       <c r="C47" s="10">
         <f>SUM(C27:C45)</f>
-        <v>5500</v>
+        <v>6000</v>
       </c>
       <c r="D47" s="10">
         <f>SUM(D27:D45)</f>
@@ -20028,7 +20047,7 @@
       </c>
       <c r="F47" s="10">
         <f>SUM(B47:E47)</f>
-        <v>13400</v>
+        <v>14300</v>
       </c>
     </row>
   </sheetData>

--- a/Budget2.xlsx
+++ b/Budget2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git-projet\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E87F322-1D2A-44ED-83A7-5595E02F4E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A9C1B50-F41B-4289-A040-2D482859A564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" firstSheet="19" activeTab="22" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
@@ -42,7 +42,7 @@
     <sheet name="Terrain" sheetId="18" r:id="rId27"/>
     <sheet name="Poulayer" sheetId="54" r:id="rId28"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -19709,8 +19709,8 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.5">
       <c r="J14">
-        <f>1000+1000</f>
-        <v>2000</v>
+        <f>1000+1000+2000</f>
+        <v>4000</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.5">
@@ -19719,7 +19719,7 @@
       </c>
       <c r="J16">
         <f>K4-J14</f>
-        <v>3000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.5">
@@ -19742,7 +19742,7 @@
       </c>
       <c r="B20">
         <f>B6-F47</f>
-        <v>12200</v>
+        <v>8053</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.5">
@@ -19884,7 +19884,9 @@
       <c r="B35" s="9">
         <v>500</v>
       </c>
-      <c r="C35" s="9"/>
+      <c r="C35" s="9">
+        <v>2147</v>
+      </c>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
@@ -19991,7 +19993,9 @@
       <c r="A43" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B43" s="9"/>
+      <c r="B43" s="9">
+        <v>500</v>
+      </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
@@ -20002,7 +20006,9 @@
         <v>65</v>
       </c>
       <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
+      <c r="C44" s="9">
+        <v>1000</v>
+      </c>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
@@ -20011,7 +20017,9 @@
       <c r="A45" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B45" s="9"/>
+      <c r="B45" s="9">
+        <v>500</v>
+      </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
@@ -20031,11 +20039,11 @@
       </c>
       <c r="B47" s="10">
         <f>SUM(B27:B45)</f>
-        <v>6300</v>
+        <v>7300</v>
       </c>
       <c r="C47" s="10">
         <f>SUM(C27:C45)</f>
-        <v>6000</v>
+        <v>9147</v>
       </c>
       <c r="D47" s="10">
         <f>SUM(D27:D45)</f>
@@ -20047,7 +20055,7 @@
       </c>
       <c r="F47" s="10">
         <f>SUM(B47:E47)</f>
-        <v>14300</v>
+        <v>18447</v>
       </c>
     </row>
   </sheetData>
